--- a/output/Data and Chart Outputs/au_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/au_power_capacity.xlsx
@@ -911,27 +911,27 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Solar</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Nuclear &amp; other</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Gas</t>
-        </is>
-      </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Battery storage</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Hydro</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Battery storage</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -945,28 +945,28 @@
         <v>46296</v>
       </c>
       <c r="B2" t="n">
-        <v>22.4862</v>
+        <v>22.4911</v>
       </c>
       <c r="C2" t="n">
-        <v>15.2837</v>
+        <v>16.1477</v>
       </c>
       <c r="D2" t="n">
-        <v>14.9383</v>
+        <v>15.7117</v>
       </c>
       <c r="E2" t="n">
+        <v>15.072</v>
+      </c>
+      <c r="F2" t="n">
         <v>14.8416</v>
       </c>
-      <c r="F2" t="n">
-        <v>12.7163</v>
-      </c>
       <c r="G2" t="n">
-        <v>7.3877</v>
+        <v>13.7294</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8248</v>
+        <v>7.3899</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9536</v>
+        <v>1.2735</v>
       </c>
     </row>
   </sheetData>
@@ -981,7 +981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1017,27 +1017,32 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Oil_MW</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Bioenergy_MW</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Total_MW</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Battery_storage_MW</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Pumped_storage_MW</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>Other_MW</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Total_MW</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Battery_storage_MW</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Pumped_storage_MW</t>
         </is>
       </c>
     </row>
@@ -1046,34 +1051,37 @@
         <v>46296</v>
       </c>
       <c r="B2" t="n">
-        <v>7387.7</v>
+        <v>7389.9</v>
       </c>
       <c r="C2" t="n">
-        <v>12716.3</v>
+        <v>15711.7</v>
       </c>
       <c r="D2" t="n">
-        <v>15283.7</v>
+        <v>16147.7</v>
       </c>
       <c r="E2" t="n">
-        <v>14938.3</v>
+        <v>15072</v>
       </c>
       <c r="F2" t="n">
-        <v>22486.2</v>
+        <v>22491.1</v>
       </c>
       <c r="G2" t="n">
-        <v>247.7</v>
+        <v>160.5</v>
       </c>
       <c r="H2" t="n">
-        <v>14841.6</v>
+        <v>407.1</v>
       </c>
       <c r="I2" t="n">
-        <v>87901.5</v>
+        <v>77380.10000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>1824.8</v>
+        <v>13729.4</v>
       </c>
       <c r="K2" t="n">
         <v>705.9</v>
+      </c>
+      <c r="L2" t="n">
+        <v>14841.6</v>
       </c>
     </row>
   </sheetData>
@@ -1132,22 +1140,22 @@
         <v>46296</v>
       </c>
       <c r="B2" t="n">
-        <v>27671.6</v>
+        <v>23796.3</v>
       </c>
       <c r="C2" t="n">
-        <v>23874.1</v>
+        <v>20482.9</v>
       </c>
       <c r="D2" t="n">
-        <v>8275.4</v>
+        <v>6518.2</v>
       </c>
       <c r="E2" t="n">
         <v>3211.2</v>
       </c>
       <c r="F2" t="n">
-        <v>20299.9</v>
+        <v>17519.1</v>
       </c>
       <c r="G2" t="n">
-        <v>4569.2</v>
+        <v>5852.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/au_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/au_power_capacity.xlsx
@@ -791,7 +791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -839,38 +839,36 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>COVERAGE</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>COVERAGE</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NEM (QLD, NSW, VIC, SA, TAS) + WA's WEM. Rooftop solar, NT and off-grid plant not included. Series starts with the first run (Oct 2026) - AEMO publishes no capacity history in these lists.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NEM (QLD, NSW, VIC, SA, TAS) + WA's WEM. Rooftop solar, NT and off-grid plant not included. Series starts with the first run (Oct 2026) - AEMO publishes no capacity history in these lists.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AEMO NEM Registration and Exemption List: https://www.aemo.com.au/-/media/Files/Electricity/NEM/Participant_Information/NEM-Registration-and-Exemption-List.xls; AEMO WA facilities list: https://data.wa.aemo.com.au/public/public-data/datafiles/facilities/facilities.csv</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>SOURCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AEMO NEM Registration and Exemption List: https://www.aemo.com.au/-/media/Files/Electricity/NEM/Participant_Information/NEM-Registration-and-Exemption-List.xls; AEMO WA facilities list: https://data.wa.aemo.com.au/public/public-data/datafiles/facilities/facilities.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>https://aemo.com.au/en/energy-systems/electricity/national-electricity-market-nem/participate-in-the-market/registration</t>
         </is>
@@ -921,17 +919,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Nuclear &amp; other</t>
+          <t>Battery storage</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Battery storage</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Pumped storage</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -957,16 +955,16 @@
         <v>15.072</v>
       </c>
       <c r="F2" t="n">
-        <v>14.8416</v>
+        <v>13.7294</v>
       </c>
       <c r="G2" t="n">
-        <v>13.7294</v>
+        <v>7.3899</v>
       </c>
       <c r="H2" t="n">
-        <v>7.3899</v>
+        <v>0.7059</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2735</v>
+        <v>0.5676</v>
       </c>
     </row>
   </sheetData>
@@ -981,7 +979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1040,11 +1038,6 @@
           <t>Pumped_storage_MW</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Other_MW</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
@@ -1079,9 +1072,6 @@
       </c>
       <c r="K2" t="n">
         <v>705.9</v>
-      </c>
-      <c r="L2" t="n">
-        <v>14841.6</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/au_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/au_power_capacity.xlsx
@@ -791,7 +791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -839,36 +839,38 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>COVERAGE</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NEM (QLD, NSW, VIC, SA, TAS) + WA's WEM. Rooftop solar, NT and off-grid plant not included. Series starts with the first run (Oct 2026) - AEMO publishes no capacity history in these lists.</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NEM (QLD, NSW, VIC, SA, TAS) + WA's WEM. Rooftop solar, NT and off-grid plant not included. Months from Jan 2021 to Sep 2026: NEM rebuilt from AEMO MMS unit history (DUDETAIL registered capacity, DUDETAILSUMMARY registration dates); WEM held at its Oct 2026 snapshot. From Oct 2026: monthly snapshots of the registration lists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>SOURCE</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>AEMO NEM Registration and Exemption List: https://www.aemo.com.au/-/media/Files/Electricity/NEM/Participant_Information/NEM-Registration-and-Exemption-List.xls; AEMO WA facilities list: https://data.wa.aemo.com.au/public/public-data/datafiles/facilities/facilities.csv</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>https://aemo.com.au/en/energy-systems/electricity/national-electricity-market-nem/participate-in-the-market/registration</t>
         </is>

--- a/output/Data and Chart Outputs/au_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/au_power_capacity.xlsx
@@ -186,12 +186,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2</f>
+              <f>'Chart'!$B$2:$B$71</f>
             </numRef>
           </val>
         </ser>
@@ -214,12 +214,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2</f>
+              <f>'Chart'!$C$2:$C$71</f>
             </numRef>
           </val>
         </ser>
@@ -242,12 +242,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2</f>
+              <f>'Chart'!$D$2:$D$71</f>
             </numRef>
           </val>
         </ser>
@@ -270,12 +270,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2</f>
+              <f>'Chart'!$E$2:$E$71</f>
             </numRef>
           </val>
         </ser>
@@ -298,12 +298,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2</f>
+              <f>'Chart'!$F$2:$F$71</f>
             </numRef>
           </val>
         </ser>
@@ -326,12 +326,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2</f>
+              <f>'Chart'!$G$2:$G$71</f>
             </numRef>
           </val>
         </ser>
@@ -354,12 +354,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2</f>
+              <f>'Chart'!$H$2:$H$71</f>
             </numRef>
           </val>
         </ser>
@@ -382,12 +382,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2</f>
+              <f>'Chart'!$I$2:$I$71</f>
             </numRef>
           </val>
         </ser>
@@ -421,8 +421,8 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
+        <tickLblSkip val="5"/>
+        <tickMarkSkip val="5"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -887,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -906,12 +906,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Battery storage</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Battery storage</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -942,30 +942,2031 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B2" t="n">
+        <v>24.7351</v>
+      </c>
+      <c r="C2" t="n">
+        <v>14.9436</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9.702</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5.9048</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7.6836</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.538</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>44228</v>
+      </c>
+      <c r="B3" t="n">
+        <v>24.7351</v>
+      </c>
+      <c r="C3" t="n">
+        <v>14.9436</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9.882</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5.9558</v>
+      </c>
+      <c r="F3" t="n">
+        <v>7.6836</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.538</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>44256</v>
+      </c>
+      <c r="B4" t="n">
+        <v>24.7351</v>
+      </c>
+      <c r="C4" t="n">
+        <v>14.9436</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6.0628</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7.6836</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.538</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>44287</v>
+      </c>
+      <c r="B5" t="n">
+        <v>24.7351</v>
+      </c>
+      <c r="C5" t="n">
+        <v>14.9436</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6.2428</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7.6836</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.508</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>44317</v>
+      </c>
+      <c r="B6" t="n">
+        <v>24.7351</v>
+      </c>
+      <c r="C6" t="n">
+        <v>14.9436</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9.974</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6.2788</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7.6836</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.508</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>44348</v>
+      </c>
+      <c r="B7" t="n">
+        <v>24.7351</v>
+      </c>
+      <c r="C7" t="n">
+        <v>14.9436</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10.017</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6.5128</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7.6836</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.508</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>44378</v>
+      </c>
+      <c r="B8" t="n">
+        <v>24.7351</v>
+      </c>
+      <c r="C8" t="n">
+        <v>14.9436</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6.6878</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7.6836</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.508</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>44409</v>
+      </c>
+      <c r="B9" t="n">
+        <v>24.7351</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14.9436</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6.7038</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7.6836</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.508</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>44440</v>
+      </c>
+      <c r="B10" t="n">
+        <v>24.7351</v>
+      </c>
+      <c r="C10" t="n">
+        <v>14.8236</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10.578</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6.7038</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7.6836</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.508</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>44470</v>
+      </c>
+      <c r="B11" t="n">
+        <v>24.7351</v>
+      </c>
+      <c r="C11" t="n">
+        <v>14.8236</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10.578</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6.813800000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7.6836</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.508</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>44501</v>
+      </c>
+      <c r="B12" t="n">
+        <v>24.7351</v>
+      </c>
+      <c r="C12" t="n">
+        <v>14.8226</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10.578</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7.4478</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7.684600000000001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.509</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B13" t="n">
+        <v>24.7351</v>
+      </c>
+      <c r="C13" t="n">
+        <v>14.9766</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10.578</v>
+      </c>
+      <c r="E13" t="n">
+        <v>7.4478</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7.684600000000001</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.537</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B14" t="n">
+        <v>24.7351</v>
+      </c>
+      <c r="C14" t="n">
+        <v>14.9766</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10.578</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7.4608</v>
+      </c>
+      <c r="F14" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.537</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B15" t="n">
+        <v>24.7351</v>
+      </c>
+      <c r="C15" t="n">
+        <v>14.9766</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10.787</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7.643800000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.537</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>44621</v>
+      </c>
+      <c r="B16" t="n">
+        <v>24.7351</v>
+      </c>
+      <c r="C16" t="n">
+        <v>14.9766</v>
+      </c>
+      <c r="D16" t="n">
+        <v>10.997</v>
+      </c>
+      <c r="E16" t="n">
+        <v>7.7788</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.537</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>44652</v>
+      </c>
+      <c r="B17" t="n">
+        <v>24.1751</v>
+      </c>
+      <c r="C17" t="n">
+        <v>14.9766</v>
+      </c>
+      <c r="D17" t="n">
+        <v>10.997</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7.805800000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.537</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>44682</v>
+      </c>
+      <c r="B18" t="n">
+        <v>24.1751</v>
+      </c>
+      <c r="C18" t="n">
+        <v>14.9766</v>
+      </c>
+      <c r="D18" t="n">
+        <v>10.997</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8.027800000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.537</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>44713</v>
+      </c>
+      <c r="B19" t="n">
+        <v>24.1751</v>
+      </c>
+      <c r="C19" t="n">
+        <v>14.9766</v>
+      </c>
+      <c r="D19" t="n">
+        <v>11.154</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8.2448</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.537</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>44743</v>
+      </c>
+      <c r="B20" t="n">
+        <v>24.1751</v>
+      </c>
+      <c r="C20" t="n">
+        <v>14.9766</v>
+      </c>
+      <c r="D20" t="n">
+        <v>11.154</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8.2478</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>44774</v>
+      </c>
+      <c r="B21" t="n">
+        <v>24.1751</v>
+      </c>
+      <c r="C21" t="n">
+        <v>14.9786</v>
+      </c>
+      <c r="D21" t="n">
+        <v>11.154</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8.2478</v>
+      </c>
+      <c r="F21" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B22" t="n">
+        <v>24.1751</v>
+      </c>
+      <c r="C22" t="n">
+        <v>14.8586</v>
+      </c>
+      <c r="D22" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="E22" t="n">
+        <v>8.451799999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>44835</v>
+      </c>
+      <c r="B23" t="n">
+        <v>24.1751</v>
+      </c>
+      <c r="C23" t="n">
+        <v>14.8586</v>
+      </c>
+      <c r="D23" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="E23" t="n">
+        <v>8.550799999999999</v>
+      </c>
+      <c r="F23" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>44866</v>
+      </c>
+      <c r="B24" t="n">
+        <v>24.1751</v>
+      </c>
+      <c r="C24" t="n">
+        <v>14.9866</v>
+      </c>
+      <c r="D24" t="n">
+        <v>11.419</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8.550799999999999</v>
+      </c>
+      <c r="F24" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B25" t="n">
+        <v>24.1751</v>
+      </c>
+      <c r="C25" t="n">
+        <v>14.9866</v>
+      </c>
+      <c r="D25" t="n">
+        <v>11.419</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9.200799999999999</v>
+      </c>
+      <c r="F25" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B26" t="n">
+        <v>24.1751</v>
+      </c>
+      <c r="C26" t="n">
+        <v>14.9866</v>
+      </c>
+      <c r="D26" t="n">
+        <v>11.419</v>
+      </c>
+      <c r="E26" t="n">
+        <v>9.200799999999999</v>
+      </c>
+      <c r="F26" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>44958</v>
+      </c>
+      <c r="B27" t="n">
+        <v>24.1751</v>
+      </c>
+      <c r="C27" t="n">
+        <v>14.9866</v>
+      </c>
+      <c r="D27" t="n">
+        <v>11.419</v>
+      </c>
+      <c r="E27" t="n">
+        <v>9.3058</v>
+      </c>
+      <c r="F27" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B28" t="n">
+        <v>24.1751</v>
+      </c>
+      <c r="C28" t="n">
+        <v>14.9866</v>
+      </c>
+      <c r="D28" t="n">
+        <v>11.419</v>
+      </c>
+      <c r="E28" t="n">
+        <v>9.7188</v>
+      </c>
+      <c r="F28" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B29" t="n">
+        <v>24.1751</v>
+      </c>
+      <c r="C29" t="n">
+        <v>14.9866</v>
+      </c>
+      <c r="D29" t="n">
+        <v>11.599</v>
+      </c>
+      <c r="E29" t="n">
+        <v>9.7188</v>
+      </c>
+      <c r="F29" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>45047</v>
+      </c>
+      <c r="B30" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C30" t="n">
+        <v>14.9866</v>
+      </c>
+      <c r="D30" t="n">
+        <v>11.599</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9.7188</v>
+      </c>
+      <c r="F30" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B31" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C31" t="n">
+        <v>14.9866</v>
+      </c>
+      <c r="D31" t="n">
+        <v>11.599</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9.780799999999999</v>
+      </c>
+      <c r="F31" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B32" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C32" t="n">
+        <v>14.9866</v>
+      </c>
+      <c r="D32" t="n">
+        <v>11.808</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9.780799999999999</v>
+      </c>
+      <c r="F32" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.661</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>45139</v>
+      </c>
+      <c r="B33" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C33" t="n">
+        <v>14.9866</v>
+      </c>
+      <c r="D33" t="n">
+        <v>12.349</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9.780799999999999</v>
+      </c>
+      <c r="F33" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.661</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B34" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C34" t="n">
+        <v>14.9866</v>
+      </c>
+      <c r="D34" t="n">
+        <v>12.349</v>
+      </c>
+      <c r="E34" t="n">
+        <v>9.780799999999999</v>
+      </c>
+      <c r="F34" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.661</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B35" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C35" t="n">
+        <v>15.3606</v>
+      </c>
+      <c r="D35" t="n">
+        <v>12.349</v>
+      </c>
+      <c r="E35" t="n">
+        <v>9.780799999999999</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.661</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>45231</v>
+      </c>
+      <c r="B36" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C36" t="n">
+        <v>15.3606</v>
+      </c>
+      <c r="D36" t="n">
+        <v>12.552</v>
+      </c>
+      <c r="E36" t="n">
+        <v>9.906799999999999</v>
+      </c>
+      <c r="F36" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.861</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B37" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C37" t="n">
+        <v>15.3606</v>
+      </c>
+      <c r="D37" t="n">
+        <v>12.552</v>
+      </c>
+      <c r="E37" t="n">
+        <v>9.9438</v>
+      </c>
+      <c r="F37" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.861</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B38" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C38" t="n">
+        <v>15.3606</v>
+      </c>
+      <c r="D38" t="n">
+        <v>12.552</v>
+      </c>
+      <c r="E38" t="n">
+        <v>9.9438</v>
+      </c>
+      <c r="F38" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.861</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B39" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C39" t="n">
+        <v>15.3606</v>
+      </c>
+      <c r="D39" t="n">
+        <v>12.552</v>
+      </c>
+      <c r="E39" t="n">
+        <v>9.9438</v>
+      </c>
+      <c r="F39" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.861</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B40" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C40" t="n">
+        <v>15.3586</v>
+      </c>
+      <c r="D40" t="n">
+        <v>12.552</v>
+      </c>
+      <c r="E40" t="n">
+        <v>9.9438</v>
+      </c>
+      <c r="F40" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.861</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B41" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C41" t="n">
+        <v>15.3586</v>
+      </c>
+      <c r="D41" t="n">
+        <v>12.552</v>
+      </c>
+      <c r="E41" t="n">
+        <v>9.9438</v>
+      </c>
+      <c r="F41" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.861</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B42" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C42" t="n">
+        <v>15.3586</v>
+      </c>
+      <c r="D42" t="n">
+        <v>12.705</v>
+      </c>
+      <c r="E42" t="n">
+        <v>10.3798</v>
+      </c>
+      <c r="F42" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.133</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B43" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C43" t="n">
+        <v>15.4006</v>
+      </c>
+      <c r="D43" t="n">
+        <v>12.705</v>
+      </c>
+      <c r="E43" t="n">
+        <v>10.3798</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.133</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B44" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C44" t="n">
+        <v>15.4006</v>
+      </c>
+      <c r="D44" t="n">
+        <v>12.923</v>
+      </c>
+      <c r="E44" t="n">
+        <v>10.4728</v>
+      </c>
+      <c r="F44" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2.283</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B45" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C45" t="n">
+        <v>15.4006</v>
+      </c>
+      <c r="D45" t="n">
+        <v>14.602</v>
+      </c>
+      <c r="E45" t="n">
+        <v>10.4728</v>
+      </c>
+      <c r="F45" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.881</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.575</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B46" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C46" t="n">
+        <v>15.4006</v>
+      </c>
+      <c r="D46" t="n">
+        <v>14.752</v>
+      </c>
+      <c r="E46" t="n">
+        <v>10.9218</v>
+      </c>
+      <c r="F46" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.575</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B47" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C47" t="n">
+        <v>15.4006</v>
+      </c>
+      <c r="D47" t="n">
+        <v>14.773</v>
+      </c>
+      <c r="E47" t="n">
+        <v>10.9148</v>
+      </c>
+      <c r="F47" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3.992</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B48" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C48" t="n">
+        <v>15.4006</v>
+      </c>
+      <c r="D48" t="n">
+        <v>14.773</v>
+      </c>
+      <c r="E48" t="n">
+        <v>11.0658</v>
+      </c>
+      <c r="F48" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G48" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B49" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C49" t="n">
+        <v>15.4006</v>
+      </c>
+      <c r="D49" t="n">
+        <v>14.769</v>
+      </c>
+      <c r="E49" t="n">
+        <v>11.9298</v>
+      </c>
+      <c r="F49" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4.037</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B50" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C50" t="n">
+        <v>15.4006</v>
+      </c>
+      <c r="D50" t="n">
+        <v>14.944</v>
+      </c>
+      <c r="E50" t="n">
+        <v>11.9298</v>
+      </c>
+      <c r="F50" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G50" t="n">
+        <v>4.222</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B51" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C51" t="n">
+        <v>15.3386</v>
+      </c>
+      <c r="D51" t="n">
+        <v>14.944</v>
+      </c>
+      <c r="E51" t="n">
+        <v>11.9298</v>
+      </c>
+      <c r="F51" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G51" t="n">
+        <v>4.222</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B52" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C52" t="n">
+        <v>16.0886</v>
+      </c>
+      <c r="D52" t="n">
+        <v>14.944</v>
+      </c>
+      <c r="E52" t="n">
+        <v>12.4648</v>
+      </c>
+      <c r="F52" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5.229</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B53" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C53" t="n">
+        <v>16.0886</v>
+      </c>
+      <c r="D53" t="n">
+        <v>15.047</v>
+      </c>
+      <c r="E53" t="n">
+        <v>12.4648</v>
+      </c>
+      <c r="F53" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5.369</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B54" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C54" t="n">
+        <v>16.0886</v>
+      </c>
+      <c r="D54" t="n">
+        <v>15.047</v>
+      </c>
+      <c r="E54" t="n">
+        <v>12.4648</v>
+      </c>
+      <c r="F54" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G54" t="n">
+        <v>5.638</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B55" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C55" t="n">
+        <v>16.0886</v>
+      </c>
+      <c r="D55" t="n">
+        <v>15.299</v>
+      </c>
+      <c r="E55" t="n">
+        <v>12.9568</v>
+      </c>
+      <c r="F55" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G55" t="n">
+        <v>6.265</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B56" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C56" t="n">
+        <v>16.0886</v>
+      </c>
+      <c r="D56" t="n">
+        <v>15.299</v>
+      </c>
+      <c r="E56" t="n">
+        <v>12.9568</v>
+      </c>
+      <c r="F56" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G56" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B57" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C57" t="n">
+        <v>16.0886</v>
+      </c>
+      <c r="D57" t="n">
+        <v>15.299</v>
+      </c>
+      <c r="E57" t="n">
+        <v>12.9568</v>
+      </c>
+      <c r="F57" t="n">
+        <v>7.6916</v>
+      </c>
+      <c r="G57" t="n">
+        <v>6.549</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B58" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C58" t="n">
+        <v>16.0886</v>
+      </c>
+      <c r="D58" t="n">
+        <v>15.293</v>
+      </c>
+      <c r="E58" t="n">
+        <v>13.4588</v>
+      </c>
+      <c r="F58" t="n">
+        <v>7.6966</v>
+      </c>
+      <c r="G58" t="n">
+        <v>8.266</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B59" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C59" t="n">
+        <v>16.0886</v>
+      </c>
+      <c r="D59" t="n">
+        <v>15.296</v>
+      </c>
+      <c r="E59" t="n">
+        <v>13.4588</v>
+      </c>
+      <c r="F59" t="n">
+        <v>7.6966</v>
+      </c>
+      <c r="G59" t="n">
+        <v>8.824</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B60" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C60" t="n">
+        <v>16.0886</v>
+      </c>
+      <c r="D60" t="n">
+        <v>15.296</v>
+      </c>
+      <c r="E60" t="n">
+        <v>14.0308</v>
+      </c>
+      <c r="F60" t="n">
+        <v>7.6966</v>
+      </c>
+      <c r="G60" t="n">
+        <v>8.824</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.571</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B61" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C61" t="n">
+        <v>16.0886</v>
+      </c>
+      <c r="D61" t="n">
+        <v>15.296</v>
+      </c>
+      <c r="E61" t="n">
+        <v>14.3988</v>
+      </c>
+      <c r="F61" t="n">
+        <v>7.6966</v>
+      </c>
+      <c r="G61" t="n">
+        <v>9.355</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.571</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B62" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C62" t="n">
+        <v>16.0886</v>
+      </c>
+      <c r="D62" t="n">
+        <v>15.872</v>
+      </c>
+      <c r="E62" t="n">
+        <v>14.5218</v>
+      </c>
+      <c r="F62" t="n">
+        <v>7.6966</v>
+      </c>
+      <c r="G62" t="n">
+        <v>9.355</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.571</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B63" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C63" t="n">
+        <v>16.0886</v>
+      </c>
+      <c r="D63" t="n">
+        <v>15.872</v>
+      </c>
+      <c r="E63" t="n">
+        <v>14.7168</v>
+      </c>
+      <c r="F63" t="n">
+        <v>7.6966</v>
+      </c>
+      <c r="G63" t="n">
+        <v>10.088</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.571</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B64" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C64" t="n">
+        <v>16.0886</v>
+      </c>
+      <c r="D64" t="n">
+        <v>15.872</v>
+      </c>
+      <c r="E64" t="n">
+        <v>14.7168</v>
+      </c>
+      <c r="F64" t="n">
+        <v>7.6966</v>
+      </c>
+      <c r="G64" t="n">
+        <v>11.104</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.571</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B65" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C65" t="n">
+        <v>16.0886</v>
+      </c>
+      <c r="D65" t="n">
+        <v>16.126</v>
+      </c>
+      <c r="E65" t="n">
+        <v>14.7478</v>
+      </c>
+      <c r="F65" t="n">
+        <v>7.6966</v>
+      </c>
+      <c r="G65" t="n">
+        <v>11.104</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.571</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B66" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C66" t="n">
+        <v>16.0886</v>
+      </c>
+      <c r="D66" t="n">
+        <v>16.126</v>
+      </c>
+      <c r="E66" t="n">
+        <v>14.7478</v>
+      </c>
+      <c r="F66" t="n">
+        <v>7.6966</v>
+      </c>
+      <c r="G66" t="n">
+        <v>11.384</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.571</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B67" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C67" t="n">
+        <v>16.0886</v>
+      </c>
+      <c r="D67" t="n">
+        <v>16.126</v>
+      </c>
+      <c r="E67" t="n">
+        <v>15.0578</v>
+      </c>
+      <c r="F67" t="n">
+        <v>7.7456</v>
+      </c>
+      <c r="G67" t="n">
+        <v>12.269</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.571</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B68" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C68" t="n">
+        <v>16.0886</v>
+      </c>
+      <c r="D68" t="n">
+        <v>16.126</v>
+      </c>
+      <c r="E68" t="n">
+        <v>15.0578</v>
+      </c>
+      <c r="F68" t="n">
+        <v>7.7456</v>
+      </c>
+      <c r="G68" t="n">
+        <v>12.613</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.571</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B69" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C69" t="n">
+        <v>16.0666</v>
+      </c>
+      <c r="D69" t="n">
+        <v>16.126</v>
+      </c>
+      <c r="E69" t="n">
+        <v>15.0578</v>
+      </c>
+      <c r="F69" t="n">
+        <v>7.743600000000001</v>
+      </c>
+      <c r="G69" t="n">
+        <v>12.964</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.5660000000000001</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>22.6751</v>
+      </c>
+      <c r="C70" t="n">
+        <v>16.0666</v>
+      </c>
+      <c r="D70" t="n">
+        <v>16.122</v>
+      </c>
+      <c r="E70" t="n">
+        <v>15.0028</v>
+      </c>
+      <c r="F70" t="n">
+        <v>7.743600000000001</v>
+      </c>
+      <c r="G70" t="n">
+        <v>11.722</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.5660000000000001</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
         <v>46296</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B71" t="n">
         <v>22.4911</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C71" t="n">
+        <v>15.7117</v>
+      </c>
+      <c r="D71" t="n">
         <v>16.1477</v>
       </c>
-      <c r="D2" t="n">
-        <v>15.7117</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="E71" t="n">
         <v>15.072</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F71" t="n">
+        <v>7.3899</v>
+      </c>
+      <c r="G71" t="n">
         <v>13.7294</v>
       </c>
-      <c r="G2" t="n">
-        <v>7.3899</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="H71" t="n">
         <v>0.7059</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I71" t="n">
         <v>0.5676</v>
       </c>
     </row>
@@ -981,7 +2982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1043,36 +3044,2451 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B2" t="n">
+        <v>7683.6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>14943.6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9702</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5904.8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24735.1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>161</v>
+      </c>
+      <c r="H2" t="n">
+        <v>377</v>
+      </c>
+      <c r="I2" t="n">
+        <v>63507</v>
+      </c>
+      <c r="J2" t="n">
+        <v>215</v>
+      </c>
+      <c r="K2" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>44228</v>
+      </c>
+      <c r="B3" t="n">
+        <v>7683.6</v>
+      </c>
+      <c r="C3" t="n">
+        <v>14943.6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9882</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5955.8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>24735.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>161</v>
+      </c>
+      <c r="H3" t="n">
+        <v>377</v>
+      </c>
+      <c r="I3" t="n">
+        <v>63738</v>
+      </c>
+      <c r="J3" t="n">
+        <v>215</v>
+      </c>
+      <c r="K3" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>44256</v>
+      </c>
+      <c r="B4" t="n">
+        <v>7683.6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>14943.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9890</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6062.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>24735.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>161</v>
+      </c>
+      <c r="H4" t="n">
+        <v>377</v>
+      </c>
+      <c r="I4" t="n">
+        <v>63853</v>
+      </c>
+      <c r="J4" t="n">
+        <v>215</v>
+      </c>
+      <c r="K4" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>44287</v>
+      </c>
+      <c r="B5" t="n">
+        <v>7683.6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>14943.6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9890</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6242.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>24735.1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>131</v>
+      </c>
+      <c r="H5" t="n">
+        <v>377</v>
+      </c>
+      <c r="I5" t="n">
+        <v>64003</v>
+      </c>
+      <c r="J5" t="n">
+        <v>215</v>
+      </c>
+      <c r="K5" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>44317</v>
+      </c>
+      <c r="B6" t="n">
+        <v>7683.6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>14943.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9974</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6278.8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>24735.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>131</v>
+      </c>
+      <c r="H6" t="n">
+        <v>377</v>
+      </c>
+      <c r="I6" t="n">
+        <v>64123</v>
+      </c>
+      <c r="J6" t="n">
+        <v>215</v>
+      </c>
+      <c r="K6" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>44348</v>
+      </c>
+      <c r="B7" t="n">
+        <v>7683.6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>14943.6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10017</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6512.8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>24735.1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>131</v>
+      </c>
+      <c r="H7" t="n">
+        <v>377</v>
+      </c>
+      <c r="I7" t="n">
+        <v>64400</v>
+      </c>
+      <c r="J7" t="n">
+        <v>217</v>
+      </c>
+      <c r="K7" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>44378</v>
+      </c>
+      <c r="B8" t="n">
+        <v>7683.6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>14943.6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10570</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6687.8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>24735.1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>131</v>
+      </c>
+      <c r="H8" t="n">
+        <v>377</v>
+      </c>
+      <c r="I8" t="n">
+        <v>65128</v>
+      </c>
+      <c r="J8" t="n">
+        <v>724</v>
+      </c>
+      <c r="K8" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>44409</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7683.6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14943.6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10570</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6703.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>24735.1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>131</v>
+      </c>
+      <c r="H9" t="n">
+        <v>377</v>
+      </c>
+      <c r="I9" t="n">
+        <v>65144</v>
+      </c>
+      <c r="J9" t="n">
+        <v>724</v>
+      </c>
+      <c r="K9" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>44440</v>
+      </c>
+      <c r="B10" t="n">
+        <v>7683.6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>14823.6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10578</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6703.8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>24735.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>131</v>
+      </c>
+      <c r="H10" t="n">
+        <v>377</v>
+      </c>
+      <c r="I10" t="n">
+        <v>65032</v>
+      </c>
+      <c r="J10" t="n">
+        <v>724</v>
+      </c>
+      <c r="K10" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>44470</v>
+      </c>
+      <c r="B11" t="n">
+        <v>7683.6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>14823.6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10578</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6813.8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>24735.1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>131</v>
+      </c>
+      <c r="H11" t="n">
+        <v>377</v>
+      </c>
+      <c r="I11" t="n">
+        <v>65142</v>
+      </c>
+      <c r="J11" t="n">
+        <v>774</v>
+      </c>
+      <c r="K11" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>44501</v>
+      </c>
+      <c r="B12" t="n">
+        <v>7684.6</v>
+      </c>
+      <c r="C12" t="n">
+        <v>14822.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10578</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7447.8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>24735.1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>132</v>
+      </c>
+      <c r="H12" t="n">
+        <v>377</v>
+      </c>
+      <c r="I12" t="n">
+        <v>65777</v>
+      </c>
+      <c r="J12" t="n">
+        <v>777</v>
+      </c>
+      <c r="K12" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B13" t="n">
+        <v>7684.6</v>
+      </c>
+      <c r="C13" t="n">
+        <v>14976.6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10578</v>
+      </c>
+      <c r="E13" t="n">
+        <v>7447.8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>24735.1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>160</v>
+      </c>
+      <c r="H13" t="n">
+        <v>377</v>
+      </c>
+      <c r="I13" t="n">
+        <v>65959</v>
+      </c>
+      <c r="J13" t="n">
+        <v>777</v>
+      </c>
+      <c r="K13" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B14" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C14" t="n">
+        <v>14976.6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10578</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7460.8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>24735.1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>160</v>
+      </c>
+      <c r="H14" t="n">
+        <v>377</v>
+      </c>
+      <c r="I14" t="n">
+        <v>65979</v>
+      </c>
+      <c r="J14" t="n">
+        <v>777</v>
+      </c>
+      <c r="K14" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B15" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>14976.6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10787</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7643.8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>24735.1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>160</v>
+      </c>
+      <c r="H15" t="n">
+        <v>377</v>
+      </c>
+      <c r="I15" t="n">
+        <v>66371</v>
+      </c>
+      <c r="J15" t="n">
+        <v>777</v>
+      </c>
+      <c r="K15" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>44621</v>
+      </c>
+      <c r="B16" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>14976.6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>10997</v>
+      </c>
+      <c r="E16" t="n">
+        <v>7778.8</v>
+      </c>
+      <c r="F16" t="n">
+        <v>24735.1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>160</v>
+      </c>
+      <c r="H16" t="n">
+        <v>377</v>
+      </c>
+      <c r="I16" t="n">
+        <v>66716</v>
+      </c>
+      <c r="J16" t="n">
+        <v>777</v>
+      </c>
+      <c r="K16" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>44652</v>
+      </c>
+      <c r="B17" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>14976.6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>10997</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7805.8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>24175.1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>160</v>
+      </c>
+      <c r="H17" t="n">
+        <v>377</v>
+      </c>
+      <c r="I17" t="n">
+        <v>66183</v>
+      </c>
+      <c r="J17" t="n">
+        <v>782</v>
+      </c>
+      <c r="K17" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>44682</v>
+      </c>
+      <c r="B18" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>14976.6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>10997</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8027.8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>24175.1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>160</v>
+      </c>
+      <c r="H18" t="n">
+        <v>377</v>
+      </c>
+      <c r="I18" t="n">
+        <v>66405</v>
+      </c>
+      <c r="J18" t="n">
+        <v>782</v>
+      </c>
+      <c r="K18" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>44713</v>
+      </c>
+      <c r="B19" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>14976.6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>11154</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8244.799999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>24175.1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>160</v>
+      </c>
+      <c r="H19" t="n">
+        <v>377</v>
+      </c>
+      <c r="I19" t="n">
+        <v>66779</v>
+      </c>
+      <c r="J19" t="n">
+        <v>782</v>
+      </c>
+      <c r="K19" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>44743</v>
+      </c>
+      <c r="B20" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>14976.6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>11154</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8247.799999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>24175.1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>165</v>
+      </c>
+      <c r="H20" t="n">
+        <v>378</v>
+      </c>
+      <c r="I20" t="n">
+        <v>66788</v>
+      </c>
+      <c r="J20" t="n">
+        <v>792</v>
+      </c>
+      <c r="K20" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>44774</v>
+      </c>
+      <c r="B21" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C21" t="n">
+        <v>14978.6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>11154</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8247.799999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>24175.1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>165</v>
+      </c>
+      <c r="H21" t="n">
+        <v>378</v>
+      </c>
+      <c r="I21" t="n">
+        <v>66790</v>
+      </c>
+      <c r="J21" t="n">
+        <v>792</v>
+      </c>
+      <c r="K21" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B22" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C22" t="n">
+        <v>14858.6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>11310</v>
+      </c>
+      <c r="E22" t="n">
+        <v>8451.799999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>24175.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>165</v>
+      </c>
+      <c r="H22" t="n">
+        <v>378</v>
+      </c>
+      <c r="I22" t="n">
+        <v>67030</v>
+      </c>
+      <c r="J22" t="n">
+        <v>792</v>
+      </c>
+      <c r="K22" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>44835</v>
+      </c>
+      <c r="B23" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C23" t="n">
+        <v>14858.6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>11310</v>
+      </c>
+      <c r="E23" t="n">
+        <v>8550.799999999999</v>
+      </c>
+      <c r="F23" t="n">
+        <v>24175.1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>165</v>
+      </c>
+      <c r="H23" t="n">
+        <v>378</v>
+      </c>
+      <c r="I23" t="n">
+        <v>67129</v>
+      </c>
+      <c r="J23" t="n">
+        <v>792</v>
+      </c>
+      <c r="K23" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>44866</v>
+      </c>
+      <c r="B24" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C24" t="n">
+        <v>14986.6</v>
+      </c>
+      <c r="D24" t="n">
+        <v>11419</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8550.799999999999</v>
+      </c>
+      <c r="F24" t="n">
+        <v>24175.1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>165</v>
+      </c>
+      <c r="H24" t="n">
+        <v>378</v>
+      </c>
+      <c r="I24" t="n">
+        <v>67366</v>
+      </c>
+      <c r="J24" t="n">
+        <v>792</v>
+      </c>
+      <c r="K24" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B25" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C25" t="n">
+        <v>14986.6</v>
+      </c>
+      <c r="D25" t="n">
+        <v>11419</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9200.799999999999</v>
+      </c>
+      <c r="F25" t="n">
+        <v>24175.1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>165</v>
+      </c>
+      <c r="H25" t="n">
+        <v>378</v>
+      </c>
+      <c r="I25" t="n">
+        <v>68016</v>
+      </c>
+      <c r="J25" t="n">
+        <v>792</v>
+      </c>
+      <c r="K25" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B26" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C26" t="n">
+        <v>14986.6</v>
+      </c>
+      <c r="D26" t="n">
+        <v>11419</v>
+      </c>
+      <c r="E26" t="n">
+        <v>9200.799999999999</v>
+      </c>
+      <c r="F26" t="n">
+        <v>24175.1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>165</v>
+      </c>
+      <c r="H26" t="n">
+        <v>378</v>
+      </c>
+      <c r="I26" t="n">
+        <v>68016</v>
+      </c>
+      <c r="J26" t="n">
+        <v>792</v>
+      </c>
+      <c r="K26" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>44958</v>
+      </c>
+      <c r="B27" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C27" t="n">
+        <v>14986.6</v>
+      </c>
+      <c r="D27" t="n">
+        <v>11419</v>
+      </c>
+      <c r="E27" t="n">
+        <v>9305.799999999999</v>
+      </c>
+      <c r="F27" t="n">
+        <v>24175.1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>165</v>
+      </c>
+      <c r="H27" t="n">
+        <v>378</v>
+      </c>
+      <c r="I27" t="n">
+        <v>68121</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1042</v>
+      </c>
+      <c r="K27" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B28" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C28" t="n">
+        <v>14986.6</v>
+      </c>
+      <c r="D28" t="n">
+        <v>11419</v>
+      </c>
+      <c r="E28" t="n">
+        <v>9718.799999999999</v>
+      </c>
+      <c r="F28" t="n">
+        <v>24175.1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>165</v>
+      </c>
+      <c r="H28" t="n">
+        <v>378</v>
+      </c>
+      <c r="I28" t="n">
+        <v>68534</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1042</v>
+      </c>
+      <c r="K28" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B29" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C29" t="n">
+        <v>14986.6</v>
+      </c>
+      <c r="D29" t="n">
+        <v>11599</v>
+      </c>
+      <c r="E29" t="n">
+        <v>9718.799999999999</v>
+      </c>
+      <c r="F29" t="n">
+        <v>24175.1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>165</v>
+      </c>
+      <c r="H29" t="n">
+        <v>378</v>
+      </c>
+      <c r="I29" t="n">
+        <v>68714</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1299</v>
+      </c>
+      <c r="K29" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>45047</v>
+      </c>
+      <c r="B30" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C30" t="n">
+        <v>14986.6</v>
+      </c>
+      <c r="D30" t="n">
+        <v>11599</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9718.799999999999</v>
+      </c>
+      <c r="F30" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>165</v>
+      </c>
+      <c r="H30" t="n">
+        <v>378</v>
+      </c>
+      <c r="I30" t="n">
+        <v>67214</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1469</v>
+      </c>
+      <c r="K30" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B31" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C31" t="n">
+        <v>14986.6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>11599</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9780.799999999999</v>
+      </c>
+      <c r="F31" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>165</v>
+      </c>
+      <c r="H31" t="n">
+        <v>378</v>
+      </c>
+      <c r="I31" t="n">
+        <v>67276</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1469</v>
+      </c>
+      <c r="K31" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B32" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C32" t="n">
+        <v>14986.6</v>
+      </c>
+      <c r="D32" t="n">
+        <v>11808</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9780.799999999999</v>
+      </c>
+      <c r="F32" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>165</v>
+      </c>
+      <c r="H32" t="n">
+        <v>378</v>
+      </c>
+      <c r="I32" t="n">
+        <v>67485</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1661</v>
+      </c>
+      <c r="K32" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>45139</v>
+      </c>
+      <c r="B33" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C33" t="n">
+        <v>14986.6</v>
+      </c>
+      <c r="D33" t="n">
+        <v>12349</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9780.799999999999</v>
+      </c>
+      <c r="F33" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>165</v>
+      </c>
+      <c r="H33" t="n">
+        <v>378</v>
+      </c>
+      <c r="I33" t="n">
+        <v>68026</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1661</v>
+      </c>
+      <c r="K33" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B34" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C34" t="n">
+        <v>14986.6</v>
+      </c>
+      <c r="D34" t="n">
+        <v>12349</v>
+      </c>
+      <c r="E34" t="n">
+        <v>9780.799999999999</v>
+      </c>
+      <c r="F34" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>165</v>
+      </c>
+      <c r="H34" t="n">
+        <v>378</v>
+      </c>
+      <c r="I34" t="n">
+        <v>68026</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1661</v>
+      </c>
+      <c r="K34" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B35" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C35" t="n">
+        <v>15360.6</v>
+      </c>
+      <c r="D35" t="n">
+        <v>12349</v>
+      </c>
+      <c r="E35" t="n">
+        <v>9780.799999999999</v>
+      </c>
+      <c r="F35" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>165</v>
+      </c>
+      <c r="H35" t="n">
+        <v>378</v>
+      </c>
+      <c r="I35" t="n">
+        <v>68400</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1661</v>
+      </c>
+      <c r="K35" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>45231</v>
+      </c>
+      <c r="B36" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C36" t="n">
+        <v>15360.6</v>
+      </c>
+      <c r="D36" t="n">
+        <v>12552</v>
+      </c>
+      <c r="E36" t="n">
+        <v>9906.799999999999</v>
+      </c>
+      <c r="F36" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>165</v>
+      </c>
+      <c r="H36" t="n">
+        <v>378</v>
+      </c>
+      <c r="I36" t="n">
+        <v>68729</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1861</v>
+      </c>
+      <c r="K36" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B37" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C37" t="n">
+        <v>15360.6</v>
+      </c>
+      <c r="D37" t="n">
+        <v>12552</v>
+      </c>
+      <c r="E37" t="n">
+        <v>9943.799999999999</v>
+      </c>
+      <c r="F37" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>165</v>
+      </c>
+      <c r="H37" t="n">
+        <v>378</v>
+      </c>
+      <c r="I37" t="n">
+        <v>68766</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1861</v>
+      </c>
+      <c r="K37" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B38" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C38" t="n">
+        <v>15360.6</v>
+      </c>
+      <c r="D38" t="n">
+        <v>12552</v>
+      </c>
+      <c r="E38" t="n">
+        <v>9943.799999999999</v>
+      </c>
+      <c r="F38" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>165</v>
+      </c>
+      <c r="H38" t="n">
+        <v>378</v>
+      </c>
+      <c r="I38" t="n">
+        <v>68766</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1861</v>
+      </c>
+      <c r="K38" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B39" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C39" t="n">
+        <v>15360.6</v>
+      </c>
+      <c r="D39" t="n">
+        <v>12552</v>
+      </c>
+      <c r="E39" t="n">
+        <v>9943.799999999999</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>165</v>
+      </c>
+      <c r="H39" t="n">
+        <v>378</v>
+      </c>
+      <c r="I39" t="n">
+        <v>68766</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1861</v>
+      </c>
+      <c r="K39" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B40" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C40" t="n">
+        <v>15358.6</v>
+      </c>
+      <c r="D40" t="n">
+        <v>12552</v>
+      </c>
+      <c r="E40" t="n">
+        <v>9943.799999999999</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G40" t="n">
+        <v>165</v>
+      </c>
+      <c r="H40" t="n">
+        <v>378</v>
+      </c>
+      <c r="I40" t="n">
+        <v>68764</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1861</v>
+      </c>
+      <c r="K40" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B41" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C41" t="n">
+        <v>15358.6</v>
+      </c>
+      <c r="D41" t="n">
+        <v>12552</v>
+      </c>
+      <c r="E41" t="n">
+        <v>9943.799999999999</v>
+      </c>
+      <c r="F41" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>165</v>
+      </c>
+      <c r="H41" t="n">
+        <v>378</v>
+      </c>
+      <c r="I41" t="n">
+        <v>68764</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1861</v>
+      </c>
+      <c r="K41" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B42" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C42" t="n">
+        <v>15358.6</v>
+      </c>
+      <c r="D42" t="n">
+        <v>12705</v>
+      </c>
+      <c r="E42" t="n">
+        <v>10379.8</v>
+      </c>
+      <c r="F42" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>165</v>
+      </c>
+      <c r="H42" t="n">
+        <v>378</v>
+      </c>
+      <c r="I42" t="n">
+        <v>69353</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2133</v>
+      </c>
+      <c r="K42" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B43" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C43" t="n">
+        <v>15400.6</v>
+      </c>
+      <c r="D43" t="n">
+        <v>12705</v>
+      </c>
+      <c r="E43" t="n">
+        <v>10379.8</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>165</v>
+      </c>
+      <c r="H43" t="n">
+        <v>378</v>
+      </c>
+      <c r="I43" t="n">
+        <v>69395</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2133</v>
+      </c>
+      <c r="K43" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B44" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C44" t="n">
+        <v>15400.6</v>
+      </c>
+      <c r="D44" t="n">
+        <v>12923</v>
+      </c>
+      <c r="E44" t="n">
+        <v>10472.8</v>
+      </c>
+      <c r="F44" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G44" t="n">
+        <v>165</v>
+      </c>
+      <c r="H44" t="n">
+        <v>378</v>
+      </c>
+      <c r="I44" t="n">
+        <v>69706</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2283</v>
+      </c>
+      <c r="K44" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B45" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C45" t="n">
+        <v>15400.6</v>
+      </c>
+      <c r="D45" t="n">
+        <v>14602</v>
+      </c>
+      <c r="E45" t="n">
+        <v>10472.8</v>
+      </c>
+      <c r="F45" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>165</v>
+      </c>
+      <c r="H45" t="n">
+        <v>410</v>
+      </c>
+      <c r="I45" t="n">
+        <v>71417</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2881</v>
+      </c>
+      <c r="K45" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B46" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C46" t="n">
+        <v>15400.6</v>
+      </c>
+      <c r="D46" t="n">
+        <v>14752</v>
+      </c>
+      <c r="E46" t="n">
+        <v>10921.8</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>165</v>
+      </c>
+      <c r="H46" t="n">
+        <v>410</v>
+      </c>
+      <c r="I46" t="n">
+        <v>72016</v>
+      </c>
+      <c r="J46" t="n">
+        <v>4370</v>
+      </c>
+      <c r="K46" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B47" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C47" t="n">
+        <v>15400.6</v>
+      </c>
+      <c r="D47" t="n">
+        <v>14773</v>
+      </c>
+      <c r="E47" t="n">
+        <v>10914.8</v>
+      </c>
+      <c r="F47" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>163</v>
+      </c>
+      <c r="H47" t="n">
+        <v>410</v>
+      </c>
+      <c r="I47" t="n">
+        <v>72028</v>
+      </c>
+      <c r="J47" t="n">
+        <v>3992</v>
+      </c>
+      <c r="K47" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B48" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C48" t="n">
+        <v>15400.6</v>
+      </c>
+      <c r="D48" t="n">
+        <v>14773</v>
+      </c>
+      <c r="E48" t="n">
+        <v>11065.8</v>
+      </c>
+      <c r="F48" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>163</v>
+      </c>
+      <c r="H48" t="n">
+        <v>410</v>
+      </c>
+      <c r="I48" t="n">
+        <v>72179</v>
+      </c>
+      <c r="J48" t="n">
+        <v>4100</v>
+      </c>
+      <c r="K48" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B49" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C49" t="n">
+        <v>15400.6</v>
+      </c>
+      <c r="D49" t="n">
+        <v>14769</v>
+      </c>
+      <c r="E49" t="n">
+        <v>11929.8</v>
+      </c>
+      <c r="F49" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>163</v>
+      </c>
+      <c r="H49" t="n">
+        <v>410</v>
+      </c>
+      <c r="I49" t="n">
+        <v>73039</v>
+      </c>
+      <c r="J49" t="n">
+        <v>4037</v>
+      </c>
+      <c r="K49" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B50" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C50" t="n">
+        <v>15400.6</v>
+      </c>
+      <c r="D50" t="n">
+        <v>14944</v>
+      </c>
+      <c r="E50" t="n">
+        <v>11929.8</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G50" t="n">
+        <v>163</v>
+      </c>
+      <c r="H50" t="n">
+        <v>410</v>
+      </c>
+      <c r="I50" t="n">
+        <v>73214</v>
+      </c>
+      <c r="J50" t="n">
+        <v>4222</v>
+      </c>
+      <c r="K50" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B51" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C51" t="n">
+        <v>15338.6</v>
+      </c>
+      <c r="D51" t="n">
+        <v>14944</v>
+      </c>
+      <c r="E51" t="n">
+        <v>11929.8</v>
+      </c>
+      <c r="F51" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G51" t="n">
+        <v>163</v>
+      </c>
+      <c r="H51" t="n">
+        <v>410</v>
+      </c>
+      <c r="I51" t="n">
+        <v>73152</v>
+      </c>
+      <c r="J51" t="n">
+        <v>4222</v>
+      </c>
+      <c r="K51" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B52" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C52" t="n">
+        <v>16088.6</v>
+      </c>
+      <c r="D52" t="n">
+        <v>14944</v>
+      </c>
+      <c r="E52" t="n">
+        <v>12464.8</v>
+      </c>
+      <c r="F52" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G52" t="n">
+        <v>163</v>
+      </c>
+      <c r="H52" t="n">
+        <v>410</v>
+      </c>
+      <c r="I52" t="n">
+        <v>74437</v>
+      </c>
+      <c r="J52" t="n">
+        <v>5229</v>
+      </c>
+      <c r="K52" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B53" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C53" t="n">
+        <v>16088.6</v>
+      </c>
+      <c r="D53" t="n">
+        <v>15047</v>
+      </c>
+      <c r="E53" t="n">
+        <v>12464.8</v>
+      </c>
+      <c r="F53" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>163</v>
+      </c>
+      <c r="H53" t="n">
+        <v>410</v>
+      </c>
+      <c r="I53" t="n">
+        <v>74540</v>
+      </c>
+      <c r="J53" t="n">
+        <v>5369</v>
+      </c>
+      <c r="K53" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B54" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C54" t="n">
+        <v>16088.6</v>
+      </c>
+      <c r="D54" t="n">
+        <v>15047</v>
+      </c>
+      <c r="E54" t="n">
+        <v>12464.8</v>
+      </c>
+      <c r="F54" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>163</v>
+      </c>
+      <c r="H54" t="n">
+        <v>410</v>
+      </c>
+      <c r="I54" t="n">
+        <v>74540</v>
+      </c>
+      <c r="J54" t="n">
+        <v>5638</v>
+      </c>
+      <c r="K54" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B55" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C55" t="n">
+        <v>16088.6</v>
+      </c>
+      <c r="D55" t="n">
+        <v>15299</v>
+      </c>
+      <c r="E55" t="n">
+        <v>12956.8</v>
+      </c>
+      <c r="F55" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G55" t="n">
+        <v>163</v>
+      </c>
+      <c r="H55" t="n">
+        <v>410</v>
+      </c>
+      <c r="I55" t="n">
+        <v>75284</v>
+      </c>
+      <c r="J55" t="n">
+        <v>6265</v>
+      </c>
+      <c r="K55" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B56" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C56" t="n">
+        <v>16088.6</v>
+      </c>
+      <c r="D56" t="n">
+        <v>15299</v>
+      </c>
+      <c r="E56" t="n">
+        <v>12956.8</v>
+      </c>
+      <c r="F56" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>163</v>
+      </c>
+      <c r="H56" t="n">
+        <v>410</v>
+      </c>
+      <c r="I56" t="n">
+        <v>75284</v>
+      </c>
+      <c r="J56" t="n">
+        <v>6480</v>
+      </c>
+      <c r="K56" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B57" t="n">
+        <v>7691.6</v>
+      </c>
+      <c r="C57" t="n">
+        <v>16088.6</v>
+      </c>
+      <c r="D57" t="n">
+        <v>15299</v>
+      </c>
+      <c r="E57" t="n">
+        <v>12956.8</v>
+      </c>
+      <c r="F57" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>163</v>
+      </c>
+      <c r="H57" t="n">
+        <v>410</v>
+      </c>
+      <c r="I57" t="n">
+        <v>75284</v>
+      </c>
+      <c r="J57" t="n">
+        <v>6549</v>
+      </c>
+      <c r="K57" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B58" t="n">
+        <v>7696.6</v>
+      </c>
+      <c r="C58" t="n">
+        <v>16088.6</v>
+      </c>
+      <c r="D58" t="n">
+        <v>15293</v>
+      </c>
+      <c r="E58" t="n">
+        <v>13458.8</v>
+      </c>
+      <c r="F58" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>163</v>
+      </c>
+      <c r="H58" t="n">
+        <v>410</v>
+      </c>
+      <c r="I58" t="n">
+        <v>75785</v>
+      </c>
+      <c r="J58" t="n">
+        <v>8266</v>
+      </c>
+      <c r="K58" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B59" t="n">
+        <v>7696.6</v>
+      </c>
+      <c r="C59" t="n">
+        <v>16088.6</v>
+      </c>
+      <c r="D59" t="n">
+        <v>15296</v>
+      </c>
+      <c r="E59" t="n">
+        <v>13458.8</v>
+      </c>
+      <c r="F59" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>163</v>
+      </c>
+      <c r="H59" t="n">
+        <v>410</v>
+      </c>
+      <c r="I59" t="n">
+        <v>75788</v>
+      </c>
+      <c r="J59" t="n">
+        <v>8824</v>
+      </c>
+      <c r="K59" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B60" t="n">
+        <v>7696.6</v>
+      </c>
+      <c r="C60" t="n">
+        <v>16088.6</v>
+      </c>
+      <c r="D60" t="n">
+        <v>15296</v>
+      </c>
+      <c r="E60" t="n">
+        <v>14030.8</v>
+      </c>
+      <c r="F60" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G60" t="n">
+        <v>163</v>
+      </c>
+      <c r="H60" t="n">
+        <v>408</v>
+      </c>
+      <c r="I60" t="n">
+        <v>76358</v>
+      </c>
+      <c r="J60" t="n">
+        <v>8824</v>
+      </c>
+      <c r="K60" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B61" t="n">
+        <v>7696.6</v>
+      </c>
+      <c r="C61" t="n">
+        <v>16088.6</v>
+      </c>
+      <c r="D61" t="n">
+        <v>15296</v>
+      </c>
+      <c r="E61" t="n">
+        <v>14398.8</v>
+      </c>
+      <c r="F61" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>163</v>
+      </c>
+      <c r="H61" t="n">
+        <v>408</v>
+      </c>
+      <c r="I61" t="n">
+        <v>76726</v>
+      </c>
+      <c r="J61" t="n">
+        <v>9355</v>
+      </c>
+      <c r="K61" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B62" t="n">
+        <v>7696.6</v>
+      </c>
+      <c r="C62" t="n">
+        <v>16088.6</v>
+      </c>
+      <c r="D62" t="n">
+        <v>15872</v>
+      </c>
+      <c r="E62" t="n">
+        <v>14521.8</v>
+      </c>
+      <c r="F62" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G62" t="n">
+        <v>163</v>
+      </c>
+      <c r="H62" t="n">
+        <v>408</v>
+      </c>
+      <c r="I62" t="n">
+        <v>77425</v>
+      </c>
+      <c r="J62" t="n">
+        <v>9355</v>
+      </c>
+      <c r="K62" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B63" t="n">
+        <v>7696.6</v>
+      </c>
+      <c r="C63" t="n">
+        <v>16088.6</v>
+      </c>
+      <c r="D63" t="n">
+        <v>15872</v>
+      </c>
+      <c r="E63" t="n">
+        <v>14716.8</v>
+      </c>
+      <c r="F63" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G63" t="n">
+        <v>163</v>
+      </c>
+      <c r="H63" t="n">
+        <v>408</v>
+      </c>
+      <c r="I63" t="n">
+        <v>77620</v>
+      </c>
+      <c r="J63" t="n">
+        <v>10088</v>
+      </c>
+      <c r="K63" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B64" t="n">
+        <v>7696.6</v>
+      </c>
+      <c r="C64" t="n">
+        <v>16088.6</v>
+      </c>
+      <c r="D64" t="n">
+        <v>15872</v>
+      </c>
+      <c r="E64" t="n">
+        <v>14716.8</v>
+      </c>
+      <c r="F64" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>163</v>
+      </c>
+      <c r="H64" t="n">
+        <v>408</v>
+      </c>
+      <c r="I64" t="n">
+        <v>77620</v>
+      </c>
+      <c r="J64" t="n">
+        <v>11104</v>
+      </c>
+      <c r="K64" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B65" t="n">
+        <v>7696.6</v>
+      </c>
+      <c r="C65" t="n">
+        <v>16088.6</v>
+      </c>
+      <c r="D65" t="n">
+        <v>16126</v>
+      </c>
+      <c r="E65" t="n">
+        <v>14747.8</v>
+      </c>
+      <c r="F65" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>163</v>
+      </c>
+      <c r="H65" t="n">
+        <v>408</v>
+      </c>
+      <c r="I65" t="n">
+        <v>77905</v>
+      </c>
+      <c r="J65" t="n">
+        <v>11104</v>
+      </c>
+      <c r="K65" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B66" t="n">
+        <v>7696.6</v>
+      </c>
+      <c r="C66" t="n">
+        <v>16088.6</v>
+      </c>
+      <c r="D66" t="n">
+        <v>16126</v>
+      </c>
+      <c r="E66" t="n">
+        <v>14747.8</v>
+      </c>
+      <c r="F66" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>163</v>
+      </c>
+      <c r="H66" t="n">
+        <v>408</v>
+      </c>
+      <c r="I66" t="n">
+        <v>77905</v>
+      </c>
+      <c r="J66" t="n">
+        <v>11384</v>
+      </c>
+      <c r="K66" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B67" t="n">
+        <v>7745.6</v>
+      </c>
+      <c r="C67" t="n">
+        <v>16088.6</v>
+      </c>
+      <c r="D67" t="n">
+        <v>16126</v>
+      </c>
+      <c r="E67" t="n">
+        <v>15057.8</v>
+      </c>
+      <c r="F67" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>163</v>
+      </c>
+      <c r="H67" t="n">
+        <v>408</v>
+      </c>
+      <c r="I67" t="n">
+        <v>78264</v>
+      </c>
+      <c r="J67" t="n">
+        <v>12269</v>
+      </c>
+      <c r="K67" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B68" t="n">
+        <v>7745.6</v>
+      </c>
+      <c r="C68" t="n">
+        <v>16088.6</v>
+      </c>
+      <c r="D68" t="n">
+        <v>16126</v>
+      </c>
+      <c r="E68" t="n">
+        <v>15057.8</v>
+      </c>
+      <c r="F68" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>163</v>
+      </c>
+      <c r="H68" t="n">
+        <v>408</v>
+      </c>
+      <c r="I68" t="n">
+        <v>78264</v>
+      </c>
+      <c r="J68" t="n">
+        <v>12613</v>
+      </c>
+      <c r="K68" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B69" t="n">
+        <v>7743.6</v>
+      </c>
+      <c r="C69" t="n">
+        <v>16066.6</v>
+      </c>
+      <c r="D69" t="n">
+        <v>16126</v>
+      </c>
+      <c r="E69" t="n">
+        <v>15057.8</v>
+      </c>
+      <c r="F69" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>163</v>
+      </c>
+      <c r="H69" t="n">
+        <v>403</v>
+      </c>
+      <c r="I69" t="n">
+        <v>78235</v>
+      </c>
+      <c r="J69" t="n">
+        <v>12964</v>
+      </c>
+      <c r="K69" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>7743.6</v>
+      </c>
+      <c r="C70" t="n">
+        <v>16066.6</v>
+      </c>
+      <c r="D70" t="n">
+        <v>16122</v>
+      </c>
+      <c r="E70" t="n">
+        <v>15002.8</v>
+      </c>
+      <c r="F70" t="n">
+        <v>22675.1</v>
+      </c>
+      <c r="G70" t="n">
+        <v>163</v>
+      </c>
+      <c r="H70" t="n">
+        <v>403</v>
+      </c>
+      <c r="I70" t="n">
+        <v>78176</v>
+      </c>
+      <c r="J70" t="n">
+        <v>11722</v>
+      </c>
+      <c r="K70" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
         <v>46296</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B71" t="n">
         <v>7389.9</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C71" t="n">
         <v>15711.7</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D71" t="n">
         <v>16147.7</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E71" t="n">
         <v>15072</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F71" t="n">
         <v>22491.1</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G71" t="n">
         <v>160.5</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H71" t="n">
         <v>407.1</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I71" t="n">
         <v>77380.10000000001</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J71" t="n">
         <v>13729.4</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K71" t="n">
         <v>705.9</v>
       </c>
     </row>
@@ -1087,7 +5503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,24 +5545,1611 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B2" t="n">
+        <v>19976</v>
+      </c>
+      <c r="C2" t="n">
+        <v>14917</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5850</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F2" t="n">
+        <v>13549.6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>44228</v>
+      </c>
+      <c r="B3" t="n">
+        <v>20012</v>
+      </c>
+      <c r="C3" t="n">
+        <v>14917</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5865</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F3" t="n">
+        <v>13729.6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>44256</v>
+      </c>
+      <c r="B4" t="n">
+        <v>20012</v>
+      </c>
+      <c r="C4" t="n">
+        <v>14917</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5865</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F4" t="n">
+        <v>13844.6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>44287</v>
+      </c>
+      <c r="B5" t="n">
+        <v>20012</v>
+      </c>
+      <c r="C5" t="n">
+        <v>15049</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5883</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13844.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>44317</v>
+      </c>
+      <c r="B6" t="n">
+        <v>20132</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15049</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5883</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F6" t="n">
+        <v>13844.6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>44348</v>
+      </c>
+      <c r="B7" t="n">
+        <v>20331</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15127</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5883</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F7" t="n">
+        <v>13844.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>44378</v>
+      </c>
+      <c r="B8" t="n">
+        <v>20506</v>
+      </c>
+      <c r="C8" t="n">
+        <v>15127</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5883</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F8" t="n">
+        <v>14397.6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>44409</v>
+      </c>
+      <c r="B9" t="n">
+        <v>20506</v>
+      </c>
+      <c r="C9" t="n">
+        <v>15127</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5899</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14397.6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>44440</v>
+      </c>
+      <c r="B10" t="n">
+        <v>20506</v>
+      </c>
+      <c r="C10" t="n">
+        <v>15127</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5779</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F10" t="n">
+        <v>14405.6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>44470</v>
+      </c>
+      <c r="B11" t="n">
+        <v>20616</v>
+      </c>
+      <c r="C11" t="n">
+        <v>15127</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5779</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F11" t="n">
+        <v>14405.6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>44501</v>
+      </c>
+      <c r="B12" t="n">
+        <v>20726</v>
+      </c>
+      <c r="C12" t="n">
+        <v>15627</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5804</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F12" t="n">
+        <v>14405.6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B13" t="n">
+        <v>20754</v>
+      </c>
+      <c r="C13" t="n">
+        <v>15627</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5958</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F13" t="n">
+        <v>14405.6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B14" t="n">
+        <v>20761</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15627</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5971</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F14" t="n">
+        <v>14405.6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B15" t="n">
+        <v>20761</v>
+      </c>
+      <c r="C15" t="n">
+        <v>15810</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5971</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F15" t="n">
+        <v>14614.6</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>44621</v>
+      </c>
+      <c r="B16" t="n">
+        <v>20896</v>
+      </c>
+      <c r="C16" t="n">
+        <v>15810</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6181</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F16" t="n">
+        <v>14614.6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>44652</v>
+      </c>
+      <c r="B17" t="n">
+        <v>20396</v>
+      </c>
+      <c r="C17" t="n">
+        <v>15750</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6208</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F17" t="n">
+        <v>14614.6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>44682</v>
+      </c>
+      <c r="B18" t="n">
+        <v>20396</v>
+      </c>
+      <c r="C18" t="n">
+        <v>15972</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6208</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F18" t="n">
+        <v>14614.6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>44713</v>
+      </c>
+      <c r="B19" t="n">
+        <v>20396</v>
+      </c>
+      <c r="C19" t="n">
+        <v>16189</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6208</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F19" t="n">
+        <v>14771.6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>44743</v>
+      </c>
+      <c r="B20" t="n">
+        <v>20396</v>
+      </c>
+      <c r="C20" t="n">
+        <v>16189</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6217</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F20" t="n">
+        <v>14771.6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>44774</v>
+      </c>
+      <c r="B21" t="n">
+        <v>20398</v>
+      </c>
+      <c r="C21" t="n">
+        <v>16189</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6217</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F21" t="n">
+        <v>14771.6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B22" t="n">
+        <v>20503</v>
+      </c>
+      <c r="C22" t="n">
+        <v>16345</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6196</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F22" t="n">
+        <v>14771.6</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>44835</v>
+      </c>
+      <c r="B23" t="n">
+        <v>20503</v>
+      </c>
+      <c r="C23" t="n">
+        <v>16444</v>
+      </c>
+      <c r="D23" t="n">
+        <v>6196</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F23" t="n">
+        <v>14771.6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>44866</v>
+      </c>
+      <c r="B24" t="n">
+        <v>20503</v>
+      </c>
+      <c r="C24" t="n">
+        <v>16444</v>
+      </c>
+      <c r="D24" t="n">
+        <v>6324</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F24" t="n">
+        <v>14880.6</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B25" t="n">
+        <v>20973</v>
+      </c>
+      <c r="C25" t="n">
+        <v>16624</v>
+      </c>
+      <c r="D25" t="n">
+        <v>6324</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F25" t="n">
+        <v>14880.6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B26" t="n">
+        <v>20973</v>
+      </c>
+      <c r="C26" t="n">
+        <v>16624</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6324</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F26" t="n">
+        <v>14880.6</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>44958</v>
+      </c>
+      <c r="B27" t="n">
+        <v>21078</v>
+      </c>
+      <c r="C27" t="n">
+        <v>16624</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6324</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F27" t="n">
+        <v>14880.6</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B28" t="n">
+        <v>21227</v>
+      </c>
+      <c r="C28" t="n">
+        <v>16783</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6429</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F28" t="n">
+        <v>14880.6</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B29" t="n">
+        <v>21227</v>
+      </c>
+      <c r="C29" t="n">
+        <v>16963</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6429</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F29" t="n">
+        <v>14880.6</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>45047</v>
+      </c>
+      <c r="B30" t="n">
+        <v>19727</v>
+      </c>
+      <c r="C30" t="n">
+        <v>16963</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6429</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F30" t="n">
+        <v>14880.6</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B31" t="n">
+        <v>19789</v>
+      </c>
+      <c r="C31" t="n">
+        <v>16963</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6429</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F31" t="n">
+        <v>14880.6</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B32" t="n">
+        <v>19789</v>
+      </c>
+      <c r="C32" t="n">
+        <v>16963</v>
+      </c>
+      <c r="D32" t="n">
+        <v>6638</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F32" t="n">
+        <v>14880.6</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>45139</v>
+      </c>
+      <c r="B33" t="n">
+        <v>20330</v>
+      </c>
+      <c r="C33" t="n">
+        <v>16963</v>
+      </c>
+      <c r="D33" t="n">
+        <v>6638</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F33" t="n">
+        <v>14880.6</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B34" t="n">
+        <v>20330</v>
+      </c>
+      <c r="C34" t="n">
+        <v>16963</v>
+      </c>
+      <c r="D34" t="n">
+        <v>6638</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F34" t="n">
+        <v>14880.6</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B35" t="n">
+        <v>20704</v>
+      </c>
+      <c r="C35" t="n">
+        <v>16963</v>
+      </c>
+      <c r="D35" t="n">
+        <v>6638</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F35" t="n">
+        <v>14880.6</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>45231</v>
+      </c>
+      <c r="B36" t="n">
+        <v>20704</v>
+      </c>
+      <c r="C36" t="n">
+        <v>16963</v>
+      </c>
+      <c r="D36" t="n">
+        <v>6841</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F36" t="n">
+        <v>15006.6</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B37" t="n">
+        <v>20704</v>
+      </c>
+      <c r="C37" t="n">
+        <v>16963</v>
+      </c>
+      <c r="D37" t="n">
+        <v>6878</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F37" t="n">
+        <v>15006.6</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B38" t="n">
+        <v>20704</v>
+      </c>
+      <c r="C38" t="n">
+        <v>16963</v>
+      </c>
+      <c r="D38" t="n">
+        <v>6878</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F38" t="n">
+        <v>15006.6</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B39" t="n">
+        <v>20704</v>
+      </c>
+      <c r="C39" t="n">
+        <v>16963</v>
+      </c>
+      <c r="D39" t="n">
+        <v>6878</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F39" t="n">
+        <v>15006.6</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B40" t="n">
+        <v>20704</v>
+      </c>
+      <c r="C40" t="n">
+        <v>16963</v>
+      </c>
+      <c r="D40" t="n">
+        <v>6878</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F40" t="n">
+        <v>15004.6</v>
+      </c>
+      <c r="G40" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B41" t="n">
+        <v>20704</v>
+      </c>
+      <c r="C41" t="n">
+        <v>16963</v>
+      </c>
+      <c r="D41" t="n">
+        <v>6878</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F41" t="n">
+        <v>15004.6</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B42" t="n">
+        <v>21197</v>
+      </c>
+      <c r="C42" t="n">
+        <v>16963</v>
+      </c>
+      <c r="D42" t="n">
+        <v>6878</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F42" t="n">
+        <v>15100.6</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B43" t="n">
+        <v>21197</v>
+      </c>
+      <c r="C43" t="n">
+        <v>16963</v>
+      </c>
+      <c r="D43" t="n">
+        <v>6878</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F43" t="n">
+        <v>15142.6</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B44" t="n">
+        <v>21197</v>
+      </c>
+      <c r="C44" t="n">
+        <v>16963</v>
+      </c>
+      <c r="D44" t="n">
+        <v>6878</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F44" t="n">
+        <v>15453.6</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B45" t="n">
+        <v>21197</v>
+      </c>
+      <c r="C45" t="n">
+        <v>17918</v>
+      </c>
+      <c r="D45" t="n">
+        <v>6878</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F45" t="n">
+        <v>16209.6</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B46" t="n">
+        <v>21599</v>
+      </c>
+      <c r="C46" t="n">
+        <v>17965</v>
+      </c>
+      <c r="D46" t="n">
+        <v>7028</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F46" t="n">
+        <v>16209.6</v>
+      </c>
+      <c r="G46" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B47" t="n">
+        <v>21599</v>
+      </c>
+      <c r="C47" t="n">
+        <v>18136</v>
+      </c>
+      <c r="D47" t="n">
+        <v>6869</v>
+      </c>
+      <c r="E47" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F47" t="n">
+        <v>16209.6</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B48" t="n">
+        <v>21599</v>
+      </c>
+      <c r="C48" t="n">
+        <v>18136</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6869</v>
+      </c>
+      <c r="E48" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F48" t="n">
+        <v>16360.6</v>
+      </c>
+      <c r="G48" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B49" t="n">
+        <v>22426</v>
+      </c>
+      <c r="C49" t="n">
+        <v>18136</v>
+      </c>
+      <c r="D49" t="n">
+        <v>6869</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F49" t="n">
+        <v>16393.6</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B50" t="n">
+        <v>22426</v>
+      </c>
+      <c r="C50" t="n">
+        <v>18311</v>
+      </c>
+      <c r="D50" t="n">
+        <v>6869</v>
+      </c>
+      <c r="E50" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F50" t="n">
+        <v>16393.6</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B51" t="n">
+        <v>22364</v>
+      </c>
+      <c r="C51" t="n">
+        <v>18311</v>
+      </c>
+      <c r="D51" t="n">
+        <v>6869</v>
+      </c>
+      <c r="E51" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F51" t="n">
+        <v>16393.6</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B52" t="n">
+        <v>23114</v>
+      </c>
+      <c r="C52" t="n">
+        <v>18846</v>
+      </c>
+      <c r="D52" t="n">
+        <v>6869</v>
+      </c>
+      <c r="E52" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F52" t="n">
+        <v>16393.6</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B53" t="n">
+        <v>23114</v>
+      </c>
+      <c r="C53" t="n">
+        <v>18949</v>
+      </c>
+      <c r="D53" t="n">
+        <v>6869</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F53" t="n">
+        <v>16393.6</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B54" t="n">
+        <v>23114</v>
+      </c>
+      <c r="C54" t="n">
+        <v>18949</v>
+      </c>
+      <c r="D54" t="n">
+        <v>6869</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F54" t="n">
+        <v>16393.6</v>
+      </c>
+      <c r="G54" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B55" t="n">
+        <v>23580</v>
+      </c>
+      <c r="C55" t="n">
+        <v>19201</v>
+      </c>
+      <c r="D55" t="n">
+        <v>6869</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F55" t="n">
+        <v>16419.6</v>
+      </c>
+      <c r="G55" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B56" t="n">
+        <v>23580</v>
+      </c>
+      <c r="C56" t="n">
+        <v>19201</v>
+      </c>
+      <c r="D56" t="n">
+        <v>6869</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F56" t="n">
+        <v>16419.6</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B57" t="n">
+        <v>23580</v>
+      </c>
+      <c r="C57" t="n">
+        <v>19201</v>
+      </c>
+      <c r="D57" t="n">
+        <v>6869</v>
+      </c>
+      <c r="E57" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F57" t="n">
+        <v>16419.6</v>
+      </c>
+      <c r="G57" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B58" t="n">
+        <v>23580</v>
+      </c>
+      <c r="C58" t="n">
+        <v>19355</v>
+      </c>
+      <c r="D58" t="n">
+        <v>6869</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F58" t="n">
+        <v>16766.6</v>
+      </c>
+      <c r="G58" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B59" t="n">
+        <v>23580</v>
+      </c>
+      <c r="C59" t="n">
+        <v>19355</v>
+      </c>
+      <c r="D59" t="n">
+        <v>6872</v>
+      </c>
+      <c r="E59" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F59" t="n">
+        <v>16766.6</v>
+      </c>
+      <c r="G59" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B60" t="n">
+        <v>23842</v>
+      </c>
+      <c r="C60" t="n">
+        <v>19477</v>
+      </c>
+      <c r="D60" t="n">
+        <v>6872</v>
+      </c>
+      <c r="E60" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F60" t="n">
+        <v>16952.6</v>
+      </c>
+      <c r="G60" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B61" t="n">
+        <v>23842</v>
+      </c>
+      <c r="C61" t="n">
+        <v>19845</v>
+      </c>
+      <c r="D61" t="n">
+        <v>6872</v>
+      </c>
+      <c r="E61" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F61" t="n">
+        <v>16952.6</v>
+      </c>
+      <c r="G61" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B62" t="n">
+        <v>23965</v>
+      </c>
+      <c r="C62" t="n">
+        <v>19845</v>
+      </c>
+      <c r="D62" t="n">
+        <v>6872</v>
+      </c>
+      <c r="E62" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F62" t="n">
+        <v>17528.6</v>
+      </c>
+      <c r="G62" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B63" t="n">
+        <v>23965</v>
+      </c>
+      <c r="C63" t="n">
+        <v>19946</v>
+      </c>
+      <c r="D63" t="n">
+        <v>6872</v>
+      </c>
+      <c r="E63" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F63" t="n">
+        <v>17622.6</v>
+      </c>
+      <c r="G63" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B64" t="n">
+        <v>23965</v>
+      </c>
+      <c r="C64" t="n">
+        <v>19946</v>
+      </c>
+      <c r="D64" t="n">
+        <v>6872</v>
+      </c>
+      <c r="E64" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F64" t="n">
+        <v>17622.6</v>
+      </c>
+      <c r="G64" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B65" t="n">
+        <v>23996</v>
+      </c>
+      <c r="C65" t="n">
+        <v>20200</v>
+      </c>
+      <c r="D65" t="n">
+        <v>6872</v>
+      </c>
+      <c r="E65" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F65" t="n">
+        <v>17622.6</v>
+      </c>
+      <c r="G65" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B66" t="n">
+        <v>23996</v>
+      </c>
+      <c r="C66" t="n">
+        <v>20200</v>
+      </c>
+      <c r="D66" t="n">
+        <v>6872</v>
+      </c>
+      <c r="E66" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F66" t="n">
+        <v>17622.6</v>
+      </c>
+      <c r="G66" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B67" t="n">
+        <v>23996</v>
+      </c>
+      <c r="C67" t="n">
+        <v>20510</v>
+      </c>
+      <c r="D67" t="n">
+        <v>6872</v>
+      </c>
+      <c r="E67" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F67" t="n">
+        <v>17671.6</v>
+      </c>
+      <c r="G67" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B68" t="n">
+        <v>23996</v>
+      </c>
+      <c r="C68" t="n">
+        <v>20510</v>
+      </c>
+      <c r="D68" t="n">
+        <v>6872</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F68" t="n">
+        <v>17671.6</v>
+      </c>
+      <c r="G68" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B69" t="n">
+        <v>23994</v>
+      </c>
+      <c r="C69" t="n">
+        <v>20510</v>
+      </c>
+      <c r="D69" t="n">
+        <v>6872</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F69" t="n">
+        <v>17644.6</v>
+      </c>
+      <c r="G69" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>23939</v>
+      </c>
+      <c r="C70" t="n">
+        <v>20510</v>
+      </c>
+      <c r="D70" t="n">
+        <v>6872</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F70" t="n">
+        <v>17640.6</v>
+      </c>
+      <c r="G70" t="n">
+        <v>5852.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
         <v>46296</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B71" t="n">
         <v>23796.3</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C71" t="n">
         <v>20482.9</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D71" t="n">
         <v>6518.2</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E71" t="n">
         <v>3211.2</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F71" t="n">
         <v>17519.1</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G71" t="n">
         <v>5852.5</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/au_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/au_power_capacity.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Monthly" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="By region" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="History" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -850,7 +851,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NEM (QLD, NSW, VIC, SA, TAS) + WA's WEM. Rooftop solar, NT and off-grid plant not included. Months from Jan 2021 to Sep 2026: NEM rebuilt from AEMO MMS unit history (DUDETAIL registered capacity, DUDETAILSUMMARY registration dates); WEM held at its Oct 2026 snapshot. From Oct 2026: monthly snapshots of the registration lists.</t>
+          <t>NEM (QLD, NSW, VIC, SA, TAS) + WA's WEM. Rooftop solar, NT and off-grid plant not included. Months from Jan 2021 to Sep 2026: NEM rebuilt from AEMO MMS unit history (DUDETAIL registered capacity, DUDETAILSUMMARY registration dates); WEM from each facility's first month of output (and last month, for facilities no longer listed - their capacity is estimated as peak daily output / 24 h). From Oct 2026: monthly snapshots of the registration lists.</t>
         </is>
       </c>
     </row>
@@ -945,13 +946,13 @@
         <v>44197</v>
       </c>
       <c r="B2" t="n">
-        <v>24.7351</v>
+        <v>24.9341</v>
       </c>
       <c r="C2" t="n">
-        <v>14.9436</v>
+        <v>14.7523</v>
       </c>
       <c r="D2" t="n">
-        <v>9.702</v>
+        <v>9.8484</v>
       </c>
       <c r="E2" t="n">
         <v>5.9048</v>
@@ -960,13 +961,13 @@
         <v>7.6836</v>
       </c>
       <c r="G2" t="n">
-        <v>0.215</v>
+        <v>0.115</v>
       </c>
       <c r="H2" t="n">
         <v>0.579</v>
       </c>
       <c r="I2" t="n">
-        <v>0.538</v>
+        <v>0.5826</v>
       </c>
     </row>
     <row r="3">
@@ -974,13 +975,13 @@
         <v>44228</v>
       </c>
       <c r="B3" t="n">
-        <v>24.7351</v>
+        <v>24.9341</v>
       </c>
       <c r="C3" t="n">
-        <v>14.9436</v>
+        <v>14.7523</v>
       </c>
       <c r="D3" t="n">
-        <v>9.882</v>
+        <v>10.0284</v>
       </c>
       <c r="E3" t="n">
         <v>5.9558</v>
@@ -989,13 +990,13 @@
         <v>7.6836</v>
       </c>
       <c r="G3" t="n">
-        <v>0.215</v>
+        <v>0.115</v>
       </c>
       <c r="H3" t="n">
         <v>0.579</v>
       </c>
       <c r="I3" t="n">
-        <v>0.538</v>
+        <v>0.6669</v>
       </c>
     </row>
     <row r="4">
@@ -1003,13 +1004,13 @@
         <v>44256</v>
       </c>
       <c r="B4" t="n">
-        <v>24.7351</v>
+        <v>24.9341</v>
       </c>
       <c r="C4" t="n">
-        <v>14.9436</v>
+        <v>14.7903</v>
       </c>
       <c r="D4" t="n">
-        <v>9.890000000000001</v>
+        <v>10.0364</v>
       </c>
       <c r="E4" t="n">
         <v>6.0628</v>
@@ -1018,13 +1019,13 @@
         <v>7.6836</v>
       </c>
       <c r="G4" t="n">
-        <v>0.215</v>
+        <v>0.115</v>
       </c>
       <c r="H4" t="n">
         <v>0.579</v>
       </c>
       <c r="I4" t="n">
-        <v>0.538</v>
+        <v>0.6669</v>
       </c>
     </row>
     <row r="5">
@@ -1032,13 +1033,13 @@
         <v>44287</v>
       </c>
       <c r="B5" t="n">
-        <v>24.7351</v>
+        <v>24.9341</v>
       </c>
       <c r="C5" t="n">
-        <v>14.9436</v>
+        <v>14.8296</v>
       </c>
       <c r="D5" t="n">
-        <v>9.890000000000001</v>
+        <v>10.0364</v>
       </c>
       <c r="E5" t="n">
         <v>6.2428</v>
@@ -1047,13 +1048,13 @@
         <v>7.6836</v>
       </c>
       <c r="G5" t="n">
-        <v>0.215</v>
+        <v>0.115</v>
       </c>
       <c r="H5" t="n">
         <v>0.579</v>
       </c>
       <c r="I5" t="n">
-        <v>0.508</v>
+        <v>0.7189000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1061,13 +1062,13 @@
         <v>44317</v>
       </c>
       <c r="B6" t="n">
-        <v>24.7351</v>
+        <v>24.9341</v>
       </c>
       <c r="C6" t="n">
-        <v>14.9436</v>
+        <v>14.8296</v>
       </c>
       <c r="D6" t="n">
-        <v>9.974</v>
+        <v>10.1204</v>
       </c>
       <c r="E6" t="n">
         <v>6.2788</v>
@@ -1076,13 +1077,13 @@
         <v>7.6836</v>
       </c>
       <c r="G6" t="n">
-        <v>0.215</v>
+        <v>0.115</v>
       </c>
       <c r="H6" t="n">
         <v>0.579</v>
       </c>
       <c r="I6" t="n">
-        <v>0.508</v>
+        <v>0.7288</v>
       </c>
     </row>
     <row r="7">
@@ -1090,13 +1091,13 @@
         <v>44348</v>
       </c>
       <c r="B7" t="n">
-        <v>24.7351</v>
+        <v>24.9341</v>
       </c>
       <c r="C7" t="n">
-        <v>14.9436</v>
+        <v>14.8296</v>
       </c>
       <c r="D7" t="n">
-        <v>10.017</v>
+        <v>10.1634</v>
       </c>
       <c r="E7" t="n">
         <v>6.5128</v>
@@ -1105,13 +1106,13 @@
         <v>7.6836</v>
       </c>
       <c r="G7" t="n">
-        <v>0.217</v>
+        <v>0.117</v>
       </c>
       <c r="H7" t="n">
         <v>0.579</v>
       </c>
       <c r="I7" t="n">
-        <v>0.508</v>
+        <v>0.7288</v>
       </c>
     </row>
     <row r="8">
@@ -1119,13 +1120,13 @@
         <v>44378</v>
       </c>
       <c r="B8" t="n">
-        <v>24.7351</v>
+        <v>24.9341</v>
       </c>
       <c r="C8" t="n">
-        <v>14.9436</v>
+        <v>14.8296</v>
       </c>
       <c r="D8" t="n">
-        <v>10.57</v>
+        <v>10.7164</v>
       </c>
       <c r="E8" t="n">
         <v>6.6878</v>
@@ -1134,13 +1135,13 @@
         <v>7.6836</v>
       </c>
       <c r="G8" t="n">
-        <v>0.724</v>
+        <v>0.624</v>
       </c>
       <c r="H8" t="n">
         <v>0.579</v>
       </c>
       <c r="I8" t="n">
-        <v>0.508</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="9">
@@ -1148,13 +1149,13 @@
         <v>44409</v>
       </c>
       <c r="B9" t="n">
-        <v>24.7351</v>
+        <v>24.9341</v>
       </c>
       <c r="C9" t="n">
-        <v>14.9436</v>
+        <v>14.8296</v>
       </c>
       <c r="D9" t="n">
-        <v>10.57</v>
+        <v>10.7164</v>
       </c>
       <c r="E9" t="n">
         <v>6.7038</v>
@@ -1163,13 +1164,13 @@
         <v>7.6836</v>
       </c>
       <c r="G9" t="n">
-        <v>0.724</v>
+        <v>0.624</v>
       </c>
       <c r="H9" t="n">
         <v>0.579</v>
       </c>
       <c r="I9" t="n">
-        <v>0.508</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="10">
@@ -1177,13 +1178,13 @@
         <v>44440</v>
       </c>
       <c r="B10" t="n">
-        <v>24.7351</v>
+        <v>24.9341</v>
       </c>
       <c r="C10" t="n">
-        <v>14.8236</v>
+        <v>14.7096</v>
       </c>
       <c r="D10" t="n">
-        <v>10.578</v>
+        <v>10.7244</v>
       </c>
       <c r="E10" t="n">
         <v>6.7038</v>
@@ -1192,13 +1193,13 @@
         <v>7.6836</v>
       </c>
       <c r="G10" t="n">
-        <v>0.724</v>
+        <v>0.624</v>
       </c>
       <c r="H10" t="n">
         <v>0.579</v>
       </c>
       <c r="I10" t="n">
-        <v>0.508</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="11">
@@ -1206,13 +1207,13 @@
         <v>44470</v>
       </c>
       <c r="B11" t="n">
-        <v>24.7351</v>
+        <v>24.9341</v>
       </c>
       <c r="C11" t="n">
-        <v>14.8236</v>
+        <v>14.7096</v>
       </c>
       <c r="D11" t="n">
-        <v>10.578</v>
+        <v>10.7244</v>
       </c>
       <c r="E11" t="n">
         <v>6.813800000000001</v>
@@ -1221,13 +1222,13 @@
         <v>7.6836</v>
       </c>
       <c r="G11" t="n">
-        <v>0.774</v>
+        <v>0.674</v>
       </c>
       <c r="H11" t="n">
         <v>0.579</v>
       </c>
       <c r="I11" t="n">
-        <v>0.508</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="12">
@@ -1235,13 +1236,13 @@
         <v>44501</v>
       </c>
       <c r="B12" t="n">
-        <v>24.7351</v>
+        <v>24.9341</v>
       </c>
       <c r="C12" t="n">
-        <v>14.8226</v>
+        <v>14.7086</v>
       </c>
       <c r="D12" t="n">
-        <v>10.578</v>
+        <v>10.726</v>
       </c>
       <c r="E12" t="n">
         <v>7.4478</v>
@@ -1250,13 +1251,13 @@
         <v>7.684600000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>0.777</v>
+        <v>0.677</v>
       </c>
       <c r="H12" t="n">
         <v>0.579</v>
       </c>
       <c r="I12" t="n">
-        <v>0.509</v>
+        <v>0.7410000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1264,13 +1265,13 @@
         <v>44531</v>
       </c>
       <c r="B13" t="n">
-        <v>24.7351</v>
+        <v>24.9341</v>
       </c>
       <c r="C13" t="n">
-        <v>14.9766</v>
+        <v>14.7726</v>
       </c>
       <c r="D13" t="n">
-        <v>10.578</v>
+        <v>10.726</v>
       </c>
       <c r="E13" t="n">
         <v>7.4478</v>
@@ -1279,13 +1280,13 @@
         <v>7.684600000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.777</v>
+        <v>0.677</v>
       </c>
       <c r="H13" t="n">
         <v>0.579</v>
       </c>
       <c r="I13" t="n">
-        <v>0.537</v>
+        <v>0.769</v>
       </c>
     </row>
     <row r="14">
@@ -1293,13 +1294,13 @@
         <v>44562</v>
       </c>
       <c r="B14" t="n">
-        <v>24.7351</v>
+        <v>24.9341</v>
       </c>
       <c r="C14" t="n">
-        <v>14.9766</v>
+        <v>14.7726</v>
       </c>
       <c r="D14" t="n">
-        <v>10.578</v>
+        <v>10.726</v>
       </c>
       <c r="E14" t="n">
         <v>7.4608</v>
@@ -1308,13 +1309,13 @@
         <v>7.6916</v>
       </c>
       <c r="G14" t="n">
-        <v>0.777</v>
+        <v>0.677</v>
       </c>
       <c r="H14" t="n">
         <v>0.579</v>
       </c>
       <c r="I14" t="n">
-        <v>0.537</v>
+        <v>0.769</v>
       </c>
     </row>
     <row r="15">
@@ -1322,13 +1323,13 @@
         <v>44593</v>
       </c>
       <c r="B15" t="n">
-        <v>24.7351</v>
+        <v>24.9341</v>
       </c>
       <c r="C15" t="n">
-        <v>14.9766</v>
+        <v>14.7726</v>
       </c>
       <c r="D15" t="n">
-        <v>10.787</v>
+        <v>10.935</v>
       </c>
       <c r="E15" t="n">
         <v>7.643800000000001</v>
@@ -1337,13 +1338,13 @@
         <v>7.6916</v>
       </c>
       <c r="G15" t="n">
-        <v>0.777</v>
+        <v>0.677</v>
       </c>
       <c r="H15" t="n">
         <v>0.579</v>
       </c>
       <c r="I15" t="n">
-        <v>0.537</v>
+        <v>0.769</v>
       </c>
     </row>
     <row r="16">
@@ -1351,13 +1352,13 @@
         <v>44621</v>
       </c>
       <c r="B16" t="n">
-        <v>24.7351</v>
+        <v>24.9341</v>
       </c>
       <c r="C16" t="n">
-        <v>14.9766</v>
+        <v>14.7726</v>
       </c>
       <c r="D16" t="n">
-        <v>10.997</v>
+        <v>11.145</v>
       </c>
       <c r="E16" t="n">
         <v>7.7788</v>
@@ -1366,13 +1367,13 @@
         <v>7.6916</v>
       </c>
       <c r="G16" t="n">
-        <v>0.777</v>
+        <v>0.677</v>
       </c>
       <c r="H16" t="n">
         <v>0.579</v>
       </c>
       <c r="I16" t="n">
-        <v>0.537</v>
+        <v>0.769</v>
       </c>
     </row>
     <row r="17">
@@ -1380,13 +1381,13 @@
         <v>44652</v>
       </c>
       <c r="B17" t="n">
-        <v>24.1751</v>
+        <v>24.3741</v>
       </c>
       <c r="C17" t="n">
-        <v>14.9766</v>
+        <v>14.7726</v>
       </c>
       <c r="D17" t="n">
-        <v>10.997</v>
+        <v>11.145</v>
       </c>
       <c r="E17" t="n">
         <v>7.805800000000001</v>
@@ -1395,13 +1396,13 @@
         <v>7.6916</v>
       </c>
       <c r="G17" t="n">
-        <v>0.782</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H17" t="n">
         <v>0.579</v>
       </c>
       <c r="I17" t="n">
-        <v>0.537</v>
+        <v>0.769</v>
       </c>
     </row>
     <row r="18">
@@ -1409,13 +1410,13 @@
         <v>44682</v>
       </c>
       <c r="B18" t="n">
-        <v>24.1751</v>
+        <v>24.3741</v>
       </c>
       <c r="C18" t="n">
-        <v>14.9766</v>
+        <v>14.7726</v>
       </c>
       <c r="D18" t="n">
-        <v>10.997</v>
+        <v>11.145</v>
       </c>
       <c r="E18" t="n">
         <v>8.027800000000001</v>
@@ -1424,13 +1425,13 @@
         <v>7.6916</v>
       </c>
       <c r="G18" t="n">
-        <v>0.782</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H18" t="n">
         <v>0.579</v>
       </c>
       <c r="I18" t="n">
-        <v>0.537</v>
+        <v>0.769</v>
       </c>
     </row>
     <row r="19">
@@ -1438,13 +1439,13 @@
         <v>44713</v>
       </c>
       <c r="B19" t="n">
-        <v>24.1751</v>
+        <v>24.3741</v>
       </c>
       <c r="C19" t="n">
-        <v>14.9766</v>
+        <v>14.7726</v>
       </c>
       <c r="D19" t="n">
-        <v>11.154</v>
+        <v>11.302</v>
       </c>
       <c r="E19" t="n">
         <v>8.2448</v>
@@ -1453,13 +1454,13 @@
         <v>7.6916</v>
       </c>
       <c r="G19" t="n">
-        <v>0.782</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H19" t="n">
         <v>0.579</v>
       </c>
       <c r="I19" t="n">
-        <v>0.537</v>
+        <v>0.769</v>
       </c>
     </row>
     <row r="20">
@@ -1467,13 +1468,13 @@
         <v>44743</v>
       </c>
       <c r="B20" t="n">
-        <v>24.1751</v>
+        <v>24.3741</v>
       </c>
       <c r="C20" t="n">
-        <v>14.9766</v>
+        <v>14.7726</v>
       </c>
       <c r="D20" t="n">
-        <v>11.154</v>
+        <v>11.302</v>
       </c>
       <c r="E20" t="n">
         <v>8.2478</v>
@@ -1482,13 +1483,13 @@
         <v>7.6916</v>
       </c>
       <c r="G20" t="n">
-        <v>0.792</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H20" t="n">
         <v>0.579</v>
       </c>
       <c r="I20" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="21">
@@ -1496,13 +1497,13 @@
         <v>44774</v>
       </c>
       <c r="B21" t="n">
-        <v>24.1751</v>
+        <v>24.3741</v>
       </c>
       <c r="C21" t="n">
-        <v>14.9786</v>
+        <v>14.7746</v>
       </c>
       <c r="D21" t="n">
-        <v>11.154</v>
+        <v>11.302</v>
       </c>
       <c r="E21" t="n">
         <v>8.2478</v>
@@ -1511,13 +1512,13 @@
         <v>7.6916</v>
       </c>
       <c r="G21" t="n">
-        <v>0.792</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H21" t="n">
         <v>0.579</v>
       </c>
       <c r="I21" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="22">
@@ -1525,13 +1526,13 @@
         <v>44805</v>
       </c>
       <c r="B22" t="n">
-        <v>24.1751</v>
+        <v>24.3741</v>
       </c>
       <c r="C22" t="n">
-        <v>14.8586</v>
+        <v>14.6546</v>
       </c>
       <c r="D22" t="n">
-        <v>11.31</v>
+        <v>11.458</v>
       </c>
       <c r="E22" t="n">
         <v>8.451799999999999</v>
@@ -1540,13 +1541,13 @@
         <v>7.6916</v>
       </c>
       <c r="G22" t="n">
-        <v>0.792</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H22" t="n">
         <v>0.579</v>
       </c>
       <c r="I22" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="23">
@@ -1557,10 +1558,10 @@
         <v>24.1751</v>
       </c>
       <c r="C23" t="n">
-        <v>14.8586</v>
+        <v>14.6546</v>
       </c>
       <c r="D23" t="n">
-        <v>11.31</v>
+        <v>11.458</v>
       </c>
       <c r="E23" t="n">
         <v>8.550799999999999</v>
@@ -1569,13 +1570,13 @@
         <v>7.6916</v>
       </c>
       <c r="G23" t="n">
-        <v>0.792</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H23" t="n">
         <v>0.579</v>
       </c>
       <c r="I23" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="24">
@@ -1586,10 +1587,10 @@
         <v>24.1751</v>
       </c>
       <c r="C24" t="n">
-        <v>14.9866</v>
+        <v>14.7826</v>
       </c>
       <c r="D24" t="n">
-        <v>11.419</v>
+        <v>11.567</v>
       </c>
       <c r="E24" t="n">
         <v>8.550799999999999</v>
@@ -1598,13 +1599,13 @@
         <v>7.6916</v>
       </c>
       <c r="G24" t="n">
-        <v>0.792</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H24" t="n">
         <v>0.579</v>
       </c>
       <c r="I24" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="25">
@@ -1615,10 +1616,10 @@
         <v>24.1751</v>
       </c>
       <c r="C25" t="n">
-        <v>14.9866</v>
+        <v>14.7826</v>
       </c>
       <c r="D25" t="n">
-        <v>11.419</v>
+        <v>11.567</v>
       </c>
       <c r="E25" t="n">
         <v>9.200799999999999</v>
@@ -1627,13 +1628,13 @@
         <v>7.6916</v>
       </c>
       <c r="G25" t="n">
-        <v>0.792</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H25" t="n">
         <v>0.579</v>
       </c>
       <c r="I25" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="26">
@@ -1644,10 +1645,10 @@
         <v>24.1751</v>
       </c>
       <c r="C26" t="n">
-        <v>14.9866</v>
+        <v>14.7826</v>
       </c>
       <c r="D26" t="n">
-        <v>11.419</v>
+        <v>11.567</v>
       </c>
       <c r="E26" t="n">
         <v>9.200799999999999</v>
@@ -1656,13 +1657,13 @@
         <v>7.6916</v>
       </c>
       <c r="G26" t="n">
-        <v>0.792</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H26" t="n">
         <v>0.579</v>
       </c>
       <c r="I26" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="27">
@@ -1673,10 +1674,10 @@
         <v>24.1751</v>
       </c>
       <c r="C27" t="n">
-        <v>14.9866</v>
+        <v>14.7826</v>
       </c>
       <c r="D27" t="n">
-        <v>11.419</v>
+        <v>11.567</v>
       </c>
       <c r="E27" t="n">
         <v>9.3058</v>
@@ -1685,13 +1686,13 @@
         <v>7.6916</v>
       </c>
       <c r="G27" t="n">
-        <v>1.042</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="H27" t="n">
         <v>0.579</v>
       </c>
       <c r="I27" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="28">
@@ -1702,10 +1703,10 @@
         <v>24.1751</v>
       </c>
       <c r="C28" t="n">
-        <v>14.9866</v>
+        <v>14.7826</v>
       </c>
       <c r="D28" t="n">
-        <v>11.419</v>
+        <v>11.567</v>
       </c>
       <c r="E28" t="n">
         <v>9.7188</v>
@@ -1714,13 +1715,13 @@
         <v>7.6916</v>
       </c>
       <c r="G28" t="n">
-        <v>1.042</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="H28" t="n">
         <v>0.579</v>
       </c>
       <c r="I28" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="29">
@@ -1731,10 +1732,10 @@
         <v>24.1751</v>
       </c>
       <c r="C29" t="n">
-        <v>14.9866</v>
+        <v>14.7826</v>
       </c>
       <c r="D29" t="n">
-        <v>11.599</v>
+        <v>11.747</v>
       </c>
       <c r="E29" t="n">
         <v>9.7188</v>
@@ -1743,13 +1744,13 @@
         <v>7.6916</v>
       </c>
       <c r="G29" t="n">
-        <v>1.299</v>
+        <v>1.199</v>
       </c>
       <c r="H29" t="n">
         <v>0.579</v>
       </c>
       <c r="I29" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="30">
@@ -1760,10 +1761,10 @@
         <v>22.6751</v>
       </c>
       <c r="C30" t="n">
-        <v>14.9866</v>
+        <v>14.7826</v>
       </c>
       <c r="D30" t="n">
-        <v>11.599</v>
+        <v>11.747</v>
       </c>
       <c r="E30" t="n">
         <v>9.7188</v>
@@ -1778,7 +1779,7 @@
         <v>0.579</v>
       </c>
       <c r="I30" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="31">
@@ -1789,10 +1790,10 @@
         <v>22.6751</v>
       </c>
       <c r="C31" t="n">
-        <v>14.9866</v>
+        <v>14.7826</v>
       </c>
       <c r="D31" t="n">
-        <v>11.599</v>
+        <v>11.747</v>
       </c>
       <c r="E31" t="n">
         <v>9.780799999999999</v>
@@ -1807,7 +1808,7 @@
         <v>0.579</v>
       </c>
       <c r="I31" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="32">
@@ -1818,10 +1819,10 @@
         <v>22.6751</v>
       </c>
       <c r="C32" t="n">
-        <v>14.9866</v>
+        <v>14.7826</v>
       </c>
       <c r="D32" t="n">
-        <v>11.808</v>
+        <v>11.956</v>
       </c>
       <c r="E32" t="n">
         <v>9.780799999999999</v>
@@ -1836,7 +1837,7 @@
         <v>0.579</v>
       </c>
       <c r="I32" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="33">
@@ -1847,10 +1848,10 @@
         <v>22.6751</v>
       </c>
       <c r="C33" t="n">
-        <v>14.9866</v>
+        <v>14.7826</v>
       </c>
       <c r="D33" t="n">
-        <v>12.349</v>
+        <v>12.497</v>
       </c>
       <c r="E33" t="n">
         <v>9.780799999999999</v>
@@ -1865,7 +1866,7 @@
         <v>0.579</v>
       </c>
       <c r="I33" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="34">
@@ -1876,10 +1877,10 @@
         <v>22.6751</v>
       </c>
       <c r="C34" t="n">
-        <v>14.9866</v>
+        <v>14.7826</v>
       </c>
       <c r="D34" t="n">
-        <v>12.349</v>
+        <v>12.497</v>
       </c>
       <c r="E34" t="n">
         <v>9.780799999999999</v>
@@ -1894,7 +1895,7 @@
         <v>0.579</v>
       </c>
       <c r="I34" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="35">
@@ -1905,10 +1906,10 @@
         <v>22.6751</v>
       </c>
       <c r="C35" t="n">
-        <v>15.3606</v>
+        <v>15.1566</v>
       </c>
       <c r="D35" t="n">
-        <v>12.349</v>
+        <v>12.497</v>
       </c>
       <c r="E35" t="n">
         <v>9.780799999999999</v>
@@ -1923,7 +1924,7 @@
         <v>0.579</v>
       </c>
       <c r="I35" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="36">
@@ -1934,10 +1935,10 @@
         <v>22.6751</v>
       </c>
       <c r="C36" t="n">
-        <v>15.3606</v>
+        <v>15.1566</v>
       </c>
       <c r="D36" t="n">
-        <v>12.552</v>
+        <v>12.772</v>
       </c>
       <c r="E36" t="n">
         <v>9.906799999999999</v>
@@ -1952,7 +1953,7 @@
         <v>0.579</v>
       </c>
       <c r="I36" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="37">
@@ -1963,10 +1964,10 @@
         <v>22.6751</v>
       </c>
       <c r="C37" t="n">
-        <v>15.3606</v>
+        <v>15.1566</v>
       </c>
       <c r="D37" t="n">
-        <v>12.552</v>
+        <v>12.772</v>
       </c>
       <c r="E37" t="n">
         <v>9.9438</v>
@@ -1981,7 +1982,7 @@
         <v>0.579</v>
       </c>
       <c r="I37" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="38">
@@ -1992,10 +1993,10 @@
         <v>22.6751</v>
       </c>
       <c r="C38" t="n">
-        <v>15.3606</v>
+        <v>15.1566</v>
       </c>
       <c r="D38" t="n">
-        <v>12.552</v>
+        <v>12.772</v>
       </c>
       <c r="E38" t="n">
         <v>9.9438</v>
@@ -2010,7 +2011,7 @@
         <v>0.579</v>
       </c>
       <c r="I38" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="39">
@@ -2021,10 +2022,10 @@
         <v>22.6751</v>
       </c>
       <c r="C39" t="n">
-        <v>15.3606</v>
+        <v>15.1566</v>
       </c>
       <c r="D39" t="n">
-        <v>12.552</v>
+        <v>12.772</v>
       </c>
       <c r="E39" t="n">
         <v>9.9438</v>
@@ -2039,7 +2040,7 @@
         <v>0.579</v>
       </c>
       <c r="I39" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="40">
@@ -2050,10 +2051,10 @@
         <v>22.6751</v>
       </c>
       <c r="C40" t="n">
-        <v>15.3586</v>
+        <v>15.1546</v>
       </c>
       <c r="D40" t="n">
-        <v>12.552</v>
+        <v>12.772</v>
       </c>
       <c r="E40" t="n">
         <v>9.9438</v>
@@ -2068,7 +2069,7 @@
         <v>0.579</v>
       </c>
       <c r="I40" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="41">
@@ -2079,10 +2080,10 @@
         <v>22.6751</v>
       </c>
       <c r="C41" t="n">
-        <v>15.3586</v>
+        <v>15.1546</v>
       </c>
       <c r="D41" t="n">
-        <v>12.552</v>
+        <v>12.772</v>
       </c>
       <c r="E41" t="n">
         <v>9.9438</v>
@@ -2097,7 +2098,7 @@
         <v>0.579</v>
       </c>
       <c r="I41" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="42">
@@ -2108,10 +2109,10 @@
         <v>22.6751</v>
       </c>
       <c r="C42" t="n">
-        <v>15.3586</v>
+        <v>15.1546</v>
       </c>
       <c r="D42" t="n">
-        <v>12.705</v>
+        <v>12.925</v>
       </c>
       <c r="E42" t="n">
         <v>10.3798</v>
@@ -2126,7 +2127,7 @@
         <v>0.579</v>
       </c>
       <c r="I42" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="43">
@@ -2137,10 +2138,10 @@
         <v>22.6751</v>
       </c>
       <c r="C43" t="n">
-        <v>15.4006</v>
+        <v>15.1966</v>
       </c>
       <c r="D43" t="n">
-        <v>12.705</v>
+        <v>12.925</v>
       </c>
       <c r="E43" t="n">
         <v>10.3798</v>
@@ -2155,7 +2156,7 @@
         <v>0.579</v>
       </c>
       <c r="I43" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="44">
@@ -2166,10 +2167,10 @@
         <v>22.6751</v>
       </c>
       <c r="C44" t="n">
-        <v>15.4006</v>
+        <v>15.1966</v>
       </c>
       <c r="D44" t="n">
-        <v>12.923</v>
+        <v>13.143</v>
       </c>
       <c r="E44" t="n">
         <v>10.4728</v>
@@ -2184,7 +2185,7 @@
         <v>0.579</v>
       </c>
       <c r="I44" t="n">
-        <v>0.543</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="45">
@@ -2195,25 +2196,25 @@
         <v>22.6751</v>
       </c>
       <c r="C45" t="n">
-        <v>15.4006</v>
+        <v>15.1966</v>
       </c>
       <c r="D45" t="n">
-        <v>14.602</v>
+        <v>14.822</v>
       </c>
       <c r="E45" t="n">
-        <v>10.4728</v>
+        <v>10.5188</v>
       </c>
       <c r="F45" t="n">
         <v>7.6916</v>
       </c>
       <c r="G45" t="n">
-        <v>2.881</v>
+        <v>2.925</v>
       </c>
       <c r="H45" t="n">
         <v>0.579</v>
       </c>
       <c r="I45" t="n">
-        <v>0.575</v>
+        <v>0.8069999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -2224,25 +2225,25 @@
         <v>22.6751</v>
       </c>
       <c r="C46" t="n">
-        <v>15.4006</v>
+        <v>15.1966</v>
       </c>
       <c r="D46" t="n">
-        <v>14.752</v>
+        <v>14.972</v>
       </c>
       <c r="E46" t="n">
-        <v>10.9218</v>
+        <v>10.9678</v>
       </c>
       <c r="F46" t="n">
         <v>7.6916</v>
       </c>
       <c r="G46" t="n">
-        <v>4.37</v>
+        <v>4.414</v>
       </c>
       <c r="H46" t="n">
         <v>0.579</v>
       </c>
       <c r="I46" t="n">
-        <v>0.575</v>
+        <v>0.8069999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2253,25 +2254,25 @@
         <v>22.6751</v>
       </c>
       <c r="C47" t="n">
-        <v>15.4006</v>
+        <v>15.1966</v>
       </c>
       <c r="D47" t="n">
-        <v>14.773</v>
+        <v>14.993</v>
       </c>
       <c r="E47" t="n">
-        <v>10.9148</v>
+        <v>10.9608</v>
       </c>
       <c r="F47" t="n">
         <v>7.6916</v>
       </c>
       <c r="G47" t="n">
-        <v>3.992</v>
+        <v>4.089</v>
       </c>
       <c r="H47" t="n">
         <v>0.579</v>
       </c>
       <c r="I47" t="n">
-        <v>0.573</v>
+        <v>0.8049999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2282,25 +2283,25 @@
         <v>22.6751</v>
       </c>
       <c r="C48" t="n">
-        <v>15.4006</v>
+        <v>15.1966</v>
       </c>
       <c r="D48" t="n">
-        <v>14.773</v>
+        <v>14.993</v>
       </c>
       <c r="E48" t="n">
-        <v>11.0658</v>
+        <v>11.1118</v>
       </c>
       <c r="F48" t="n">
         <v>7.6916</v>
       </c>
       <c r="G48" t="n">
-        <v>4.1</v>
+        <v>4.197</v>
       </c>
       <c r="H48" t="n">
         <v>0.579</v>
       </c>
       <c r="I48" t="n">
-        <v>0.573</v>
+        <v>0.8049999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2311,25 +2312,25 @@
         <v>22.6751</v>
       </c>
       <c r="C49" t="n">
-        <v>15.4006</v>
+        <v>15.1966</v>
       </c>
       <c r="D49" t="n">
-        <v>14.769</v>
+        <v>14.989</v>
       </c>
       <c r="E49" t="n">
-        <v>11.9298</v>
+        <v>11.9758</v>
       </c>
       <c r="F49" t="n">
         <v>7.6916</v>
       </c>
       <c r="G49" t="n">
-        <v>4.037</v>
+        <v>4.134</v>
       </c>
       <c r="H49" t="n">
         <v>0.579</v>
       </c>
       <c r="I49" t="n">
-        <v>0.573</v>
+        <v>0.8049999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2340,25 +2341,25 @@
         <v>22.6751</v>
       </c>
       <c r="C50" t="n">
-        <v>15.4006</v>
+        <v>15.1966</v>
       </c>
       <c r="D50" t="n">
-        <v>14.944</v>
+        <v>15.164</v>
       </c>
       <c r="E50" t="n">
-        <v>11.9298</v>
+        <v>11.9758</v>
       </c>
       <c r="F50" t="n">
         <v>7.6916</v>
       </c>
       <c r="G50" t="n">
-        <v>4.222</v>
+        <v>4.319</v>
       </c>
       <c r="H50" t="n">
         <v>0.579</v>
       </c>
       <c r="I50" t="n">
-        <v>0.573</v>
+        <v>0.8049999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2369,25 +2370,25 @@
         <v>22.6751</v>
       </c>
       <c r="C51" t="n">
-        <v>15.3386</v>
+        <v>15.1346</v>
       </c>
       <c r="D51" t="n">
-        <v>14.944</v>
+        <v>15.164</v>
       </c>
       <c r="E51" t="n">
-        <v>11.9298</v>
+        <v>11.9758</v>
       </c>
       <c r="F51" t="n">
         <v>7.6916</v>
       </c>
       <c r="G51" t="n">
-        <v>4.222</v>
+        <v>4.319</v>
       </c>
       <c r="H51" t="n">
         <v>0.579</v>
       </c>
       <c r="I51" t="n">
-        <v>0.573</v>
+        <v>0.8049999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2398,25 +2399,25 @@
         <v>22.6751</v>
       </c>
       <c r="C52" t="n">
-        <v>16.0886</v>
+        <v>15.8846</v>
       </c>
       <c r="D52" t="n">
-        <v>14.944</v>
+        <v>15.164</v>
       </c>
       <c r="E52" t="n">
-        <v>12.4648</v>
+        <v>12.5108</v>
       </c>
       <c r="F52" t="n">
         <v>7.6916</v>
       </c>
       <c r="G52" t="n">
-        <v>5.229</v>
+        <v>5.326</v>
       </c>
       <c r="H52" t="n">
         <v>0.579</v>
       </c>
       <c r="I52" t="n">
-        <v>0.573</v>
+        <v>0.8049999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2427,25 +2428,25 @@
         <v>22.6751</v>
       </c>
       <c r="C53" t="n">
-        <v>16.0886</v>
+        <v>15.8846</v>
       </c>
       <c r="D53" t="n">
-        <v>15.047</v>
+        <v>15.267</v>
       </c>
       <c r="E53" t="n">
-        <v>12.4648</v>
+        <v>12.5108</v>
       </c>
       <c r="F53" t="n">
         <v>7.6916</v>
       </c>
       <c r="G53" t="n">
-        <v>5.369</v>
+        <v>5.527</v>
       </c>
       <c r="H53" t="n">
         <v>0.579</v>
       </c>
       <c r="I53" t="n">
-        <v>0.573</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="54">
@@ -2456,25 +2457,25 @@
         <v>22.6751</v>
       </c>
       <c r="C54" t="n">
-        <v>16.0886</v>
+        <v>15.8846</v>
       </c>
       <c r="D54" t="n">
-        <v>15.047</v>
+        <v>15.267</v>
       </c>
       <c r="E54" t="n">
-        <v>12.4648</v>
+        <v>12.5108</v>
       </c>
       <c r="F54" t="n">
         <v>7.6916</v>
       </c>
       <c r="G54" t="n">
-        <v>5.638</v>
+        <v>5.796</v>
       </c>
       <c r="H54" t="n">
         <v>0.579</v>
       </c>
       <c r="I54" t="n">
-        <v>0.573</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="55">
@@ -2485,25 +2486,25 @@
         <v>22.6751</v>
       </c>
       <c r="C55" t="n">
-        <v>16.0886</v>
+        <v>15.8846</v>
       </c>
       <c r="D55" t="n">
-        <v>15.299</v>
+        <v>15.519</v>
       </c>
       <c r="E55" t="n">
-        <v>12.9568</v>
+        <v>13.0028</v>
       </c>
       <c r="F55" t="n">
         <v>7.6916</v>
       </c>
       <c r="G55" t="n">
-        <v>6.265</v>
+        <v>6.423</v>
       </c>
       <c r="H55" t="n">
         <v>0.579</v>
       </c>
       <c r="I55" t="n">
-        <v>0.573</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="56">
@@ -2514,25 +2515,25 @@
         <v>22.6751</v>
       </c>
       <c r="C56" t="n">
-        <v>16.0886</v>
+        <v>15.8846</v>
       </c>
       <c r="D56" t="n">
-        <v>15.299</v>
+        <v>15.519</v>
       </c>
       <c r="E56" t="n">
-        <v>12.9568</v>
+        <v>13.0028</v>
       </c>
       <c r="F56" t="n">
         <v>7.6916</v>
       </c>
       <c r="G56" t="n">
-        <v>6.48</v>
+        <v>6.638</v>
       </c>
       <c r="H56" t="n">
         <v>0.579</v>
       </c>
       <c r="I56" t="n">
-        <v>0.573</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="57">
@@ -2543,25 +2544,25 @@
         <v>22.6751</v>
       </c>
       <c r="C57" t="n">
-        <v>16.0886</v>
+        <v>15.8846</v>
       </c>
       <c r="D57" t="n">
-        <v>15.299</v>
+        <v>15.519</v>
       </c>
       <c r="E57" t="n">
-        <v>12.9568</v>
+        <v>13.0028</v>
       </c>
       <c r="F57" t="n">
         <v>7.6916</v>
       </c>
       <c r="G57" t="n">
-        <v>6.549</v>
+        <v>6.707</v>
       </c>
       <c r="H57" t="n">
         <v>0.579</v>
       </c>
       <c r="I57" t="n">
-        <v>0.573</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="58">
@@ -2572,25 +2573,25 @@
         <v>22.6751</v>
       </c>
       <c r="C58" t="n">
-        <v>16.0886</v>
+        <v>15.8846</v>
       </c>
       <c r="D58" t="n">
-        <v>15.293</v>
+        <v>15.513</v>
       </c>
       <c r="E58" t="n">
-        <v>13.4588</v>
+        <v>13.5048</v>
       </c>
       <c r="F58" t="n">
         <v>7.6966</v>
       </c>
       <c r="G58" t="n">
-        <v>8.266</v>
+        <v>8.423999999999999</v>
       </c>
       <c r="H58" t="n">
         <v>0.579</v>
       </c>
       <c r="I58" t="n">
-        <v>0.573</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="59">
@@ -2601,25 +2602,25 @@
         <v>22.6751</v>
       </c>
       <c r="C59" t="n">
-        <v>16.0886</v>
+        <v>15.8846</v>
       </c>
       <c r="D59" t="n">
-        <v>15.296</v>
+        <v>15.516</v>
       </c>
       <c r="E59" t="n">
-        <v>13.4588</v>
+        <v>13.5048</v>
       </c>
       <c r="F59" t="n">
         <v>7.6966</v>
       </c>
       <c r="G59" t="n">
-        <v>8.824</v>
+        <v>9.035</v>
       </c>
       <c r="H59" t="n">
         <v>0.579</v>
       </c>
       <c r="I59" t="n">
-        <v>0.573</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="60">
@@ -2630,25 +2631,25 @@
         <v>22.6751</v>
       </c>
       <c r="C60" t="n">
-        <v>16.0886</v>
+        <v>15.8846</v>
       </c>
       <c r="D60" t="n">
-        <v>15.296</v>
+        <v>15.516</v>
       </c>
       <c r="E60" t="n">
-        <v>14.0308</v>
+        <v>14.0768</v>
       </c>
       <c r="F60" t="n">
         <v>7.6966</v>
       </c>
       <c r="G60" t="n">
-        <v>8.824</v>
+        <v>9.1</v>
       </c>
       <c r="H60" t="n">
         <v>0.831</v>
       </c>
       <c r="I60" t="n">
-        <v>0.571</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="61">
@@ -2659,25 +2660,25 @@
         <v>22.6751</v>
       </c>
       <c r="C61" t="n">
-        <v>16.0886</v>
+        <v>15.8846</v>
       </c>
       <c r="D61" t="n">
-        <v>15.296</v>
+        <v>15.516</v>
       </c>
       <c r="E61" t="n">
-        <v>14.3988</v>
+        <v>14.4448</v>
       </c>
       <c r="F61" t="n">
         <v>7.6966</v>
       </c>
       <c r="G61" t="n">
-        <v>9.355</v>
+        <v>9.631</v>
       </c>
       <c r="H61" t="n">
         <v>0.831</v>
       </c>
       <c r="I61" t="n">
-        <v>0.571</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="62">
@@ -2688,25 +2689,25 @@
         <v>22.6751</v>
       </c>
       <c r="C62" t="n">
-        <v>16.0886</v>
+        <v>15.8846</v>
       </c>
       <c r="D62" t="n">
-        <v>15.872</v>
+        <v>16.092</v>
       </c>
       <c r="E62" t="n">
-        <v>14.5218</v>
+        <v>14.5678</v>
       </c>
       <c r="F62" t="n">
         <v>7.6966</v>
       </c>
       <c r="G62" t="n">
-        <v>9.355</v>
+        <v>9.631</v>
       </c>
       <c r="H62" t="n">
         <v>0.831</v>
       </c>
       <c r="I62" t="n">
-        <v>0.571</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="63">
@@ -2717,25 +2718,25 @@
         <v>22.6751</v>
       </c>
       <c r="C63" t="n">
-        <v>16.0886</v>
+        <v>15.8846</v>
       </c>
       <c r="D63" t="n">
-        <v>15.872</v>
+        <v>16.092</v>
       </c>
       <c r="E63" t="n">
-        <v>14.7168</v>
+        <v>14.7628</v>
       </c>
       <c r="F63" t="n">
         <v>7.6966</v>
       </c>
       <c r="G63" t="n">
-        <v>10.088</v>
+        <v>10.364</v>
       </c>
       <c r="H63" t="n">
         <v>0.831</v>
       </c>
       <c r="I63" t="n">
-        <v>0.571</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="64">
@@ -2746,25 +2747,25 @@
         <v>22.6751</v>
       </c>
       <c r="C64" t="n">
-        <v>16.0886</v>
+        <v>15.8846</v>
       </c>
       <c r="D64" t="n">
-        <v>15.872</v>
+        <v>16.092</v>
       </c>
       <c r="E64" t="n">
-        <v>14.7168</v>
+        <v>14.7628</v>
       </c>
       <c r="F64" t="n">
         <v>7.6966</v>
       </c>
       <c r="G64" t="n">
-        <v>11.104</v>
+        <v>11.38</v>
       </c>
       <c r="H64" t="n">
         <v>0.831</v>
       </c>
       <c r="I64" t="n">
-        <v>0.571</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="65">
@@ -2775,25 +2776,25 @@
         <v>22.6751</v>
       </c>
       <c r="C65" t="n">
-        <v>16.0886</v>
+        <v>15.8846</v>
       </c>
       <c r="D65" t="n">
-        <v>16.126</v>
+        <v>16.346</v>
       </c>
       <c r="E65" t="n">
-        <v>14.7478</v>
+        <v>14.7938</v>
       </c>
       <c r="F65" t="n">
         <v>7.6966</v>
       </c>
       <c r="G65" t="n">
-        <v>11.104</v>
+        <v>11.38</v>
       </c>
       <c r="H65" t="n">
         <v>0.831</v>
       </c>
       <c r="I65" t="n">
-        <v>0.571</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="66">
@@ -2804,25 +2805,25 @@
         <v>22.6751</v>
       </c>
       <c r="C66" t="n">
-        <v>16.0886</v>
+        <v>15.8846</v>
       </c>
       <c r="D66" t="n">
-        <v>16.126</v>
+        <v>16.346</v>
       </c>
       <c r="E66" t="n">
-        <v>14.7478</v>
+        <v>14.7938</v>
       </c>
       <c r="F66" t="n">
         <v>7.6966</v>
       </c>
       <c r="G66" t="n">
-        <v>11.384</v>
+        <v>11.66</v>
       </c>
       <c r="H66" t="n">
         <v>0.831</v>
       </c>
       <c r="I66" t="n">
-        <v>0.571</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="67">
@@ -2833,25 +2834,25 @@
         <v>22.6751</v>
       </c>
       <c r="C67" t="n">
-        <v>16.0886</v>
+        <v>15.8846</v>
       </c>
       <c r="D67" t="n">
-        <v>16.126</v>
+        <v>16.346</v>
       </c>
       <c r="E67" t="n">
-        <v>15.0578</v>
+        <v>15.1038</v>
       </c>
       <c r="F67" t="n">
         <v>7.7456</v>
       </c>
       <c r="G67" t="n">
-        <v>12.269</v>
+        <v>12.545</v>
       </c>
       <c r="H67" t="n">
         <v>0.831</v>
       </c>
       <c r="I67" t="n">
-        <v>0.571</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="68">
@@ -2862,25 +2863,25 @@
         <v>22.6751</v>
       </c>
       <c r="C68" t="n">
-        <v>16.0886</v>
+        <v>15.8846</v>
       </c>
       <c r="D68" t="n">
-        <v>16.126</v>
+        <v>16.346</v>
       </c>
       <c r="E68" t="n">
-        <v>15.0578</v>
+        <v>15.1038</v>
       </c>
       <c r="F68" t="n">
         <v>7.7456</v>
       </c>
       <c r="G68" t="n">
-        <v>12.613</v>
+        <v>12.901</v>
       </c>
       <c r="H68" t="n">
         <v>0.831</v>
       </c>
       <c r="I68" t="n">
-        <v>0.571</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="69">
@@ -2891,25 +2892,25 @@
         <v>22.6751</v>
       </c>
       <c r="C69" t="n">
-        <v>16.0666</v>
+        <v>15.8626</v>
       </c>
       <c r="D69" t="n">
-        <v>16.126</v>
+        <v>16.346</v>
       </c>
       <c r="E69" t="n">
-        <v>15.0578</v>
+        <v>15.1038</v>
       </c>
       <c r="F69" t="n">
         <v>7.743600000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>12.964</v>
+        <v>13.252</v>
       </c>
       <c r="H69" t="n">
         <v>0.831</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5660000000000001</v>
+        <v>0.8360000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -2920,25 +2921,25 @@
         <v>22.6751</v>
       </c>
       <c r="C70" t="n">
-        <v>16.0666</v>
+        <v>15.8626</v>
       </c>
       <c r="D70" t="n">
-        <v>16.122</v>
+        <v>16.342</v>
       </c>
       <c r="E70" t="n">
-        <v>15.0028</v>
+        <v>15.0488</v>
       </c>
       <c r="F70" t="n">
         <v>7.743600000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>11.722</v>
+        <v>12.01</v>
       </c>
       <c r="H70" t="n">
         <v>0.831</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5660000000000001</v>
+        <v>0.8360000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -2949,7 +2950,7 @@
         <v>22.4911</v>
       </c>
       <c r="C71" t="n">
-        <v>15.7117</v>
+        <v>15.5077</v>
       </c>
       <c r="D71" t="n">
         <v>16.1477</v>
@@ -2967,7 +2968,7 @@
         <v>0.7059</v>
       </c>
       <c r="I71" t="n">
-        <v>0.5676</v>
+        <v>0.7716000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3050,28 +3051,28 @@
         <v>7683.6</v>
       </c>
       <c r="C2" t="n">
-        <v>14943.6</v>
+        <v>14752.3</v>
       </c>
       <c r="D2" t="n">
-        <v>9702</v>
+        <v>9848.4</v>
       </c>
       <c r="E2" t="n">
         <v>5904.8</v>
       </c>
       <c r="F2" t="n">
-        <v>24735.1</v>
+        <v>24934.1</v>
       </c>
       <c r="G2" t="n">
         <v>161</v>
       </c>
       <c r="H2" t="n">
-        <v>377</v>
+        <v>421.6</v>
       </c>
       <c r="I2" t="n">
-        <v>63507</v>
+        <v>63705.7</v>
       </c>
       <c r="J2" t="n">
-        <v>215</v>
+        <v>115</v>
       </c>
       <c r="K2" t="n">
         <v>579</v>
@@ -3085,28 +3086,28 @@
         <v>7683.6</v>
       </c>
       <c r="C3" t="n">
-        <v>14943.6</v>
+        <v>14752.3</v>
       </c>
       <c r="D3" t="n">
-        <v>9882</v>
+        <v>10028.4</v>
       </c>
       <c r="E3" t="n">
         <v>5955.8</v>
       </c>
       <c r="F3" t="n">
-        <v>24735.1</v>
+        <v>24934.1</v>
       </c>
       <c r="G3" t="n">
-        <v>161</v>
+        <v>245.3</v>
       </c>
       <c r="H3" t="n">
-        <v>377</v>
+        <v>421.6</v>
       </c>
       <c r="I3" t="n">
-        <v>63738</v>
+        <v>64021</v>
       </c>
       <c r="J3" t="n">
-        <v>215</v>
+        <v>115</v>
       </c>
       <c r="K3" t="n">
         <v>579</v>
@@ -3120,28 +3121,28 @@
         <v>7683.6</v>
       </c>
       <c r="C4" t="n">
-        <v>14943.6</v>
+        <v>14790.3</v>
       </c>
       <c r="D4" t="n">
-        <v>9890</v>
+        <v>10036.4</v>
       </c>
       <c r="E4" t="n">
         <v>6062.8</v>
       </c>
       <c r="F4" t="n">
-        <v>24735.1</v>
+        <v>24934.1</v>
       </c>
       <c r="G4" t="n">
-        <v>161</v>
+        <v>245.3</v>
       </c>
       <c r="H4" t="n">
-        <v>377</v>
+        <v>421.6</v>
       </c>
       <c r="I4" t="n">
-        <v>63853</v>
+        <v>64174</v>
       </c>
       <c r="J4" t="n">
-        <v>215</v>
+        <v>115</v>
       </c>
       <c r="K4" t="n">
         <v>579</v>
@@ -3155,28 +3156,28 @@
         <v>7683.6</v>
       </c>
       <c r="C5" t="n">
-        <v>14943.6</v>
+        <v>14829.6</v>
       </c>
       <c r="D5" t="n">
-        <v>9890</v>
+        <v>10036.4</v>
       </c>
       <c r="E5" t="n">
         <v>6242.8</v>
       </c>
       <c r="F5" t="n">
-        <v>24735.1</v>
+        <v>24934.1</v>
       </c>
       <c r="G5" t="n">
-        <v>131</v>
+        <v>297.3</v>
       </c>
       <c r="H5" t="n">
-        <v>377</v>
+        <v>421.6</v>
       </c>
       <c r="I5" t="n">
-        <v>64003</v>
+        <v>64445.3</v>
       </c>
       <c r="J5" t="n">
-        <v>215</v>
+        <v>115</v>
       </c>
       <c r="K5" t="n">
         <v>579</v>
@@ -3190,28 +3191,28 @@
         <v>7683.6</v>
       </c>
       <c r="C6" t="n">
-        <v>14943.6</v>
+        <v>14829.6</v>
       </c>
       <c r="D6" t="n">
-        <v>9974</v>
+        <v>10120.4</v>
       </c>
       <c r="E6" t="n">
         <v>6278.8</v>
       </c>
       <c r="F6" t="n">
-        <v>24735.1</v>
+        <v>24934.1</v>
       </c>
       <c r="G6" t="n">
-        <v>131</v>
+        <v>307.2</v>
       </c>
       <c r="H6" t="n">
-        <v>377</v>
+        <v>421.6</v>
       </c>
       <c r="I6" t="n">
-        <v>64123</v>
+        <v>64575.2</v>
       </c>
       <c r="J6" t="n">
-        <v>215</v>
+        <v>115</v>
       </c>
       <c r="K6" t="n">
         <v>579</v>
@@ -3225,28 +3226,28 @@
         <v>7683.6</v>
       </c>
       <c r="C7" t="n">
-        <v>14943.6</v>
+        <v>14829.6</v>
       </c>
       <c r="D7" t="n">
-        <v>10017</v>
+        <v>10163.4</v>
       </c>
       <c r="E7" t="n">
         <v>6512.8</v>
       </c>
       <c r="F7" t="n">
-        <v>24735.1</v>
+        <v>24934.1</v>
       </c>
       <c r="G7" t="n">
-        <v>131</v>
+        <v>307.2</v>
       </c>
       <c r="H7" t="n">
-        <v>377</v>
+        <v>421.6</v>
       </c>
       <c r="I7" t="n">
-        <v>64400</v>
+        <v>64852.2</v>
       </c>
       <c r="J7" t="n">
-        <v>217</v>
+        <v>117</v>
       </c>
       <c r="K7" t="n">
         <v>579</v>
@@ -3260,28 +3261,28 @@
         <v>7683.6</v>
       </c>
       <c r="C8" t="n">
-        <v>14943.6</v>
+        <v>14829.6</v>
       </c>
       <c r="D8" t="n">
-        <v>10570</v>
+        <v>10716.4</v>
       </c>
       <c r="E8" t="n">
         <v>6687.8</v>
       </c>
       <c r="F8" t="n">
-        <v>24735.1</v>
+        <v>24934.1</v>
       </c>
       <c r="G8" t="n">
-        <v>131</v>
+        <v>317.1</v>
       </c>
       <c r="H8" t="n">
-        <v>377</v>
+        <v>422.9</v>
       </c>
       <c r="I8" t="n">
-        <v>65128</v>
+        <v>65591.39999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>724</v>
+        <v>624</v>
       </c>
       <c r="K8" t="n">
         <v>579</v>
@@ -3295,28 +3296,28 @@
         <v>7683.6</v>
       </c>
       <c r="C9" t="n">
-        <v>14943.6</v>
+        <v>14829.6</v>
       </c>
       <c r="D9" t="n">
-        <v>10570</v>
+        <v>10716.4</v>
       </c>
       <c r="E9" t="n">
         <v>6703.8</v>
       </c>
       <c r="F9" t="n">
-        <v>24735.1</v>
+        <v>24934.1</v>
       </c>
       <c r="G9" t="n">
-        <v>131</v>
+        <v>317.1</v>
       </c>
       <c r="H9" t="n">
-        <v>377</v>
+        <v>422.9</v>
       </c>
       <c r="I9" t="n">
-        <v>65144</v>
+        <v>65607.39999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>724</v>
+        <v>624</v>
       </c>
       <c r="K9" t="n">
         <v>579</v>
@@ -3330,28 +3331,28 @@
         <v>7683.6</v>
       </c>
       <c r="C10" t="n">
-        <v>14823.6</v>
+        <v>14709.6</v>
       </c>
       <c r="D10" t="n">
-        <v>10578</v>
+        <v>10724.4</v>
       </c>
       <c r="E10" t="n">
         <v>6703.8</v>
       </c>
       <c r="F10" t="n">
-        <v>24735.1</v>
+        <v>24934.1</v>
       </c>
       <c r="G10" t="n">
-        <v>131</v>
+        <v>317.1</v>
       </c>
       <c r="H10" t="n">
-        <v>377</v>
+        <v>422.9</v>
       </c>
       <c r="I10" t="n">
-        <v>65032</v>
+        <v>65495.4</v>
       </c>
       <c r="J10" t="n">
-        <v>724</v>
+        <v>624</v>
       </c>
       <c r="K10" t="n">
         <v>579</v>
@@ -3365,28 +3366,28 @@
         <v>7683.6</v>
       </c>
       <c r="C11" t="n">
-        <v>14823.6</v>
+        <v>14709.6</v>
       </c>
       <c r="D11" t="n">
-        <v>10578</v>
+        <v>10724.4</v>
       </c>
       <c r="E11" t="n">
         <v>6813.8</v>
       </c>
       <c r="F11" t="n">
-        <v>24735.1</v>
+        <v>24934.1</v>
       </c>
       <c r="G11" t="n">
-        <v>131</v>
+        <v>317.1</v>
       </c>
       <c r="H11" t="n">
-        <v>377</v>
+        <v>422.9</v>
       </c>
       <c r="I11" t="n">
-        <v>65142</v>
+        <v>65605.39999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>774</v>
+        <v>674</v>
       </c>
       <c r="K11" t="n">
         <v>579</v>
@@ -3400,28 +3401,28 @@
         <v>7684.6</v>
       </c>
       <c r="C12" t="n">
-        <v>14822.6</v>
+        <v>14708.6</v>
       </c>
       <c r="D12" t="n">
-        <v>10578</v>
+        <v>10726</v>
       </c>
       <c r="E12" t="n">
         <v>7447.8</v>
       </c>
       <c r="F12" t="n">
-        <v>24735.1</v>
+        <v>24934.1</v>
       </c>
       <c r="G12" t="n">
-        <v>132</v>
+        <v>318.1</v>
       </c>
       <c r="H12" t="n">
-        <v>377</v>
+        <v>422.9</v>
       </c>
       <c r="I12" t="n">
-        <v>65777</v>
+        <v>66242</v>
       </c>
       <c r="J12" t="n">
-        <v>777</v>
+        <v>677</v>
       </c>
       <c r="K12" t="n">
         <v>579</v>
@@ -3435,28 +3436,28 @@
         <v>7684.6</v>
       </c>
       <c r="C13" t="n">
-        <v>14976.6</v>
+        <v>14772.6</v>
       </c>
       <c r="D13" t="n">
-        <v>10578</v>
+        <v>10726</v>
       </c>
       <c r="E13" t="n">
         <v>7447.8</v>
       </c>
       <c r="F13" t="n">
-        <v>24735.1</v>
+        <v>24934.1</v>
       </c>
       <c r="G13" t="n">
-        <v>160</v>
+        <v>346.1</v>
       </c>
       <c r="H13" t="n">
-        <v>377</v>
+        <v>422.9</v>
       </c>
       <c r="I13" t="n">
-        <v>65959</v>
+        <v>66334</v>
       </c>
       <c r="J13" t="n">
-        <v>777</v>
+        <v>677</v>
       </c>
       <c r="K13" t="n">
         <v>579</v>
@@ -3470,28 +3471,28 @@
         <v>7691.6</v>
       </c>
       <c r="C14" t="n">
-        <v>14976.6</v>
+        <v>14772.6</v>
       </c>
       <c r="D14" t="n">
-        <v>10578</v>
+        <v>10726</v>
       </c>
       <c r="E14" t="n">
         <v>7460.8</v>
       </c>
       <c r="F14" t="n">
-        <v>24735.1</v>
+        <v>24934.1</v>
       </c>
       <c r="G14" t="n">
-        <v>160</v>
+        <v>346.1</v>
       </c>
       <c r="H14" t="n">
-        <v>377</v>
+        <v>422.9</v>
       </c>
       <c r="I14" t="n">
-        <v>65979</v>
+        <v>66354</v>
       </c>
       <c r="J14" t="n">
-        <v>777</v>
+        <v>677</v>
       </c>
       <c r="K14" t="n">
         <v>579</v>
@@ -3505,28 +3506,28 @@
         <v>7691.6</v>
       </c>
       <c r="C15" t="n">
-        <v>14976.6</v>
+        <v>14772.6</v>
       </c>
       <c r="D15" t="n">
-        <v>10787</v>
+        <v>10935</v>
       </c>
       <c r="E15" t="n">
         <v>7643.8</v>
       </c>
       <c r="F15" t="n">
-        <v>24735.1</v>
+        <v>24934.1</v>
       </c>
       <c r="G15" t="n">
-        <v>160</v>
+        <v>346.1</v>
       </c>
       <c r="H15" t="n">
-        <v>377</v>
+        <v>422.9</v>
       </c>
       <c r="I15" t="n">
-        <v>66371</v>
+        <v>66746</v>
       </c>
       <c r="J15" t="n">
-        <v>777</v>
+        <v>677</v>
       </c>
       <c r="K15" t="n">
         <v>579</v>
@@ -3540,28 +3541,28 @@
         <v>7691.6</v>
       </c>
       <c r="C16" t="n">
-        <v>14976.6</v>
+        <v>14772.6</v>
       </c>
       <c r="D16" t="n">
-        <v>10997</v>
+        <v>11145</v>
       </c>
       <c r="E16" t="n">
         <v>7778.8</v>
       </c>
       <c r="F16" t="n">
-        <v>24735.1</v>
+        <v>24934.1</v>
       </c>
       <c r="G16" t="n">
-        <v>160</v>
+        <v>346.1</v>
       </c>
       <c r="H16" t="n">
-        <v>377</v>
+        <v>422.9</v>
       </c>
       <c r="I16" t="n">
-        <v>66716</v>
+        <v>67091</v>
       </c>
       <c r="J16" t="n">
-        <v>777</v>
+        <v>677</v>
       </c>
       <c r="K16" t="n">
         <v>579</v>
@@ -3575,28 +3576,28 @@
         <v>7691.6</v>
       </c>
       <c r="C17" t="n">
-        <v>14976.6</v>
+        <v>14772.6</v>
       </c>
       <c r="D17" t="n">
-        <v>10997</v>
+        <v>11145</v>
       </c>
       <c r="E17" t="n">
         <v>7805.8</v>
       </c>
       <c r="F17" t="n">
-        <v>24175.1</v>
+        <v>24374.1</v>
       </c>
       <c r="G17" t="n">
-        <v>160</v>
+        <v>346.1</v>
       </c>
       <c r="H17" t="n">
-        <v>377</v>
+        <v>422.9</v>
       </c>
       <c r="I17" t="n">
-        <v>66183</v>
+        <v>66558</v>
       </c>
       <c r="J17" t="n">
-        <v>782</v>
+        <v>682</v>
       </c>
       <c r="K17" t="n">
         <v>579</v>
@@ -3610,28 +3611,28 @@
         <v>7691.6</v>
       </c>
       <c r="C18" t="n">
-        <v>14976.6</v>
+        <v>14772.6</v>
       </c>
       <c r="D18" t="n">
-        <v>10997</v>
+        <v>11145</v>
       </c>
       <c r="E18" t="n">
         <v>8027.8</v>
       </c>
       <c r="F18" t="n">
-        <v>24175.1</v>
+        <v>24374.1</v>
       </c>
       <c r="G18" t="n">
-        <v>160</v>
+        <v>346.1</v>
       </c>
       <c r="H18" t="n">
-        <v>377</v>
+        <v>422.9</v>
       </c>
       <c r="I18" t="n">
-        <v>66405</v>
+        <v>66780</v>
       </c>
       <c r="J18" t="n">
-        <v>782</v>
+        <v>682</v>
       </c>
       <c r="K18" t="n">
         <v>579</v>
@@ -3645,28 +3646,28 @@
         <v>7691.6</v>
       </c>
       <c r="C19" t="n">
-        <v>14976.6</v>
+        <v>14772.6</v>
       </c>
       <c r="D19" t="n">
-        <v>11154</v>
+        <v>11302</v>
       </c>
       <c r="E19" t="n">
         <v>8244.799999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>24175.1</v>
+        <v>24374.1</v>
       </c>
       <c r="G19" t="n">
-        <v>160</v>
+        <v>346.1</v>
       </c>
       <c r="H19" t="n">
-        <v>377</v>
+        <v>422.9</v>
       </c>
       <c r="I19" t="n">
-        <v>66779</v>
+        <v>67154</v>
       </c>
       <c r="J19" t="n">
-        <v>782</v>
+        <v>682</v>
       </c>
       <c r="K19" t="n">
         <v>579</v>
@@ -3680,28 +3681,28 @@
         <v>7691.6</v>
       </c>
       <c r="C20" t="n">
-        <v>14976.6</v>
+        <v>14772.6</v>
       </c>
       <c r="D20" t="n">
-        <v>11154</v>
+        <v>11302</v>
       </c>
       <c r="E20" t="n">
         <v>8247.799999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>24175.1</v>
+        <v>24374.1</v>
       </c>
       <c r="G20" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H20" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I20" t="n">
-        <v>66788</v>
+        <v>67163</v>
       </c>
       <c r="J20" t="n">
-        <v>792</v>
+        <v>692</v>
       </c>
       <c r="K20" t="n">
         <v>579</v>
@@ -3715,28 +3716,28 @@
         <v>7691.6</v>
       </c>
       <c r="C21" t="n">
-        <v>14978.6</v>
+        <v>14774.6</v>
       </c>
       <c r="D21" t="n">
-        <v>11154</v>
+        <v>11302</v>
       </c>
       <c r="E21" t="n">
         <v>8247.799999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>24175.1</v>
+        <v>24374.1</v>
       </c>
       <c r="G21" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H21" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I21" t="n">
-        <v>66790</v>
+        <v>67165</v>
       </c>
       <c r="J21" t="n">
-        <v>792</v>
+        <v>692</v>
       </c>
       <c r="K21" t="n">
         <v>579</v>
@@ -3750,28 +3751,28 @@
         <v>7691.6</v>
       </c>
       <c r="C22" t="n">
-        <v>14858.6</v>
+        <v>14654.6</v>
       </c>
       <c r="D22" t="n">
-        <v>11310</v>
+        <v>11458</v>
       </c>
       <c r="E22" t="n">
         <v>8451.799999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>24175.1</v>
+        <v>24374.1</v>
       </c>
       <c r="G22" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H22" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I22" t="n">
-        <v>67030</v>
+        <v>67405</v>
       </c>
       <c r="J22" t="n">
-        <v>792</v>
+        <v>692</v>
       </c>
       <c r="K22" t="n">
         <v>579</v>
@@ -3785,10 +3786,10 @@
         <v>7691.6</v>
       </c>
       <c r="C23" t="n">
-        <v>14858.6</v>
+        <v>14654.6</v>
       </c>
       <c r="D23" t="n">
-        <v>11310</v>
+        <v>11458</v>
       </c>
       <c r="E23" t="n">
         <v>8550.799999999999</v>
@@ -3797,16 +3798,16 @@
         <v>24175.1</v>
       </c>
       <c r="G23" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H23" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I23" t="n">
-        <v>67129</v>
+        <v>67305</v>
       </c>
       <c r="J23" t="n">
-        <v>792</v>
+        <v>692</v>
       </c>
       <c r="K23" t="n">
         <v>579</v>
@@ -3820,10 +3821,10 @@
         <v>7691.6</v>
       </c>
       <c r="C24" t="n">
-        <v>14986.6</v>
+        <v>14782.6</v>
       </c>
       <c r="D24" t="n">
-        <v>11419</v>
+        <v>11567</v>
       </c>
       <c r="E24" t="n">
         <v>8550.799999999999</v>
@@ -3832,16 +3833,16 @@
         <v>24175.1</v>
       </c>
       <c r="G24" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H24" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I24" t="n">
-        <v>67366</v>
+        <v>67542</v>
       </c>
       <c r="J24" t="n">
-        <v>792</v>
+        <v>692</v>
       </c>
       <c r="K24" t="n">
         <v>579</v>
@@ -3855,10 +3856,10 @@
         <v>7691.6</v>
       </c>
       <c r="C25" t="n">
-        <v>14986.6</v>
+        <v>14782.6</v>
       </c>
       <c r="D25" t="n">
-        <v>11419</v>
+        <v>11567</v>
       </c>
       <c r="E25" t="n">
         <v>9200.799999999999</v>
@@ -3867,16 +3868,16 @@
         <v>24175.1</v>
       </c>
       <c r="G25" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H25" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I25" t="n">
-        <v>68016</v>
+        <v>68192</v>
       </c>
       <c r="J25" t="n">
-        <v>792</v>
+        <v>692</v>
       </c>
       <c r="K25" t="n">
         <v>579</v>
@@ -3890,10 +3891,10 @@
         <v>7691.6</v>
       </c>
       <c r="C26" t="n">
-        <v>14986.6</v>
+        <v>14782.6</v>
       </c>
       <c r="D26" t="n">
-        <v>11419</v>
+        <v>11567</v>
       </c>
       <c r="E26" t="n">
         <v>9200.799999999999</v>
@@ -3902,16 +3903,16 @@
         <v>24175.1</v>
       </c>
       <c r="G26" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H26" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I26" t="n">
-        <v>68016</v>
+        <v>68192</v>
       </c>
       <c r="J26" t="n">
-        <v>792</v>
+        <v>692</v>
       </c>
       <c r="K26" t="n">
         <v>579</v>
@@ -3925,10 +3926,10 @@
         <v>7691.6</v>
       </c>
       <c r="C27" t="n">
-        <v>14986.6</v>
+        <v>14782.6</v>
       </c>
       <c r="D27" t="n">
-        <v>11419</v>
+        <v>11567</v>
       </c>
       <c r="E27" t="n">
         <v>9305.799999999999</v>
@@ -3937,16 +3938,16 @@
         <v>24175.1</v>
       </c>
       <c r="G27" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H27" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I27" t="n">
-        <v>68121</v>
+        <v>68297</v>
       </c>
       <c r="J27" t="n">
-        <v>1042</v>
+        <v>942</v>
       </c>
       <c r="K27" t="n">
         <v>579</v>
@@ -3960,10 +3961,10 @@
         <v>7691.6</v>
       </c>
       <c r="C28" t="n">
-        <v>14986.6</v>
+        <v>14782.6</v>
       </c>
       <c r="D28" t="n">
-        <v>11419</v>
+        <v>11567</v>
       </c>
       <c r="E28" t="n">
         <v>9718.799999999999</v>
@@ -3972,16 +3973,16 @@
         <v>24175.1</v>
       </c>
       <c r="G28" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H28" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I28" t="n">
-        <v>68534</v>
+        <v>68710</v>
       </c>
       <c r="J28" t="n">
-        <v>1042</v>
+        <v>942</v>
       </c>
       <c r="K28" t="n">
         <v>579</v>
@@ -3995,10 +3996,10 @@
         <v>7691.6</v>
       </c>
       <c r="C29" t="n">
-        <v>14986.6</v>
+        <v>14782.6</v>
       </c>
       <c r="D29" t="n">
-        <v>11599</v>
+        <v>11747</v>
       </c>
       <c r="E29" t="n">
         <v>9718.799999999999</v>
@@ -4007,16 +4008,16 @@
         <v>24175.1</v>
       </c>
       <c r="G29" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H29" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I29" t="n">
-        <v>68714</v>
+        <v>68890</v>
       </c>
       <c r="J29" t="n">
-        <v>1299</v>
+        <v>1199</v>
       </c>
       <c r="K29" t="n">
         <v>579</v>
@@ -4030,10 +4031,10 @@
         <v>7691.6</v>
       </c>
       <c r="C30" t="n">
-        <v>14986.6</v>
+        <v>14782.6</v>
       </c>
       <c r="D30" t="n">
-        <v>11599</v>
+        <v>11747</v>
       </c>
       <c r="E30" t="n">
         <v>9718.799999999999</v>
@@ -4042,13 +4043,13 @@
         <v>22675.1</v>
       </c>
       <c r="G30" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H30" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I30" t="n">
-        <v>67214</v>
+        <v>67390</v>
       </c>
       <c r="J30" t="n">
         <v>1469</v>
@@ -4065,10 +4066,10 @@
         <v>7691.6</v>
       </c>
       <c r="C31" t="n">
-        <v>14986.6</v>
+        <v>14782.6</v>
       </c>
       <c r="D31" t="n">
-        <v>11599</v>
+        <v>11747</v>
       </c>
       <c r="E31" t="n">
         <v>9780.799999999999</v>
@@ -4077,13 +4078,13 @@
         <v>22675.1</v>
       </c>
       <c r="G31" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H31" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I31" t="n">
-        <v>67276</v>
+        <v>67452</v>
       </c>
       <c r="J31" t="n">
         <v>1469</v>
@@ -4100,10 +4101,10 @@
         <v>7691.6</v>
       </c>
       <c r="C32" t="n">
-        <v>14986.6</v>
+        <v>14782.6</v>
       </c>
       <c r="D32" t="n">
-        <v>11808</v>
+        <v>11956</v>
       </c>
       <c r="E32" t="n">
         <v>9780.799999999999</v>
@@ -4112,13 +4113,13 @@
         <v>22675.1</v>
       </c>
       <c r="G32" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H32" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I32" t="n">
-        <v>67485</v>
+        <v>67661</v>
       </c>
       <c r="J32" t="n">
         <v>1661</v>
@@ -4135,10 +4136,10 @@
         <v>7691.6</v>
       </c>
       <c r="C33" t="n">
-        <v>14986.6</v>
+        <v>14782.6</v>
       </c>
       <c r="D33" t="n">
-        <v>12349</v>
+        <v>12497</v>
       </c>
       <c r="E33" t="n">
         <v>9780.799999999999</v>
@@ -4147,13 +4148,13 @@
         <v>22675.1</v>
       </c>
       <c r="G33" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H33" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I33" t="n">
-        <v>68026</v>
+        <v>68202</v>
       </c>
       <c r="J33" t="n">
         <v>1661</v>
@@ -4170,10 +4171,10 @@
         <v>7691.6</v>
       </c>
       <c r="C34" t="n">
-        <v>14986.6</v>
+        <v>14782.6</v>
       </c>
       <c r="D34" t="n">
-        <v>12349</v>
+        <v>12497</v>
       </c>
       <c r="E34" t="n">
         <v>9780.799999999999</v>
@@ -4182,13 +4183,13 @@
         <v>22675.1</v>
       </c>
       <c r="G34" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H34" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I34" t="n">
-        <v>68026</v>
+        <v>68202</v>
       </c>
       <c r="J34" t="n">
         <v>1661</v>
@@ -4205,10 +4206,10 @@
         <v>7691.6</v>
       </c>
       <c r="C35" t="n">
-        <v>15360.6</v>
+        <v>15156.6</v>
       </c>
       <c r="D35" t="n">
-        <v>12349</v>
+        <v>12497</v>
       </c>
       <c r="E35" t="n">
         <v>9780.799999999999</v>
@@ -4217,13 +4218,13 @@
         <v>22675.1</v>
       </c>
       <c r="G35" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H35" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I35" t="n">
-        <v>68400</v>
+        <v>68576</v>
       </c>
       <c r="J35" t="n">
         <v>1661</v>
@@ -4240,10 +4241,10 @@
         <v>7691.6</v>
       </c>
       <c r="C36" t="n">
-        <v>15360.6</v>
+        <v>15156.6</v>
       </c>
       <c r="D36" t="n">
-        <v>12552</v>
+        <v>12772</v>
       </c>
       <c r="E36" t="n">
         <v>9906.799999999999</v>
@@ -4252,13 +4253,13 @@
         <v>22675.1</v>
       </c>
       <c r="G36" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H36" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I36" t="n">
-        <v>68729</v>
+        <v>68977</v>
       </c>
       <c r="J36" t="n">
         <v>1861</v>
@@ -4275,10 +4276,10 @@
         <v>7691.6</v>
       </c>
       <c r="C37" t="n">
-        <v>15360.6</v>
+        <v>15156.6</v>
       </c>
       <c r="D37" t="n">
-        <v>12552</v>
+        <v>12772</v>
       </c>
       <c r="E37" t="n">
         <v>9943.799999999999</v>
@@ -4287,13 +4288,13 @@
         <v>22675.1</v>
       </c>
       <c r="G37" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H37" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I37" t="n">
-        <v>68766</v>
+        <v>69014</v>
       </c>
       <c r="J37" t="n">
         <v>1861</v>
@@ -4310,10 +4311,10 @@
         <v>7691.6</v>
       </c>
       <c r="C38" t="n">
-        <v>15360.6</v>
+        <v>15156.6</v>
       </c>
       <c r="D38" t="n">
-        <v>12552</v>
+        <v>12772</v>
       </c>
       <c r="E38" t="n">
         <v>9943.799999999999</v>
@@ -4322,13 +4323,13 @@
         <v>22675.1</v>
       </c>
       <c r="G38" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H38" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I38" t="n">
-        <v>68766</v>
+        <v>69014</v>
       </c>
       <c r="J38" t="n">
         <v>1861</v>
@@ -4345,10 +4346,10 @@
         <v>7691.6</v>
       </c>
       <c r="C39" t="n">
-        <v>15360.6</v>
+        <v>15156.6</v>
       </c>
       <c r="D39" t="n">
-        <v>12552</v>
+        <v>12772</v>
       </c>
       <c r="E39" t="n">
         <v>9943.799999999999</v>
@@ -4357,13 +4358,13 @@
         <v>22675.1</v>
       </c>
       <c r="G39" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H39" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I39" t="n">
-        <v>68766</v>
+        <v>69014</v>
       </c>
       <c r="J39" t="n">
         <v>1861</v>
@@ -4380,10 +4381,10 @@
         <v>7691.6</v>
       </c>
       <c r="C40" t="n">
-        <v>15358.6</v>
+        <v>15154.6</v>
       </c>
       <c r="D40" t="n">
-        <v>12552</v>
+        <v>12772</v>
       </c>
       <c r="E40" t="n">
         <v>9943.799999999999</v>
@@ -4392,13 +4393,13 @@
         <v>22675.1</v>
       </c>
       <c r="G40" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H40" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I40" t="n">
-        <v>68764</v>
+        <v>69012</v>
       </c>
       <c r="J40" t="n">
         <v>1861</v>
@@ -4415,10 +4416,10 @@
         <v>7691.6</v>
       </c>
       <c r="C41" t="n">
-        <v>15358.6</v>
+        <v>15154.6</v>
       </c>
       <c r="D41" t="n">
-        <v>12552</v>
+        <v>12772</v>
       </c>
       <c r="E41" t="n">
         <v>9943.799999999999</v>
@@ -4427,13 +4428,13 @@
         <v>22675.1</v>
       </c>
       <c r="G41" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H41" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I41" t="n">
-        <v>68764</v>
+        <v>69012</v>
       </c>
       <c r="J41" t="n">
         <v>1861</v>
@@ -4450,10 +4451,10 @@
         <v>7691.6</v>
       </c>
       <c r="C42" t="n">
-        <v>15358.6</v>
+        <v>15154.6</v>
       </c>
       <c r="D42" t="n">
-        <v>12705</v>
+        <v>12925</v>
       </c>
       <c r="E42" t="n">
         <v>10379.8</v>
@@ -4462,13 +4463,13 @@
         <v>22675.1</v>
       </c>
       <c r="G42" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H42" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I42" t="n">
-        <v>69353</v>
+        <v>69601</v>
       </c>
       <c r="J42" t="n">
         <v>2133</v>
@@ -4485,10 +4486,10 @@
         <v>7691.6</v>
       </c>
       <c r="C43" t="n">
-        <v>15400.6</v>
+        <v>15196.6</v>
       </c>
       <c r="D43" t="n">
-        <v>12705</v>
+        <v>12925</v>
       </c>
       <c r="E43" t="n">
         <v>10379.8</v>
@@ -4497,13 +4498,13 @@
         <v>22675.1</v>
       </c>
       <c r="G43" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H43" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I43" t="n">
-        <v>69395</v>
+        <v>69643</v>
       </c>
       <c r="J43" t="n">
         <v>2133</v>
@@ -4520,10 +4521,10 @@
         <v>7691.6</v>
       </c>
       <c r="C44" t="n">
-        <v>15400.6</v>
+        <v>15196.6</v>
       </c>
       <c r="D44" t="n">
-        <v>12923</v>
+        <v>13143</v>
       </c>
       <c r="E44" t="n">
         <v>10472.8</v>
@@ -4532,13 +4533,13 @@
         <v>22675.1</v>
       </c>
       <c r="G44" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H44" t="n">
-        <v>378</v>
+        <v>423.9</v>
       </c>
       <c r="I44" t="n">
-        <v>69706</v>
+        <v>69954</v>
       </c>
       <c r="J44" t="n">
         <v>2283</v>
@@ -4555,28 +4556,28 @@
         <v>7691.6</v>
       </c>
       <c r="C45" t="n">
-        <v>15400.6</v>
+        <v>15196.6</v>
       </c>
       <c r="D45" t="n">
-        <v>14602</v>
+        <v>14822</v>
       </c>
       <c r="E45" t="n">
-        <v>10472.8</v>
+        <v>10518.8</v>
       </c>
       <c r="F45" t="n">
         <v>22675.1</v>
       </c>
       <c r="G45" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H45" t="n">
-        <v>410</v>
+        <v>455.9</v>
       </c>
       <c r="I45" t="n">
-        <v>71417</v>
+        <v>71711</v>
       </c>
       <c r="J45" t="n">
-        <v>2881</v>
+        <v>2925</v>
       </c>
       <c r="K45" t="n">
         <v>579</v>
@@ -4590,28 +4591,28 @@
         <v>7691.6</v>
       </c>
       <c r="C46" t="n">
-        <v>15400.6</v>
+        <v>15196.6</v>
       </c>
       <c r="D46" t="n">
-        <v>14752</v>
+        <v>14972</v>
       </c>
       <c r="E46" t="n">
-        <v>10921.8</v>
+        <v>10967.8</v>
       </c>
       <c r="F46" t="n">
         <v>22675.1</v>
       </c>
       <c r="G46" t="n">
-        <v>165</v>
+        <v>351.1</v>
       </c>
       <c r="H46" t="n">
-        <v>410</v>
+        <v>455.9</v>
       </c>
       <c r="I46" t="n">
-        <v>72016</v>
+        <v>72310</v>
       </c>
       <c r="J46" t="n">
-        <v>4370</v>
+        <v>4414</v>
       </c>
       <c r="K46" t="n">
         <v>579</v>
@@ -4625,28 +4626,28 @@
         <v>7691.6</v>
       </c>
       <c r="C47" t="n">
-        <v>15400.6</v>
+        <v>15196.6</v>
       </c>
       <c r="D47" t="n">
-        <v>14773</v>
+        <v>14993</v>
       </c>
       <c r="E47" t="n">
-        <v>10914.8</v>
+        <v>10960.8</v>
       </c>
       <c r="F47" t="n">
         <v>22675.1</v>
       </c>
       <c r="G47" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H47" t="n">
-        <v>410</v>
+        <v>455.9</v>
       </c>
       <c r="I47" t="n">
-        <v>72028</v>
+        <v>72322</v>
       </c>
       <c r="J47" t="n">
-        <v>3992</v>
+        <v>4089</v>
       </c>
       <c r="K47" t="n">
         <v>579</v>
@@ -4660,28 +4661,28 @@
         <v>7691.6</v>
       </c>
       <c r="C48" t="n">
-        <v>15400.6</v>
+        <v>15196.6</v>
       </c>
       <c r="D48" t="n">
-        <v>14773</v>
+        <v>14993</v>
       </c>
       <c r="E48" t="n">
-        <v>11065.8</v>
+        <v>11111.8</v>
       </c>
       <c r="F48" t="n">
         <v>22675.1</v>
       </c>
       <c r="G48" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H48" t="n">
-        <v>410</v>
+        <v>455.9</v>
       </c>
       <c r="I48" t="n">
-        <v>72179</v>
+        <v>72473</v>
       </c>
       <c r="J48" t="n">
-        <v>4100</v>
+        <v>4197</v>
       </c>
       <c r="K48" t="n">
         <v>579</v>
@@ -4695,28 +4696,28 @@
         <v>7691.6</v>
       </c>
       <c r="C49" t="n">
-        <v>15400.6</v>
+        <v>15196.6</v>
       </c>
       <c r="D49" t="n">
-        <v>14769</v>
+        <v>14989</v>
       </c>
       <c r="E49" t="n">
-        <v>11929.8</v>
+        <v>11975.8</v>
       </c>
       <c r="F49" t="n">
         <v>22675.1</v>
       </c>
       <c r="G49" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H49" t="n">
-        <v>410</v>
+        <v>455.9</v>
       </c>
       <c r="I49" t="n">
-        <v>73039</v>
+        <v>73333</v>
       </c>
       <c r="J49" t="n">
-        <v>4037</v>
+        <v>4134</v>
       </c>
       <c r="K49" t="n">
         <v>579</v>
@@ -4730,28 +4731,28 @@
         <v>7691.6</v>
       </c>
       <c r="C50" t="n">
-        <v>15400.6</v>
+        <v>15196.6</v>
       </c>
       <c r="D50" t="n">
-        <v>14944</v>
+        <v>15164</v>
       </c>
       <c r="E50" t="n">
-        <v>11929.8</v>
+        <v>11975.8</v>
       </c>
       <c r="F50" t="n">
         <v>22675.1</v>
       </c>
       <c r="G50" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H50" t="n">
-        <v>410</v>
+        <v>455.9</v>
       </c>
       <c r="I50" t="n">
-        <v>73214</v>
+        <v>73508</v>
       </c>
       <c r="J50" t="n">
-        <v>4222</v>
+        <v>4319</v>
       </c>
       <c r="K50" t="n">
         <v>579</v>
@@ -4765,28 +4766,28 @@
         <v>7691.6</v>
       </c>
       <c r="C51" t="n">
-        <v>15338.6</v>
+        <v>15134.6</v>
       </c>
       <c r="D51" t="n">
-        <v>14944</v>
+        <v>15164</v>
       </c>
       <c r="E51" t="n">
-        <v>11929.8</v>
+        <v>11975.8</v>
       </c>
       <c r="F51" t="n">
         <v>22675.1</v>
       </c>
       <c r="G51" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H51" t="n">
-        <v>410</v>
+        <v>455.9</v>
       </c>
       <c r="I51" t="n">
-        <v>73152</v>
+        <v>73446</v>
       </c>
       <c r="J51" t="n">
-        <v>4222</v>
+        <v>4319</v>
       </c>
       <c r="K51" t="n">
         <v>579</v>
@@ -4800,28 +4801,28 @@
         <v>7691.6</v>
       </c>
       <c r="C52" t="n">
-        <v>16088.6</v>
+        <v>15884.6</v>
       </c>
       <c r="D52" t="n">
-        <v>14944</v>
+        <v>15164</v>
       </c>
       <c r="E52" t="n">
-        <v>12464.8</v>
+        <v>12510.8</v>
       </c>
       <c r="F52" t="n">
         <v>22675.1</v>
       </c>
       <c r="G52" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H52" t="n">
-        <v>410</v>
+        <v>455.9</v>
       </c>
       <c r="I52" t="n">
-        <v>74437</v>
+        <v>74731</v>
       </c>
       <c r="J52" t="n">
-        <v>5229</v>
+        <v>5326</v>
       </c>
       <c r="K52" t="n">
         <v>579</v>
@@ -4835,28 +4836,28 @@
         <v>7691.6</v>
       </c>
       <c r="C53" t="n">
-        <v>16088.6</v>
+        <v>15884.6</v>
       </c>
       <c r="D53" t="n">
-        <v>15047</v>
+        <v>15267</v>
       </c>
       <c r="E53" t="n">
-        <v>12464.8</v>
+        <v>12510.8</v>
       </c>
       <c r="F53" t="n">
         <v>22675.1</v>
       </c>
       <c r="G53" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H53" t="n">
-        <v>410</v>
+        <v>493.9</v>
       </c>
       <c r="I53" t="n">
-        <v>74540</v>
+        <v>74872</v>
       </c>
       <c r="J53" t="n">
-        <v>5369</v>
+        <v>5527</v>
       </c>
       <c r="K53" t="n">
         <v>579</v>
@@ -4870,28 +4871,28 @@
         <v>7691.6</v>
       </c>
       <c r="C54" t="n">
-        <v>16088.6</v>
+        <v>15884.6</v>
       </c>
       <c r="D54" t="n">
-        <v>15047</v>
+        <v>15267</v>
       </c>
       <c r="E54" t="n">
-        <v>12464.8</v>
+        <v>12510.8</v>
       </c>
       <c r="F54" t="n">
         <v>22675.1</v>
       </c>
       <c r="G54" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H54" t="n">
-        <v>410</v>
+        <v>493.9</v>
       </c>
       <c r="I54" t="n">
-        <v>74540</v>
+        <v>74872</v>
       </c>
       <c r="J54" t="n">
-        <v>5638</v>
+        <v>5796</v>
       </c>
       <c r="K54" t="n">
         <v>579</v>
@@ -4905,28 +4906,28 @@
         <v>7691.6</v>
       </c>
       <c r="C55" t="n">
-        <v>16088.6</v>
+        <v>15884.6</v>
       </c>
       <c r="D55" t="n">
-        <v>15299</v>
+        <v>15519</v>
       </c>
       <c r="E55" t="n">
-        <v>12956.8</v>
+        <v>13002.8</v>
       </c>
       <c r="F55" t="n">
         <v>22675.1</v>
       </c>
       <c r="G55" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H55" t="n">
-        <v>410</v>
+        <v>493.9</v>
       </c>
       <c r="I55" t="n">
-        <v>75284</v>
+        <v>75616</v>
       </c>
       <c r="J55" t="n">
-        <v>6265</v>
+        <v>6423</v>
       </c>
       <c r="K55" t="n">
         <v>579</v>
@@ -4940,28 +4941,28 @@
         <v>7691.6</v>
       </c>
       <c r="C56" t="n">
-        <v>16088.6</v>
+        <v>15884.6</v>
       </c>
       <c r="D56" t="n">
-        <v>15299</v>
+        <v>15519</v>
       </c>
       <c r="E56" t="n">
-        <v>12956.8</v>
+        <v>13002.8</v>
       </c>
       <c r="F56" t="n">
         <v>22675.1</v>
       </c>
       <c r="G56" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H56" t="n">
-        <v>410</v>
+        <v>493.9</v>
       </c>
       <c r="I56" t="n">
-        <v>75284</v>
+        <v>75616</v>
       </c>
       <c r="J56" t="n">
-        <v>6480</v>
+        <v>6638</v>
       </c>
       <c r="K56" t="n">
         <v>579</v>
@@ -4975,28 +4976,28 @@
         <v>7691.6</v>
       </c>
       <c r="C57" t="n">
-        <v>16088.6</v>
+        <v>15884.6</v>
       </c>
       <c r="D57" t="n">
-        <v>15299</v>
+        <v>15519</v>
       </c>
       <c r="E57" t="n">
-        <v>12956.8</v>
+        <v>13002.8</v>
       </c>
       <c r="F57" t="n">
         <v>22675.1</v>
       </c>
       <c r="G57" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H57" t="n">
-        <v>410</v>
+        <v>493.9</v>
       </c>
       <c r="I57" t="n">
-        <v>75284</v>
+        <v>75616</v>
       </c>
       <c r="J57" t="n">
-        <v>6549</v>
+        <v>6707</v>
       </c>
       <c r="K57" t="n">
         <v>579</v>
@@ -5010,28 +5011,28 @@
         <v>7696.6</v>
       </c>
       <c r="C58" t="n">
-        <v>16088.6</v>
+        <v>15884.6</v>
       </c>
       <c r="D58" t="n">
-        <v>15293</v>
+        <v>15513</v>
       </c>
       <c r="E58" t="n">
-        <v>13458.8</v>
+        <v>13504.8</v>
       </c>
       <c r="F58" t="n">
         <v>22675.1</v>
       </c>
       <c r="G58" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H58" t="n">
-        <v>410</v>
+        <v>493.9</v>
       </c>
       <c r="I58" t="n">
-        <v>75785</v>
+        <v>76117</v>
       </c>
       <c r="J58" t="n">
-        <v>8266</v>
+        <v>8424</v>
       </c>
       <c r="K58" t="n">
         <v>579</v>
@@ -5045,28 +5046,28 @@
         <v>7696.6</v>
       </c>
       <c r="C59" t="n">
-        <v>16088.6</v>
+        <v>15884.6</v>
       </c>
       <c r="D59" t="n">
-        <v>15296</v>
+        <v>15516</v>
       </c>
       <c r="E59" t="n">
-        <v>13458.8</v>
+        <v>13504.8</v>
       </c>
       <c r="F59" t="n">
         <v>22675.1</v>
       </c>
       <c r="G59" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H59" t="n">
-        <v>410</v>
+        <v>493.9</v>
       </c>
       <c r="I59" t="n">
-        <v>75788</v>
+        <v>76120</v>
       </c>
       <c r="J59" t="n">
-        <v>8824</v>
+        <v>9035</v>
       </c>
       <c r="K59" t="n">
         <v>579</v>
@@ -5080,28 +5081,28 @@
         <v>7696.6</v>
       </c>
       <c r="C60" t="n">
-        <v>16088.6</v>
+        <v>15884.6</v>
       </c>
       <c r="D60" t="n">
-        <v>15296</v>
+        <v>15516</v>
       </c>
       <c r="E60" t="n">
-        <v>14030.8</v>
+        <v>14076.8</v>
       </c>
       <c r="F60" t="n">
         <v>22675.1</v>
       </c>
       <c r="G60" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H60" t="n">
-        <v>408</v>
+        <v>491.9</v>
       </c>
       <c r="I60" t="n">
-        <v>76358</v>
+        <v>76690</v>
       </c>
       <c r="J60" t="n">
-        <v>8824</v>
+        <v>9100</v>
       </c>
       <c r="K60" t="n">
         <v>831</v>
@@ -5115,28 +5116,28 @@
         <v>7696.6</v>
       </c>
       <c r="C61" t="n">
-        <v>16088.6</v>
+        <v>15884.6</v>
       </c>
       <c r="D61" t="n">
-        <v>15296</v>
+        <v>15516</v>
       </c>
       <c r="E61" t="n">
-        <v>14398.8</v>
+        <v>14444.8</v>
       </c>
       <c r="F61" t="n">
         <v>22675.1</v>
       </c>
       <c r="G61" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H61" t="n">
-        <v>408</v>
+        <v>491.9</v>
       </c>
       <c r="I61" t="n">
-        <v>76726</v>
+        <v>77058</v>
       </c>
       <c r="J61" t="n">
-        <v>9355</v>
+        <v>9631</v>
       </c>
       <c r="K61" t="n">
         <v>831</v>
@@ -5150,28 +5151,28 @@
         <v>7696.6</v>
       </c>
       <c r="C62" t="n">
-        <v>16088.6</v>
+        <v>15884.6</v>
       </c>
       <c r="D62" t="n">
-        <v>15872</v>
+        <v>16092</v>
       </c>
       <c r="E62" t="n">
-        <v>14521.8</v>
+        <v>14567.8</v>
       </c>
       <c r="F62" t="n">
         <v>22675.1</v>
       </c>
       <c r="G62" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H62" t="n">
-        <v>408</v>
+        <v>491.9</v>
       </c>
       <c r="I62" t="n">
-        <v>77425</v>
+        <v>77757</v>
       </c>
       <c r="J62" t="n">
-        <v>9355</v>
+        <v>9631</v>
       </c>
       <c r="K62" t="n">
         <v>831</v>
@@ -5185,28 +5186,28 @@
         <v>7696.6</v>
       </c>
       <c r="C63" t="n">
-        <v>16088.6</v>
+        <v>15884.6</v>
       </c>
       <c r="D63" t="n">
-        <v>15872</v>
+        <v>16092</v>
       </c>
       <c r="E63" t="n">
-        <v>14716.8</v>
+        <v>14762.8</v>
       </c>
       <c r="F63" t="n">
         <v>22675.1</v>
       </c>
       <c r="G63" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H63" t="n">
-        <v>408</v>
+        <v>491.9</v>
       </c>
       <c r="I63" t="n">
-        <v>77620</v>
+        <v>77952</v>
       </c>
       <c r="J63" t="n">
-        <v>10088</v>
+        <v>10364</v>
       </c>
       <c r="K63" t="n">
         <v>831</v>
@@ -5220,28 +5221,28 @@
         <v>7696.6</v>
       </c>
       <c r="C64" t="n">
-        <v>16088.6</v>
+        <v>15884.6</v>
       </c>
       <c r="D64" t="n">
-        <v>15872</v>
+        <v>16092</v>
       </c>
       <c r="E64" t="n">
-        <v>14716.8</v>
+        <v>14762.8</v>
       </c>
       <c r="F64" t="n">
         <v>22675.1</v>
       </c>
       <c r="G64" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H64" t="n">
-        <v>408</v>
+        <v>491.9</v>
       </c>
       <c r="I64" t="n">
-        <v>77620</v>
+        <v>77952</v>
       </c>
       <c r="J64" t="n">
-        <v>11104</v>
+        <v>11380</v>
       </c>
       <c r="K64" t="n">
         <v>831</v>
@@ -5255,28 +5256,28 @@
         <v>7696.6</v>
       </c>
       <c r="C65" t="n">
-        <v>16088.6</v>
+        <v>15884.6</v>
       </c>
       <c r="D65" t="n">
-        <v>16126</v>
+        <v>16346</v>
       </c>
       <c r="E65" t="n">
-        <v>14747.8</v>
+        <v>14793.8</v>
       </c>
       <c r="F65" t="n">
         <v>22675.1</v>
       </c>
       <c r="G65" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H65" t="n">
-        <v>408</v>
+        <v>491.9</v>
       </c>
       <c r="I65" t="n">
-        <v>77905</v>
+        <v>78237</v>
       </c>
       <c r="J65" t="n">
-        <v>11104</v>
+        <v>11380</v>
       </c>
       <c r="K65" t="n">
         <v>831</v>
@@ -5290,28 +5291,28 @@
         <v>7696.6</v>
       </c>
       <c r="C66" t="n">
-        <v>16088.6</v>
+        <v>15884.6</v>
       </c>
       <c r="D66" t="n">
-        <v>16126</v>
+        <v>16346</v>
       </c>
       <c r="E66" t="n">
-        <v>14747.8</v>
+        <v>14793.8</v>
       </c>
       <c r="F66" t="n">
         <v>22675.1</v>
       </c>
       <c r="G66" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H66" t="n">
-        <v>408</v>
+        <v>491.9</v>
       </c>
       <c r="I66" t="n">
-        <v>77905</v>
+        <v>78237</v>
       </c>
       <c r="J66" t="n">
-        <v>11384</v>
+        <v>11660</v>
       </c>
       <c r="K66" t="n">
         <v>831</v>
@@ -5325,28 +5326,28 @@
         <v>7745.6</v>
       </c>
       <c r="C67" t="n">
-        <v>16088.6</v>
+        <v>15884.6</v>
       </c>
       <c r="D67" t="n">
-        <v>16126</v>
+        <v>16346</v>
       </c>
       <c r="E67" t="n">
-        <v>15057.8</v>
+        <v>15103.8</v>
       </c>
       <c r="F67" t="n">
         <v>22675.1</v>
       </c>
       <c r="G67" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H67" t="n">
-        <v>408</v>
+        <v>491.9</v>
       </c>
       <c r="I67" t="n">
-        <v>78264</v>
+        <v>78596</v>
       </c>
       <c r="J67" t="n">
-        <v>12269</v>
+        <v>12545</v>
       </c>
       <c r="K67" t="n">
         <v>831</v>
@@ -5360,28 +5361,28 @@
         <v>7745.6</v>
       </c>
       <c r="C68" t="n">
-        <v>16088.6</v>
+        <v>15884.6</v>
       </c>
       <c r="D68" t="n">
-        <v>16126</v>
+        <v>16346</v>
       </c>
       <c r="E68" t="n">
-        <v>15057.8</v>
+        <v>15103.8</v>
       </c>
       <c r="F68" t="n">
         <v>22675.1</v>
       </c>
       <c r="G68" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H68" t="n">
-        <v>408</v>
+        <v>491.9</v>
       </c>
       <c r="I68" t="n">
-        <v>78264</v>
+        <v>78596</v>
       </c>
       <c r="J68" t="n">
-        <v>12613</v>
+        <v>12901</v>
       </c>
       <c r="K68" t="n">
         <v>831</v>
@@ -5395,28 +5396,28 @@
         <v>7743.6</v>
       </c>
       <c r="C69" t="n">
-        <v>16066.6</v>
+        <v>15862.6</v>
       </c>
       <c r="D69" t="n">
-        <v>16126</v>
+        <v>16346</v>
       </c>
       <c r="E69" t="n">
-        <v>15057.8</v>
+        <v>15103.8</v>
       </c>
       <c r="F69" t="n">
         <v>22675.1</v>
       </c>
       <c r="G69" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H69" t="n">
-        <v>403</v>
+        <v>486.9</v>
       </c>
       <c r="I69" t="n">
-        <v>78235</v>
+        <v>78567</v>
       </c>
       <c r="J69" t="n">
-        <v>12964</v>
+        <v>13252</v>
       </c>
       <c r="K69" t="n">
         <v>831</v>
@@ -5430,28 +5431,28 @@
         <v>7743.6</v>
       </c>
       <c r="C70" t="n">
-        <v>16066.6</v>
+        <v>15862.6</v>
       </c>
       <c r="D70" t="n">
-        <v>16122</v>
+        <v>16342</v>
       </c>
       <c r="E70" t="n">
-        <v>15002.8</v>
+        <v>15048.8</v>
       </c>
       <c r="F70" t="n">
         <v>22675.1</v>
       </c>
       <c r="G70" t="n">
-        <v>163</v>
+        <v>349.1</v>
       </c>
       <c r="H70" t="n">
-        <v>403</v>
+        <v>486.9</v>
       </c>
       <c r="I70" t="n">
-        <v>78176</v>
+        <v>78508</v>
       </c>
       <c r="J70" t="n">
-        <v>11722</v>
+        <v>12010</v>
       </c>
       <c r="K70" t="n">
         <v>831</v>
@@ -5465,7 +5466,7 @@
         <v>7389.9</v>
       </c>
       <c r="C71" t="n">
-        <v>15711.7</v>
+        <v>15507.7</v>
       </c>
       <c r="D71" t="n">
         <v>16147.7</v>
@@ -5477,10 +5478,10 @@
         <v>22491.1</v>
       </c>
       <c r="G71" t="n">
-        <v>160.5</v>
+        <v>346.6</v>
       </c>
       <c r="H71" t="n">
-        <v>407.1</v>
+        <v>425</v>
       </c>
       <c r="I71" t="n">
         <v>77380.10000000001</v>
@@ -5551,7 +5552,7 @@
         <v>19976</v>
       </c>
       <c r="C2" t="n">
-        <v>14917</v>
+        <v>14985</v>
       </c>
       <c r="D2" t="n">
         <v>5850</v>
@@ -5560,10 +5561,10 @@
         <v>3362</v>
       </c>
       <c r="F2" t="n">
-        <v>13549.6</v>
+        <v>13697.6</v>
       </c>
       <c r="G2" t="n">
-        <v>5852.5</v>
+        <v>5835.2</v>
       </c>
     </row>
     <row r="3">
@@ -5574,7 +5575,7 @@
         <v>20012</v>
       </c>
       <c r="C3" t="n">
-        <v>14917</v>
+        <v>14985</v>
       </c>
       <c r="D3" t="n">
         <v>5865</v>
@@ -5583,10 +5584,10 @@
         <v>3362</v>
       </c>
       <c r="F3" t="n">
-        <v>13729.6</v>
+        <v>13877.6</v>
       </c>
       <c r="G3" t="n">
-        <v>5852.5</v>
+        <v>5919.5</v>
       </c>
     </row>
     <row r="4">
@@ -5597,7 +5598,7 @@
         <v>20012</v>
       </c>
       <c r="C4" t="n">
-        <v>14917</v>
+        <v>14985</v>
       </c>
       <c r="D4" t="n">
         <v>5865</v>
@@ -5606,10 +5607,10 @@
         <v>3362</v>
       </c>
       <c r="F4" t="n">
-        <v>13844.6</v>
+        <v>13992.6</v>
       </c>
       <c r="G4" t="n">
-        <v>5852.5</v>
+        <v>5957.5</v>
       </c>
     </row>
     <row r="5">
@@ -5620,7 +5621,7 @@
         <v>20012</v>
       </c>
       <c r="C5" t="n">
-        <v>15049</v>
+        <v>15117</v>
       </c>
       <c r="D5" t="n">
         <v>5883</v>
@@ -5629,10 +5630,10 @@
         <v>3362</v>
       </c>
       <c r="F5" t="n">
-        <v>13844.6</v>
+        <v>13992.6</v>
       </c>
       <c r="G5" t="n">
-        <v>5852.5</v>
+        <v>6078.8</v>
       </c>
     </row>
     <row r="6">
@@ -5643,7 +5644,7 @@
         <v>20132</v>
       </c>
       <c r="C6" t="n">
-        <v>15049</v>
+        <v>15117</v>
       </c>
       <c r="D6" t="n">
         <v>5883</v>
@@ -5652,10 +5653,10 @@
         <v>3362</v>
       </c>
       <c r="F6" t="n">
-        <v>13844.6</v>
+        <v>13992.6</v>
       </c>
       <c r="G6" t="n">
-        <v>5852.5</v>
+        <v>6088.7</v>
       </c>
     </row>
     <row r="7">
@@ -5666,7 +5667,7 @@
         <v>20331</v>
       </c>
       <c r="C7" t="n">
-        <v>15127</v>
+        <v>15195</v>
       </c>
       <c r="D7" t="n">
         <v>5883</v>
@@ -5675,10 +5676,10 @@
         <v>3362</v>
       </c>
       <c r="F7" t="n">
-        <v>13844.6</v>
+        <v>13992.6</v>
       </c>
       <c r="G7" t="n">
-        <v>5852.5</v>
+        <v>6088.7</v>
       </c>
     </row>
     <row r="8">
@@ -5689,7 +5690,7 @@
         <v>20506</v>
       </c>
       <c r="C8" t="n">
-        <v>15127</v>
+        <v>15195</v>
       </c>
       <c r="D8" t="n">
         <v>5883</v>
@@ -5698,10 +5699,10 @@
         <v>3362</v>
       </c>
       <c r="F8" t="n">
-        <v>14397.6</v>
+        <v>14545.6</v>
       </c>
       <c r="G8" t="n">
-        <v>5852.5</v>
+        <v>6099.9</v>
       </c>
     </row>
     <row r="9">
@@ -5712,7 +5713,7 @@
         <v>20506</v>
       </c>
       <c r="C9" t="n">
-        <v>15127</v>
+        <v>15195</v>
       </c>
       <c r="D9" t="n">
         <v>5899</v>
@@ -5721,10 +5722,10 @@
         <v>3362</v>
       </c>
       <c r="F9" t="n">
-        <v>14397.6</v>
+        <v>14545.6</v>
       </c>
       <c r="G9" t="n">
-        <v>5852.5</v>
+        <v>6099.9</v>
       </c>
     </row>
     <row r="10">
@@ -5735,7 +5736,7 @@
         <v>20506</v>
       </c>
       <c r="C10" t="n">
-        <v>15127</v>
+        <v>15195</v>
       </c>
       <c r="D10" t="n">
         <v>5779</v>
@@ -5744,10 +5745,10 @@
         <v>3362</v>
       </c>
       <c r="F10" t="n">
-        <v>14405.6</v>
+        <v>14553.6</v>
       </c>
       <c r="G10" t="n">
-        <v>5852.5</v>
+        <v>6099.9</v>
       </c>
     </row>
     <row r="11">
@@ -5758,7 +5759,7 @@
         <v>20616</v>
       </c>
       <c r="C11" t="n">
-        <v>15127</v>
+        <v>15195</v>
       </c>
       <c r="D11" t="n">
         <v>5779</v>
@@ -5767,10 +5768,10 @@
         <v>3362</v>
       </c>
       <c r="F11" t="n">
-        <v>14405.6</v>
+        <v>14553.6</v>
       </c>
       <c r="G11" t="n">
-        <v>5852.5</v>
+        <v>6099.9</v>
       </c>
     </row>
     <row r="12">
@@ -5781,7 +5782,7 @@
         <v>20726</v>
       </c>
       <c r="C12" t="n">
-        <v>15627</v>
+        <v>15695</v>
       </c>
       <c r="D12" t="n">
         <v>5804</v>
@@ -5790,10 +5791,10 @@
         <v>3362</v>
       </c>
       <c r="F12" t="n">
-        <v>14405.6</v>
+        <v>14553.6</v>
       </c>
       <c r="G12" t="n">
-        <v>5852.5</v>
+        <v>6101.5</v>
       </c>
     </row>
     <row r="13">
@@ -5804,7 +5805,7 @@
         <v>20754</v>
       </c>
       <c r="C13" t="n">
-        <v>15627</v>
+        <v>15695</v>
       </c>
       <c r="D13" t="n">
         <v>5958</v>
@@ -5813,10 +5814,10 @@
         <v>3362</v>
       </c>
       <c r="F13" t="n">
-        <v>14405.6</v>
+        <v>14553.6</v>
       </c>
       <c r="G13" t="n">
-        <v>5852.5</v>
+        <v>6011.5</v>
       </c>
     </row>
     <row r="14">
@@ -5827,7 +5828,7 @@
         <v>20761</v>
       </c>
       <c r="C14" t="n">
-        <v>15627</v>
+        <v>15695</v>
       </c>
       <c r="D14" t="n">
         <v>5971</v>
@@ -5836,10 +5837,10 @@
         <v>3362</v>
       </c>
       <c r="F14" t="n">
-        <v>14405.6</v>
+        <v>14553.6</v>
       </c>
       <c r="G14" t="n">
-        <v>5852.5</v>
+        <v>6011.5</v>
       </c>
     </row>
     <row r="15">
@@ -5850,7 +5851,7 @@
         <v>20761</v>
       </c>
       <c r="C15" t="n">
-        <v>15810</v>
+        <v>15878</v>
       </c>
       <c r="D15" t="n">
         <v>5971</v>
@@ -5859,10 +5860,10 @@
         <v>3362</v>
       </c>
       <c r="F15" t="n">
-        <v>14614.6</v>
+        <v>14762.6</v>
       </c>
       <c r="G15" t="n">
-        <v>5852.5</v>
+        <v>6011.5</v>
       </c>
     </row>
     <row r="16">
@@ -5873,7 +5874,7 @@
         <v>20896</v>
       </c>
       <c r="C16" t="n">
-        <v>15810</v>
+        <v>15878</v>
       </c>
       <c r="D16" t="n">
         <v>6181</v>
@@ -5882,10 +5883,10 @@
         <v>3362</v>
       </c>
       <c r="F16" t="n">
-        <v>14614.6</v>
+        <v>14762.6</v>
       </c>
       <c r="G16" t="n">
-        <v>5852.5</v>
+        <v>6011.5</v>
       </c>
     </row>
     <row r="17">
@@ -5896,7 +5897,7 @@
         <v>20396</v>
       </c>
       <c r="C17" t="n">
-        <v>15750</v>
+        <v>15818</v>
       </c>
       <c r="D17" t="n">
         <v>6208</v>
@@ -5905,10 +5906,10 @@
         <v>3362</v>
       </c>
       <c r="F17" t="n">
-        <v>14614.6</v>
+        <v>14762.6</v>
       </c>
       <c r="G17" t="n">
-        <v>5852.5</v>
+        <v>6011.5</v>
       </c>
     </row>
     <row r="18">
@@ -5919,7 +5920,7 @@
         <v>20396</v>
       </c>
       <c r="C18" t="n">
-        <v>15972</v>
+        <v>16040</v>
       </c>
       <c r="D18" t="n">
         <v>6208</v>
@@ -5928,10 +5929,10 @@
         <v>3362</v>
       </c>
       <c r="F18" t="n">
-        <v>14614.6</v>
+        <v>14762.6</v>
       </c>
       <c r="G18" t="n">
-        <v>5852.5</v>
+        <v>6011.5</v>
       </c>
     </row>
     <row r="19">
@@ -5942,7 +5943,7 @@
         <v>20396</v>
       </c>
       <c r="C19" t="n">
-        <v>16189</v>
+        <v>16257</v>
       </c>
       <c r="D19" t="n">
         <v>6208</v>
@@ -5951,10 +5952,10 @@
         <v>3362</v>
       </c>
       <c r="F19" t="n">
-        <v>14771.6</v>
+        <v>14919.6</v>
       </c>
       <c r="G19" t="n">
-        <v>5852.5</v>
+        <v>6011.5</v>
       </c>
     </row>
     <row r="20">
@@ -5965,7 +5966,7 @@
         <v>20396</v>
       </c>
       <c r="C20" t="n">
-        <v>16189</v>
+        <v>16257</v>
       </c>
       <c r="D20" t="n">
         <v>6217</v>
@@ -5974,10 +5975,10 @@
         <v>3362</v>
       </c>
       <c r="F20" t="n">
-        <v>14771.6</v>
+        <v>14919.6</v>
       </c>
       <c r="G20" t="n">
-        <v>5852.5</v>
+        <v>6011.5</v>
       </c>
     </row>
     <row r="21">
@@ -5988,7 +5989,7 @@
         <v>20398</v>
       </c>
       <c r="C21" t="n">
-        <v>16189</v>
+        <v>16257</v>
       </c>
       <c r="D21" t="n">
         <v>6217</v>
@@ -5997,10 +5998,10 @@
         <v>3362</v>
       </c>
       <c r="F21" t="n">
-        <v>14771.6</v>
+        <v>14919.6</v>
       </c>
       <c r="G21" t="n">
-        <v>5852.5</v>
+        <v>6011.5</v>
       </c>
     </row>
     <row r="22">
@@ -6011,7 +6012,7 @@
         <v>20503</v>
       </c>
       <c r="C22" t="n">
-        <v>16345</v>
+        <v>16413</v>
       </c>
       <c r="D22" t="n">
         <v>6196</v>
@@ -6020,10 +6021,10 @@
         <v>3362</v>
       </c>
       <c r="F22" t="n">
-        <v>14771.6</v>
+        <v>14919.6</v>
       </c>
       <c r="G22" t="n">
-        <v>5852.5</v>
+        <v>6011.5</v>
       </c>
     </row>
     <row r="23">
@@ -6034,7 +6035,7 @@
         <v>20503</v>
       </c>
       <c r="C23" t="n">
-        <v>16444</v>
+        <v>16512</v>
       </c>
       <c r="D23" t="n">
         <v>6196</v>
@@ -6043,10 +6044,10 @@
         <v>3362</v>
       </c>
       <c r="F23" t="n">
-        <v>14771.6</v>
+        <v>14919.6</v>
       </c>
       <c r="G23" t="n">
-        <v>5852.5</v>
+        <v>5812.5</v>
       </c>
     </row>
     <row r="24">
@@ -6057,7 +6058,7 @@
         <v>20503</v>
       </c>
       <c r="C24" t="n">
-        <v>16444</v>
+        <v>16512</v>
       </c>
       <c r="D24" t="n">
         <v>6324</v>
@@ -6066,10 +6067,10 @@
         <v>3362</v>
       </c>
       <c r="F24" t="n">
-        <v>14880.6</v>
+        <v>15028.6</v>
       </c>
       <c r="G24" t="n">
-        <v>5852.5</v>
+        <v>5812.5</v>
       </c>
     </row>
     <row r="25">
@@ -6080,7 +6081,7 @@
         <v>20973</v>
       </c>
       <c r="C25" t="n">
-        <v>16624</v>
+        <v>16692</v>
       </c>
       <c r="D25" t="n">
         <v>6324</v>
@@ -6089,10 +6090,10 @@
         <v>3362</v>
       </c>
       <c r="F25" t="n">
-        <v>14880.6</v>
+        <v>15028.6</v>
       </c>
       <c r="G25" t="n">
-        <v>5852.5</v>
+        <v>5812.5</v>
       </c>
     </row>
     <row r="26">
@@ -6103,7 +6104,7 @@
         <v>20973</v>
       </c>
       <c r="C26" t="n">
-        <v>16624</v>
+        <v>16692</v>
       </c>
       <c r="D26" t="n">
         <v>6324</v>
@@ -6112,10 +6113,10 @@
         <v>3362</v>
       </c>
       <c r="F26" t="n">
-        <v>14880.6</v>
+        <v>15028.6</v>
       </c>
       <c r="G26" t="n">
-        <v>5852.5</v>
+        <v>5812.5</v>
       </c>
     </row>
     <row r="27">
@@ -6126,7 +6127,7 @@
         <v>21078</v>
       </c>
       <c r="C27" t="n">
-        <v>16624</v>
+        <v>16692</v>
       </c>
       <c r="D27" t="n">
         <v>6324</v>
@@ -6135,10 +6136,10 @@
         <v>3362</v>
       </c>
       <c r="F27" t="n">
-        <v>14880.6</v>
+        <v>15028.6</v>
       </c>
       <c r="G27" t="n">
-        <v>5852.5</v>
+        <v>5812.5</v>
       </c>
     </row>
     <row r="28">
@@ -6149,7 +6150,7 @@
         <v>21227</v>
       </c>
       <c r="C28" t="n">
-        <v>16783</v>
+        <v>16851</v>
       </c>
       <c r="D28" t="n">
         <v>6429</v>
@@ -6158,10 +6159,10 @@
         <v>3362</v>
       </c>
       <c r="F28" t="n">
-        <v>14880.6</v>
+        <v>15028.6</v>
       </c>
       <c r="G28" t="n">
-        <v>5852.5</v>
+        <v>5812.5</v>
       </c>
     </row>
     <row r="29">
@@ -6172,7 +6173,7 @@
         <v>21227</v>
       </c>
       <c r="C29" t="n">
-        <v>16963</v>
+        <v>17031</v>
       </c>
       <c r="D29" t="n">
         <v>6429</v>
@@ -6181,10 +6182,10 @@
         <v>3362</v>
       </c>
       <c r="F29" t="n">
-        <v>14880.6</v>
+        <v>15028.6</v>
       </c>
       <c r="G29" t="n">
-        <v>5852.5</v>
+        <v>5812.5</v>
       </c>
     </row>
     <row r="30">
@@ -6195,7 +6196,7 @@
         <v>19727</v>
       </c>
       <c r="C30" t="n">
-        <v>16963</v>
+        <v>17031</v>
       </c>
       <c r="D30" t="n">
         <v>6429</v>
@@ -6204,10 +6205,10 @@
         <v>3362</v>
       </c>
       <c r="F30" t="n">
-        <v>14880.6</v>
+        <v>15028.6</v>
       </c>
       <c r="G30" t="n">
-        <v>5852.5</v>
+        <v>5812.5</v>
       </c>
     </row>
     <row r="31">
@@ -6218,7 +6219,7 @@
         <v>19789</v>
       </c>
       <c r="C31" t="n">
-        <v>16963</v>
+        <v>17031</v>
       </c>
       <c r="D31" t="n">
         <v>6429</v>
@@ -6227,10 +6228,10 @@
         <v>3362</v>
       </c>
       <c r="F31" t="n">
-        <v>14880.6</v>
+        <v>15028.6</v>
       </c>
       <c r="G31" t="n">
-        <v>5852.5</v>
+        <v>5812.5</v>
       </c>
     </row>
     <row r="32">
@@ -6241,7 +6242,7 @@
         <v>19789</v>
       </c>
       <c r="C32" t="n">
-        <v>16963</v>
+        <v>17031</v>
       </c>
       <c r="D32" t="n">
         <v>6638</v>
@@ -6250,10 +6251,10 @@
         <v>3362</v>
       </c>
       <c r="F32" t="n">
-        <v>14880.6</v>
+        <v>15028.6</v>
       </c>
       <c r="G32" t="n">
-        <v>5852.5</v>
+        <v>5812.5</v>
       </c>
     </row>
     <row r="33">
@@ -6264,7 +6265,7 @@
         <v>20330</v>
       </c>
       <c r="C33" t="n">
-        <v>16963</v>
+        <v>17031</v>
       </c>
       <c r="D33" t="n">
         <v>6638</v>
@@ -6273,10 +6274,10 @@
         <v>3362</v>
       </c>
       <c r="F33" t="n">
-        <v>14880.6</v>
+        <v>15028.6</v>
       </c>
       <c r="G33" t="n">
-        <v>5852.5</v>
+        <v>5812.5</v>
       </c>
     </row>
     <row r="34">
@@ -6287,7 +6288,7 @@
         <v>20330</v>
       </c>
       <c r="C34" t="n">
-        <v>16963</v>
+        <v>17031</v>
       </c>
       <c r="D34" t="n">
         <v>6638</v>
@@ -6296,10 +6297,10 @@
         <v>3362</v>
       </c>
       <c r="F34" t="n">
-        <v>14880.6</v>
+        <v>15028.6</v>
       </c>
       <c r="G34" t="n">
-        <v>5852.5</v>
+        <v>5812.5</v>
       </c>
     </row>
     <row r="35">
@@ -6310,7 +6311,7 @@
         <v>20704</v>
       </c>
       <c r="C35" t="n">
-        <v>16963</v>
+        <v>17031</v>
       </c>
       <c r="D35" t="n">
         <v>6638</v>
@@ -6319,10 +6320,10 @@
         <v>3362</v>
       </c>
       <c r="F35" t="n">
-        <v>14880.6</v>
+        <v>15028.6</v>
       </c>
       <c r="G35" t="n">
-        <v>5852.5</v>
+        <v>5812.5</v>
       </c>
     </row>
     <row r="36">
@@ -6333,7 +6334,7 @@
         <v>20704</v>
       </c>
       <c r="C36" t="n">
-        <v>16963</v>
+        <v>17031</v>
       </c>
       <c r="D36" t="n">
         <v>6841</v>
@@ -6342,10 +6343,10 @@
         <v>3362</v>
       </c>
       <c r="F36" t="n">
-        <v>15006.6</v>
+        <v>15154.6</v>
       </c>
       <c r="G36" t="n">
-        <v>5852.5</v>
+        <v>5884.5</v>
       </c>
     </row>
     <row r="37">
@@ -6356,7 +6357,7 @@
         <v>20704</v>
       </c>
       <c r="C37" t="n">
-        <v>16963</v>
+        <v>17031</v>
       </c>
       <c r="D37" t="n">
         <v>6878</v>
@@ -6365,10 +6366,10 @@
         <v>3362</v>
       </c>
       <c r="F37" t="n">
-        <v>15006.6</v>
+        <v>15154.6</v>
       </c>
       <c r="G37" t="n">
-        <v>5852.5</v>
+        <v>5884.5</v>
       </c>
     </row>
     <row r="38">
@@ -6379,7 +6380,7 @@
         <v>20704</v>
       </c>
       <c r="C38" t="n">
-        <v>16963</v>
+        <v>17031</v>
       </c>
       <c r="D38" t="n">
         <v>6878</v>
@@ -6388,10 +6389,10 @@
         <v>3362</v>
       </c>
       <c r="F38" t="n">
-        <v>15006.6</v>
+        <v>15154.6</v>
       </c>
       <c r="G38" t="n">
-        <v>5852.5</v>
+        <v>5884.5</v>
       </c>
     </row>
     <row r="39">
@@ -6402,7 +6403,7 @@
         <v>20704</v>
       </c>
       <c r="C39" t="n">
-        <v>16963</v>
+        <v>17031</v>
       </c>
       <c r="D39" t="n">
         <v>6878</v>
@@ -6411,10 +6412,10 @@
         <v>3362</v>
       </c>
       <c r="F39" t="n">
-        <v>15006.6</v>
+        <v>15154.6</v>
       </c>
       <c r="G39" t="n">
-        <v>5852.5</v>
+        <v>5884.5</v>
       </c>
     </row>
     <row r="40">
@@ -6425,7 +6426,7 @@
         <v>20704</v>
       </c>
       <c r="C40" t="n">
-        <v>16963</v>
+        <v>17031</v>
       </c>
       <c r="D40" t="n">
         <v>6878</v>
@@ -6434,10 +6435,10 @@
         <v>3362</v>
       </c>
       <c r="F40" t="n">
-        <v>15004.6</v>
+        <v>15152.6</v>
       </c>
       <c r="G40" t="n">
-        <v>5852.5</v>
+        <v>5884.5</v>
       </c>
     </row>
     <row r="41">
@@ -6448,7 +6449,7 @@
         <v>20704</v>
       </c>
       <c r="C41" t="n">
-        <v>16963</v>
+        <v>17031</v>
       </c>
       <c r="D41" t="n">
         <v>6878</v>
@@ -6457,10 +6458,10 @@
         <v>3362</v>
       </c>
       <c r="F41" t="n">
-        <v>15004.6</v>
+        <v>15152.6</v>
       </c>
       <c r="G41" t="n">
-        <v>5852.5</v>
+        <v>5884.5</v>
       </c>
     </row>
     <row r="42">
@@ -6471,7 +6472,7 @@
         <v>21197</v>
       </c>
       <c r="C42" t="n">
-        <v>16963</v>
+        <v>17031</v>
       </c>
       <c r="D42" t="n">
         <v>6878</v>
@@ -6480,10 +6481,10 @@
         <v>3362</v>
       </c>
       <c r="F42" t="n">
-        <v>15100.6</v>
+        <v>15248.6</v>
       </c>
       <c r="G42" t="n">
-        <v>5852.5</v>
+        <v>5884.5</v>
       </c>
     </row>
     <row r="43">
@@ -6494,7 +6495,7 @@
         <v>21197</v>
       </c>
       <c r="C43" t="n">
-        <v>16963</v>
+        <v>17031</v>
       </c>
       <c r="D43" t="n">
         <v>6878</v>
@@ -6503,10 +6504,10 @@
         <v>3362</v>
       </c>
       <c r="F43" t="n">
-        <v>15142.6</v>
+        <v>15290.6</v>
       </c>
       <c r="G43" t="n">
-        <v>5852.5</v>
+        <v>5884.5</v>
       </c>
     </row>
     <row r="44">
@@ -6517,7 +6518,7 @@
         <v>21197</v>
       </c>
       <c r="C44" t="n">
-        <v>16963</v>
+        <v>17031</v>
       </c>
       <c r="D44" t="n">
         <v>6878</v>
@@ -6526,10 +6527,10 @@
         <v>3362</v>
       </c>
       <c r="F44" t="n">
-        <v>15453.6</v>
+        <v>15601.6</v>
       </c>
       <c r="G44" t="n">
-        <v>5852.5</v>
+        <v>5884.5</v>
       </c>
     </row>
     <row r="45">
@@ -6540,7 +6541,7 @@
         <v>21197</v>
       </c>
       <c r="C45" t="n">
-        <v>17918</v>
+        <v>17986</v>
       </c>
       <c r="D45" t="n">
         <v>6878</v>
@@ -6549,10 +6550,10 @@
         <v>3362</v>
       </c>
       <c r="F45" t="n">
-        <v>16209.6</v>
+        <v>16357.6</v>
       </c>
       <c r="G45" t="n">
-        <v>5852.5</v>
+        <v>5930.5</v>
       </c>
     </row>
     <row r="46">
@@ -6563,7 +6564,7 @@
         <v>21599</v>
       </c>
       <c r="C46" t="n">
-        <v>17965</v>
+        <v>18033</v>
       </c>
       <c r="D46" t="n">
         <v>7028</v>
@@ -6572,10 +6573,10 @@
         <v>3362</v>
       </c>
       <c r="F46" t="n">
-        <v>16209.6</v>
+        <v>16357.6</v>
       </c>
       <c r="G46" t="n">
-        <v>5852.5</v>
+        <v>5930.5</v>
       </c>
     </row>
     <row r="47">
@@ -6586,7 +6587,7 @@
         <v>21599</v>
       </c>
       <c r="C47" t="n">
-        <v>18136</v>
+        <v>18204</v>
       </c>
       <c r="D47" t="n">
         <v>6869</v>
@@ -6595,10 +6596,10 @@
         <v>3362</v>
       </c>
       <c r="F47" t="n">
-        <v>16209.6</v>
+        <v>16357.6</v>
       </c>
       <c r="G47" t="n">
-        <v>5852.5</v>
+        <v>5930.5</v>
       </c>
     </row>
     <row r="48">
@@ -6609,7 +6610,7 @@
         <v>21599</v>
       </c>
       <c r="C48" t="n">
-        <v>18136</v>
+        <v>18204</v>
       </c>
       <c r="D48" t="n">
         <v>6869</v>
@@ -6618,10 +6619,10 @@
         <v>3362</v>
       </c>
       <c r="F48" t="n">
-        <v>16360.6</v>
+        <v>16508.6</v>
       </c>
       <c r="G48" t="n">
-        <v>5852.5</v>
+        <v>5930.5</v>
       </c>
     </row>
     <row r="49">
@@ -6632,7 +6633,7 @@
         <v>22426</v>
       </c>
       <c r="C49" t="n">
-        <v>18136</v>
+        <v>18204</v>
       </c>
       <c r="D49" t="n">
         <v>6869</v>
@@ -6641,10 +6642,10 @@
         <v>3362</v>
       </c>
       <c r="F49" t="n">
-        <v>16393.6</v>
+        <v>16541.6</v>
       </c>
       <c r="G49" t="n">
-        <v>5852.5</v>
+        <v>5930.5</v>
       </c>
     </row>
     <row r="50">
@@ -6655,7 +6656,7 @@
         <v>22426</v>
       </c>
       <c r="C50" t="n">
-        <v>18311</v>
+        <v>18379</v>
       </c>
       <c r="D50" t="n">
         <v>6869</v>
@@ -6664,10 +6665,10 @@
         <v>3362</v>
       </c>
       <c r="F50" t="n">
-        <v>16393.6</v>
+        <v>16541.6</v>
       </c>
       <c r="G50" t="n">
-        <v>5852.5</v>
+        <v>5930.5</v>
       </c>
     </row>
     <row r="51">
@@ -6678,7 +6679,7 @@
         <v>22364</v>
       </c>
       <c r="C51" t="n">
-        <v>18311</v>
+        <v>18379</v>
       </c>
       <c r="D51" t="n">
         <v>6869</v>
@@ -6687,10 +6688,10 @@
         <v>3362</v>
       </c>
       <c r="F51" t="n">
-        <v>16393.6</v>
+        <v>16541.6</v>
       </c>
       <c r="G51" t="n">
-        <v>5852.5</v>
+        <v>5930.5</v>
       </c>
     </row>
     <row r="52">
@@ -6701,7 +6702,7 @@
         <v>23114</v>
       </c>
       <c r="C52" t="n">
-        <v>18846</v>
+        <v>18914</v>
       </c>
       <c r="D52" t="n">
         <v>6869</v>
@@ -6710,10 +6711,10 @@
         <v>3362</v>
       </c>
       <c r="F52" t="n">
-        <v>16393.6</v>
+        <v>16541.6</v>
       </c>
       <c r="G52" t="n">
-        <v>5852.5</v>
+        <v>5930.5</v>
       </c>
     </row>
     <row r="53">
@@ -6724,7 +6725,7 @@
         <v>23114</v>
       </c>
       <c r="C53" t="n">
-        <v>18949</v>
+        <v>19017</v>
       </c>
       <c r="D53" t="n">
         <v>6869</v>
@@ -6733,10 +6734,10 @@
         <v>3362</v>
       </c>
       <c r="F53" t="n">
-        <v>16393.6</v>
+        <v>16541.6</v>
       </c>
       <c r="G53" t="n">
-        <v>5852.5</v>
+        <v>5968.5</v>
       </c>
     </row>
     <row r="54">
@@ -6747,7 +6748,7 @@
         <v>23114</v>
       </c>
       <c r="C54" t="n">
-        <v>18949</v>
+        <v>19017</v>
       </c>
       <c r="D54" t="n">
         <v>6869</v>
@@ -6756,10 +6757,10 @@
         <v>3362</v>
       </c>
       <c r="F54" t="n">
-        <v>16393.6</v>
+        <v>16541.6</v>
       </c>
       <c r="G54" t="n">
-        <v>5852.5</v>
+        <v>5968.5</v>
       </c>
     </row>
     <row r="55">
@@ -6770,7 +6771,7 @@
         <v>23580</v>
       </c>
       <c r="C55" t="n">
-        <v>19201</v>
+        <v>19269</v>
       </c>
       <c r="D55" t="n">
         <v>6869</v>
@@ -6779,10 +6780,10 @@
         <v>3362</v>
       </c>
       <c r="F55" t="n">
-        <v>16419.6</v>
+        <v>16567.6</v>
       </c>
       <c r="G55" t="n">
-        <v>5852.5</v>
+        <v>5968.5</v>
       </c>
     </row>
     <row r="56">
@@ -6793,7 +6794,7 @@
         <v>23580</v>
       </c>
       <c r="C56" t="n">
-        <v>19201</v>
+        <v>19269</v>
       </c>
       <c r="D56" t="n">
         <v>6869</v>
@@ -6802,10 +6803,10 @@
         <v>3362</v>
       </c>
       <c r="F56" t="n">
-        <v>16419.6</v>
+        <v>16567.6</v>
       </c>
       <c r="G56" t="n">
-        <v>5852.5</v>
+        <v>5968.5</v>
       </c>
     </row>
     <row r="57">
@@ -6816,7 +6817,7 @@
         <v>23580</v>
       </c>
       <c r="C57" t="n">
-        <v>19201</v>
+        <v>19269</v>
       </c>
       <c r="D57" t="n">
         <v>6869</v>
@@ -6825,10 +6826,10 @@
         <v>3362</v>
       </c>
       <c r="F57" t="n">
-        <v>16419.6</v>
+        <v>16567.6</v>
       </c>
       <c r="G57" t="n">
-        <v>5852.5</v>
+        <v>5968.5</v>
       </c>
     </row>
     <row r="58">
@@ -6839,7 +6840,7 @@
         <v>23580</v>
       </c>
       <c r="C58" t="n">
-        <v>19355</v>
+        <v>19423</v>
       </c>
       <c r="D58" t="n">
         <v>6869</v>
@@ -6848,10 +6849,10 @@
         <v>3362</v>
       </c>
       <c r="F58" t="n">
-        <v>16766.6</v>
+        <v>16914.6</v>
       </c>
       <c r="G58" t="n">
-        <v>5852.5</v>
+        <v>5968.5</v>
       </c>
     </row>
     <row r="59">
@@ -6862,7 +6863,7 @@
         <v>23580</v>
       </c>
       <c r="C59" t="n">
-        <v>19355</v>
+        <v>19423</v>
       </c>
       <c r="D59" t="n">
         <v>6872</v>
@@ -6871,10 +6872,10 @@
         <v>3362</v>
       </c>
       <c r="F59" t="n">
-        <v>16766.6</v>
+        <v>16914.6</v>
       </c>
       <c r="G59" t="n">
-        <v>5852.5</v>
+        <v>5968.5</v>
       </c>
     </row>
     <row r="60">
@@ -6885,7 +6886,7 @@
         <v>23842</v>
       </c>
       <c r="C60" t="n">
-        <v>19477</v>
+        <v>19545</v>
       </c>
       <c r="D60" t="n">
         <v>6872</v>
@@ -6894,10 +6895,10 @@
         <v>3362</v>
       </c>
       <c r="F60" t="n">
-        <v>16952.6</v>
+        <v>17100.6</v>
       </c>
       <c r="G60" t="n">
-        <v>5852.5</v>
+        <v>5968.5</v>
       </c>
     </row>
     <row r="61">
@@ -6908,7 +6909,7 @@
         <v>23842</v>
       </c>
       <c r="C61" t="n">
-        <v>19845</v>
+        <v>19913</v>
       </c>
       <c r="D61" t="n">
         <v>6872</v>
@@ -6917,10 +6918,10 @@
         <v>3362</v>
       </c>
       <c r="F61" t="n">
-        <v>16952.6</v>
+        <v>17100.6</v>
       </c>
       <c r="G61" t="n">
-        <v>5852.5</v>
+        <v>5968.5</v>
       </c>
     </row>
     <row r="62">
@@ -6931,7 +6932,7 @@
         <v>23965</v>
       </c>
       <c r="C62" t="n">
-        <v>19845</v>
+        <v>19913</v>
       </c>
       <c r="D62" t="n">
         <v>6872</v>
@@ -6940,10 +6941,10 @@
         <v>3362</v>
       </c>
       <c r="F62" t="n">
-        <v>17528.6</v>
+        <v>17676.6</v>
       </c>
       <c r="G62" t="n">
-        <v>5852.5</v>
+        <v>5968.5</v>
       </c>
     </row>
     <row r="63">
@@ -6954,7 +6955,7 @@
         <v>23965</v>
       </c>
       <c r="C63" t="n">
-        <v>19946</v>
+        <v>20014</v>
       </c>
       <c r="D63" t="n">
         <v>6872</v>
@@ -6963,10 +6964,10 @@
         <v>3362</v>
       </c>
       <c r="F63" t="n">
-        <v>17622.6</v>
+        <v>17770.6</v>
       </c>
       <c r="G63" t="n">
-        <v>5852.5</v>
+        <v>5968.5</v>
       </c>
     </row>
     <row r="64">
@@ -6977,7 +6978,7 @@
         <v>23965</v>
       </c>
       <c r="C64" t="n">
-        <v>19946</v>
+        <v>20014</v>
       </c>
       <c r="D64" t="n">
         <v>6872</v>
@@ -6986,10 +6987,10 @@
         <v>3362</v>
       </c>
       <c r="F64" t="n">
-        <v>17622.6</v>
+        <v>17770.6</v>
       </c>
       <c r="G64" t="n">
-        <v>5852.5</v>
+        <v>5968.5</v>
       </c>
     </row>
     <row r="65">
@@ -7000,7 +7001,7 @@
         <v>23996</v>
       </c>
       <c r="C65" t="n">
-        <v>20200</v>
+        <v>20268</v>
       </c>
       <c r="D65" t="n">
         <v>6872</v>
@@ -7009,10 +7010,10 @@
         <v>3362</v>
       </c>
       <c r="F65" t="n">
-        <v>17622.6</v>
+        <v>17770.6</v>
       </c>
       <c r="G65" t="n">
-        <v>5852.5</v>
+        <v>5968.5</v>
       </c>
     </row>
     <row r="66">
@@ -7023,7 +7024,7 @@
         <v>23996</v>
       </c>
       <c r="C66" t="n">
-        <v>20200</v>
+        <v>20268</v>
       </c>
       <c r="D66" t="n">
         <v>6872</v>
@@ -7032,10 +7033,10 @@
         <v>3362</v>
       </c>
       <c r="F66" t="n">
-        <v>17622.6</v>
+        <v>17770.6</v>
       </c>
       <c r="G66" t="n">
-        <v>5852.5</v>
+        <v>5968.5</v>
       </c>
     </row>
     <row r="67">
@@ -7046,7 +7047,7 @@
         <v>23996</v>
       </c>
       <c r="C67" t="n">
-        <v>20510</v>
+        <v>20578</v>
       </c>
       <c r="D67" t="n">
         <v>6872</v>
@@ -7055,10 +7056,10 @@
         <v>3362</v>
       </c>
       <c r="F67" t="n">
-        <v>17671.6</v>
+        <v>17819.6</v>
       </c>
       <c r="G67" t="n">
-        <v>5852.5</v>
+        <v>5968.5</v>
       </c>
     </row>
     <row r="68">
@@ -7069,7 +7070,7 @@
         <v>23996</v>
       </c>
       <c r="C68" t="n">
-        <v>20510</v>
+        <v>20578</v>
       </c>
       <c r="D68" t="n">
         <v>6872</v>
@@ -7078,10 +7079,10 @@
         <v>3362</v>
       </c>
       <c r="F68" t="n">
-        <v>17671.6</v>
+        <v>17819.6</v>
       </c>
       <c r="G68" t="n">
-        <v>5852.5</v>
+        <v>5968.5</v>
       </c>
     </row>
     <row r="69">
@@ -7092,7 +7093,7 @@
         <v>23994</v>
       </c>
       <c r="C69" t="n">
-        <v>20510</v>
+        <v>20578</v>
       </c>
       <c r="D69" t="n">
         <v>6872</v>
@@ -7101,10 +7102,10 @@
         <v>3362</v>
       </c>
       <c r="F69" t="n">
-        <v>17644.6</v>
+        <v>17792.6</v>
       </c>
       <c r="G69" t="n">
-        <v>5852.5</v>
+        <v>5968.5</v>
       </c>
     </row>
     <row r="70">
@@ -7115,7 +7116,7 @@
         <v>23939</v>
       </c>
       <c r="C70" t="n">
-        <v>20510</v>
+        <v>20578</v>
       </c>
       <c r="D70" t="n">
         <v>6872</v>
@@ -7124,10 +7125,10 @@
         <v>3362</v>
       </c>
       <c r="F70" t="n">
-        <v>17640.6</v>
+        <v>17788.6</v>
       </c>
       <c r="G70" t="n">
-        <v>5852.5</v>
+        <v>5968.5</v>
       </c>
     </row>
     <row r="71">
@@ -7151,6 +7152,40 @@
       </c>
       <c r="G71" t="n">
         <v>5852.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/au_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/au_power_capacity.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,12 +63,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -840,7 +841,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -855,7 +855,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -942,7 +941,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -971,7 +970,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1000,7 +999,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1029,7 +1028,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1058,7 +1057,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1087,7 +1086,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1116,7 +1115,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1145,7 +1144,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1174,7 +1173,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1203,7 +1202,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1232,7 +1231,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1261,7 +1260,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1290,7 +1289,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1319,7 +1318,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1348,7 +1347,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1377,7 +1376,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1406,7 +1405,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1435,7 +1434,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1464,7 +1463,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1493,7 +1492,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1522,7 +1521,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1551,7 +1550,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1580,7 +1579,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1609,7 +1608,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1638,7 +1637,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1667,7 +1666,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1696,7 +1695,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1725,7 +1724,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1754,7 +1753,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1783,7 +1782,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1812,7 +1811,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1841,7 +1840,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1870,7 +1869,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1899,7 +1898,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1928,7 +1927,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1957,7 +1956,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1986,7 +1985,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2015,7 +2014,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2044,7 +2043,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2073,7 +2072,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2102,7 +2101,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2131,7 +2130,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2160,7 +2159,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2189,7 +2188,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2218,7 +2217,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2247,7 +2246,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2276,7 +2275,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2305,7 +2304,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2334,7 +2333,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2363,7 +2362,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2392,7 +2391,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2421,7 +2420,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2450,7 +2449,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2479,7 +2478,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2508,7 +2507,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2537,7 +2536,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2566,7 +2565,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2595,7 +2594,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2624,7 +2623,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2653,7 +2652,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2682,7 +2681,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2711,7 +2710,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2740,7 +2739,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2769,7 +2768,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2798,7 +2797,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2827,7 +2826,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2856,7 +2855,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2885,7 +2884,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -2914,7 +2913,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="5" t="n">
         <v>46266</v>
       </c>
       <c r="B70" t="n">
@@ -2943,7 +2942,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="5" t="n">
         <v>46296</v>
       </c>
       <c r="B71" t="n">

--- a/output/Data and Chart Outputs/au_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/au_power_capacity.xlsx
@@ -158,6 +158,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Australia registered generating capacity (AEMO, NEM + WEM) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -179,7 +180,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -291,7 +292,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="2A78D6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -319,7 +320,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="4A3AA7"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>

--- a/output/Data and Chart Outputs/au_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/au_power_capacity.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,13 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -842,6 +841,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -856,6 +856,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -942,7 +943,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -971,7 +972,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1000,7 +1001,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1029,7 +1030,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1058,7 +1059,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1087,7 +1088,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1116,7 +1117,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1145,7 +1146,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1174,7 +1175,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1203,7 +1204,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1232,7 +1233,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1261,7 +1262,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1290,7 +1291,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1319,7 +1320,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1348,7 +1349,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1377,7 +1378,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1406,7 +1407,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1435,7 +1436,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1464,7 +1465,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1493,7 +1494,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1522,7 +1523,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1551,7 +1552,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1580,7 +1581,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1609,7 +1610,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1638,7 +1639,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1667,7 +1668,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1696,7 +1697,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1725,7 +1726,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1754,7 +1755,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1783,7 +1784,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1812,7 +1813,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1841,7 +1842,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1870,7 +1871,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1899,7 +1900,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1928,7 +1929,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1957,7 +1958,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1986,7 +1987,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2015,7 +2016,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2044,7 +2045,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2073,7 +2074,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2102,7 +2103,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2131,7 +2132,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2160,7 +2161,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2189,7 +2190,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2218,7 +2219,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2247,7 +2248,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2276,7 +2277,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2305,7 +2306,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2334,7 +2335,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2363,7 +2364,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2392,7 +2393,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2421,7 +2422,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2450,7 +2451,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2479,7 +2480,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2508,7 +2509,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2537,7 +2538,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2566,7 +2567,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2595,7 +2596,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2624,7 +2625,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2653,7 +2654,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2682,7 +2683,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2711,7 +2712,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2740,7 +2741,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2769,7 +2770,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2798,7 +2799,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2827,7 +2828,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2856,7 +2857,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2885,7 +2886,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -2914,7 +2915,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="n">
+      <c r="A70" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B70" t="n">
@@ -2943,7 +2944,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="n">
+      <c r="A71" s="3" t="n">
         <v>46296</v>
       </c>
       <c r="B71" t="n">
@@ -2953,7 +2954,7 @@
         <v>15.5077</v>
       </c>
       <c r="D71" t="n">
-        <v>16.1477</v>
+        <v>16.5617</v>
       </c>
       <c r="E71" t="n">
         <v>15.072</v>
@@ -5469,7 +5470,7 @@
         <v>15507.7</v>
       </c>
       <c r="D71" t="n">
-        <v>16147.7</v>
+        <v>16561.7</v>
       </c>
       <c r="E71" t="n">
         <v>15072</v>
@@ -5484,7 +5485,7 @@
         <v>425</v>
       </c>
       <c r="I71" t="n">
-        <v>77380.10000000001</v>
+        <v>77794.10000000001</v>
       </c>
       <c r="J71" t="n">
         <v>13729.4</v>
@@ -7136,7 +7137,7 @@
         <v>46296</v>
       </c>
       <c r="B71" t="n">
-        <v>23796.3</v>
+        <v>24210.3</v>
       </c>
       <c r="C71" t="n">
         <v>20482.9</v>
